--- a/assets/Listados/CJLL - 3415417 - 2026.xlsx
+++ b/assets/Listados/CJLL - 3415417 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CE9F69-4408-46A1-B412-AECE0E397079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A84F680-8436-41BC-BBC6-BD7C86F99F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="403">
   <si>
     <r>
       <rPr>
@@ -275,9 +275,6 @@
     <t>12 COMUNICACIÓN COMERCIAL Y MARKETING.</t>
   </si>
   <si>
-    <t>NO MATRICULADO</t>
-  </si>
-  <si>
     <t>ASIATE</t>
   </si>
   <si>
@@ -481,9 +478,6 @@
   </si>
   <si>
     <t xml:space="preserve">CORREO </t>
-  </si>
-  <si>
-    <t>NOMBRE DEL GRUPO</t>
   </si>
   <si>
     <t xml:space="preserve">N° 2 </t>
@@ -1287,9 +1281,6 @@
     <t>Camacho Bejarano</t>
   </si>
   <si>
-    <t>Gabriela s</t>
-  </si>
-  <si>
     <t>Quinchía Torre</t>
   </si>
   <si>
@@ -1407,13 +1398,43 @@
     <t>Ramos Villada</t>
   </si>
   <si>
-    <t xml:space="preserve">Laura Camila </t>
+    <t>https://drive.google.com/drive/folders/1e5MnNm38wj8rlME9h65wZQxm8wT1fW3i</t>
   </si>
   <si>
-    <t>Gómez Beltrán</t>
+    <t>DELI DELI POSTRES</t>
   </si>
   <si>
-    <t>https://drive.google.com/drive/folders/1e5MnNm38wj8rlME9h65wZQxm8wT1fW3i</t>
+    <t xml:space="preserve">DULCE FRAGANCIA </t>
+  </si>
+  <si>
+    <t>RITMO CAFÉ</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA COLIBRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriela </t>
+  </si>
+  <si>
+    <t>BEAUTY LAB</t>
+  </si>
+  <si>
+    <t>PINKY GLOW</t>
+  </si>
+  <si>
+    <t>KUMENZA</t>
+  </si>
+  <si>
+    <t>JEANSCOLOM</t>
+  </si>
+  <si>
+    <t>SUGAR RUNNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Luis </t>
+  </si>
+  <si>
+    <t>Ochoa Bayona</t>
   </si>
 </sst>
 </file>
@@ -3133,6 +3154,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3348,17 +3372,14 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -5125,125 +5146,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="176"/>
-      <c r="B1" s="177"/>
-      <c r="C1" s="180" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="156" t="s">
+      <c r="A1" s="179"/>
+      <c r="B1" s="180"/>
+      <c r="C1" s="183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="160"/>
-      <c r="T1" s="164"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="165"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="105"/>
-      <c r="AB1" s="164"/>
-      <c r="AC1" s="105"/>
-      <c r="AD1" s="105"/>
-      <c r="AE1" s="105"/>
-      <c r="AF1" s="105"/>
-      <c r="AG1" s="105"/>
-      <c r="AH1" s="105"/>
-      <c r="AI1" s="105"/>
-      <c r="AJ1" s="105"/>
-      <c r="AK1" s="108"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="105"/>
-      <c r="AN1" s="105"/>
-      <c r="AO1" s="105"/>
-      <c r="AP1" s="105"/>
-      <c r="AQ1" s="105"/>
-      <c r="AR1" s="105"/>
-      <c r="AS1" s="105"/>
-      <c r="AT1" s="105"/>
-      <c r="AU1" s="106"/>
-      <c r="AV1" s="105"/>
-      <c r="AW1" s="105"/>
-      <c r="AX1" s="105"/>
-      <c r="AY1" s="105"/>
-      <c r="AZ1" s="105"/>
-      <c r="BA1" s="105"/>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
-      <c r="BD1" s="105"/>
-      <c r="BE1" s="105"/>
-      <c r="BF1" s="105"/>
-      <c r="BG1" s="105"/>
-      <c r="BH1" s="105"/>
-      <c r="BI1" s="105"/>
-      <c r="BJ1" s="105"/>
-      <c r="BK1" s="105"/>
-      <c r="BL1" s="105"/>
-      <c r="BM1" s="105"/>
-      <c r="BN1" s="105"/>
-      <c r="BO1" s="105"/>
-      <c r="BP1" s="105"/>
-      <c r="BQ1" s="105"/>
-      <c r="BR1" s="105"/>
-      <c r="BS1" s="105"/>
-      <c r="BT1" s="105"/>
-      <c r="BU1" s="105"/>
-      <c r="BV1" s="107"/>
-      <c r="BW1" s="105"/>
-      <c r="BX1" s="105"/>
-      <c r="BY1" s="105"/>
-      <c r="BZ1" s="105"/>
-      <c r="CA1" s="105"/>
-      <c r="CB1" s="105"/>
-      <c r="CC1" s="105"/>
-      <c r="CD1" s="105"/>
-      <c r="CE1" s="105"/>
-      <c r="CF1" s="105"/>
-      <c r="CG1" s="105"/>
-      <c r="CH1" s="105"/>
-      <c r="CI1" s="105"/>
-      <c r="CJ1" s="105"/>
-      <c r="CK1" s="105"/>
-      <c r="CL1" s="105"/>
-      <c r="CM1" s="105"/>
-      <c r="CN1" s="105"/>
-      <c r="CO1" s="105"/>
-      <c r="CP1" s="105"/>
-      <c r="CQ1" s="105"/>
-      <c r="CR1" s="108"/>
-      <c r="CS1" s="111" t="s">
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="163"/>
+      <c r="T1" s="167"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="168"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="167"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="111"/>
+      <c r="AL1" s="107"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="108"/>
+      <c r="AT1" s="108"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="108"/>
+      <c r="AW1" s="108"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="108"/>
+      <c r="BG1" s="108"/>
+      <c r="BH1" s="108"/>
+      <c r="BI1" s="108"/>
+      <c r="BJ1" s="108"/>
+      <c r="BK1" s="108"/>
+      <c r="BL1" s="108"/>
+      <c r="BM1" s="108"/>
+      <c r="BN1" s="108"/>
+      <c r="BO1" s="108"/>
+      <c r="BP1" s="108"/>
+      <c r="BQ1" s="108"/>
+      <c r="BR1" s="108"/>
+      <c r="BS1" s="108"/>
+      <c r="BT1" s="108"/>
+      <c r="BU1" s="108"/>
+      <c r="BV1" s="110"/>
+      <c r="BW1" s="108"/>
+      <c r="BX1" s="108"/>
+      <c r="BY1" s="108"/>
+      <c r="BZ1" s="108"/>
+      <c r="CA1" s="108"/>
+      <c r="CB1" s="108"/>
+      <c r="CC1" s="108"/>
+      <c r="CD1" s="108"/>
+      <c r="CE1" s="108"/>
+      <c r="CF1" s="108"/>
+      <c r="CG1" s="108"/>
+      <c r="CH1" s="108"/>
+      <c r="CI1" s="108"/>
+      <c r="CJ1" s="108"/>
+      <c r="CK1" s="108"/>
+      <c r="CL1" s="108"/>
+      <c r="CM1" s="108"/>
+      <c r="CN1" s="108"/>
+      <c r="CO1" s="108"/>
+      <c r="CP1" s="108"/>
+      <c r="CQ1" s="108"/>
+      <c r="CR1" s="111"/>
+      <c r="CS1" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="112"/>
-      <c r="CU1" s="112"/>
-      <c r="CV1" s="112"/>
-      <c r="CW1" s="113"/>
+      <c r="CT1" s="115"/>
+      <c r="CU1" s="115"/>
+      <c r="CV1" s="115"/>
+      <c r="CW1" s="116"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="128" t="s">
+      <c r="CY1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="115"/>
-      <c r="DA1" s="115"/>
-      <c r="DB1" s="115"/>
-      <c r="DC1" s="115"/>
-      <c r="DD1" s="115"/>
-      <c r="DE1" s="115"/>
-      <c r="DF1" s="115"/>
-      <c r="DG1" s="115"/>
+      <c r="CZ1" s="118"/>
+      <c r="DA1" s="118"/>
+      <c r="DB1" s="118"/>
+      <c r="DC1" s="118"/>
+      <c r="DD1" s="118"/>
+      <c r="DE1" s="118"/>
+      <c r="DF1" s="118"/>
+      <c r="DG1" s="118"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -5262,122 +5283,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="178"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="179"/>
-      <c r="G2" s="156" t="s">
+      <c r="A2" s="181"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="181"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="158"/>
-      <c r="S2" s="158"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="110"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="124"/>
-      <c r="Y2" s="110"/>
-      <c r="Z2" s="110"/>
-      <c r="AA2" s="110"/>
-      <c r="AB2" s="166"/>
-      <c r="AC2" s="110"/>
-      <c r="AD2" s="110"/>
-      <c r="AE2" s="110"/>
-      <c r="AF2" s="110"/>
-      <c r="AG2" s="110"/>
-      <c r="AH2" s="110"/>
-      <c r="AI2" s="110"/>
-      <c r="AJ2" s="110"/>
-      <c r="AK2" s="122"/>
-      <c r="AL2" s="124"/>
-      <c r="AM2" s="110"/>
-      <c r="AN2" s="110"/>
-      <c r="AO2" s="110"/>
-      <c r="AP2" s="110"/>
-      <c r="AQ2" s="110"/>
-      <c r="AR2" s="110"/>
-      <c r="AS2" s="110"/>
-      <c r="AT2" s="110"/>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="110"/>
-      <c r="AW2" s="110"/>
-      <c r="AX2" s="110"/>
-      <c r="AY2" s="110"/>
-      <c r="AZ2" s="110"/>
-      <c r="BA2" s="110"/>
-      <c r="BB2" s="110"/>
-      <c r="BC2" s="110"/>
-      <c r="BD2" s="110"/>
-      <c r="BE2" s="110"/>
-      <c r="BF2" s="110"/>
-      <c r="BG2" s="110"/>
-      <c r="BH2" s="110"/>
-      <c r="BI2" s="110"/>
-      <c r="BJ2" s="110"/>
-      <c r="BK2" s="110"/>
-      <c r="BL2" s="110"/>
-      <c r="BM2" s="110"/>
-      <c r="BN2" s="110"/>
-      <c r="BO2" s="110"/>
-      <c r="BP2" s="110"/>
-      <c r="BQ2" s="110"/>
-      <c r="BR2" s="110"/>
-      <c r="BS2" s="110"/>
-      <c r="BT2" s="110"/>
-      <c r="BU2" s="110"/>
-      <c r="BV2" s="121"/>
-      <c r="BW2" s="110"/>
-      <c r="BX2" s="110"/>
-      <c r="BY2" s="110"/>
-      <c r="BZ2" s="110"/>
-      <c r="CA2" s="110"/>
-      <c r="CB2" s="110"/>
-      <c r="CC2" s="110"/>
-      <c r="CD2" s="110"/>
-      <c r="CE2" s="110"/>
-      <c r="CF2" s="110"/>
-      <c r="CG2" s="110"/>
-      <c r="CH2" s="110"/>
-      <c r="CI2" s="110"/>
-      <c r="CJ2" s="110"/>
-      <c r="CK2" s="110"/>
-      <c r="CL2" s="110"/>
-      <c r="CM2" s="110"/>
-      <c r="CN2" s="110"/>
-      <c r="CO2" s="110"/>
-      <c r="CP2" s="110"/>
-      <c r="CQ2" s="110"/>
-      <c r="CR2" s="122"/>
-      <c r="CS2" s="114"/>
-      <c r="CT2" s="115"/>
-      <c r="CU2" s="115"/>
-      <c r="CV2" s="115"/>
-      <c r="CW2" s="116"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="123"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="169"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
+      <c r="AE2" s="113"/>
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="113"/>
+      <c r="AH2" s="113"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="113"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="127"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="113"/>
+      <c r="AP2" s="113"/>
+      <c r="AQ2" s="113"/>
+      <c r="AR2" s="113"/>
+      <c r="AS2" s="113"/>
+      <c r="AT2" s="113"/>
+      <c r="AU2" s="123"/>
+      <c r="AV2" s="113"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="113"/>
+      <c r="AY2" s="113"/>
+      <c r="AZ2" s="113"/>
+      <c r="BA2" s="113"/>
+      <c r="BB2" s="113"/>
+      <c r="BC2" s="113"/>
+      <c r="BD2" s="113"/>
+      <c r="BE2" s="113"/>
+      <c r="BF2" s="113"/>
+      <c r="BG2" s="113"/>
+      <c r="BH2" s="113"/>
+      <c r="BI2" s="113"/>
+      <c r="BJ2" s="113"/>
+      <c r="BK2" s="113"/>
+      <c r="BL2" s="113"/>
+      <c r="BM2" s="113"/>
+      <c r="BN2" s="113"/>
+      <c r="BO2" s="113"/>
+      <c r="BP2" s="113"/>
+      <c r="BQ2" s="113"/>
+      <c r="BR2" s="113"/>
+      <c r="BS2" s="113"/>
+      <c r="BT2" s="113"/>
+      <c r="BU2" s="113"/>
+      <c r="BV2" s="124"/>
+      <c r="BW2" s="113"/>
+      <c r="BX2" s="113"/>
+      <c r="BY2" s="113"/>
+      <c r="BZ2" s="113"/>
+      <c r="CA2" s="113"/>
+      <c r="CB2" s="113"/>
+      <c r="CC2" s="113"/>
+      <c r="CD2" s="113"/>
+      <c r="CE2" s="113"/>
+      <c r="CF2" s="113"/>
+      <c r="CG2" s="113"/>
+      <c r="CH2" s="113"/>
+      <c r="CI2" s="113"/>
+      <c r="CJ2" s="113"/>
+      <c r="CK2" s="113"/>
+      <c r="CL2" s="113"/>
+      <c r="CM2" s="113"/>
+      <c r="CN2" s="113"/>
+      <c r="CO2" s="113"/>
+      <c r="CP2" s="113"/>
+      <c r="CQ2" s="113"/>
+      <c r="CR2" s="125"/>
+      <c r="CS2" s="117"/>
+      <c r="CT2" s="118"/>
+      <c r="CU2" s="118"/>
+      <c r="CV2" s="118"/>
+      <c r="CW2" s="119"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="129">
+      <c r="CY2" s="132">
         <f>COUNTA('BASE DE DATOS'!B26:B50)</f>
         <v>25</v>
       </c>
-      <c r="CZ2" s="130"/>
-      <c r="DA2" s="130"/>
-      <c r="DB2" s="130"/>
-      <c r="DC2" s="130"/>
-      <c r="DD2" s="130"/>
-      <c r="DE2" s="130"/>
-      <c r="DF2" s="130"/>
-      <c r="DG2" s="130"/>
+      <c r="CZ2" s="133"/>
+      <c r="DA2" s="133"/>
+      <c r="DB2" s="133"/>
+      <c r="DC2" s="133"/>
+      <c r="DD2" s="133"/>
+      <c r="DE2" s="133"/>
+      <c r="DF2" s="133"/>
+      <c r="DG2" s="133"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -5396,113 +5417,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="159" t="s">
+      <c r="A3" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="161" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="110"/>
-      <c r="F3" s="160"/>
-      <c r="G3" s="168" t="s">
+      <c r="B3" s="113"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="164" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="113"/>
+      <c r="F3" s="163"/>
+      <c r="G3" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="152"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="110"/>
-      <c r="AB3" s="151"/>
-      <c r="AC3" s="110"/>
-      <c r="AD3" s="110"/>
-      <c r="AE3" s="110"/>
-      <c r="AF3" s="110"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="110"/>
-      <c r="AI3" s="110"/>
-      <c r="AJ3" s="110"/>
-      <c r="AK3" s="122"/>
-      <c r="AL3" s="109"/>
-      <c r="AM3" s="110"/>
-      <c r="AN3" s="110"/>
-      <c r="AO3" s="110"/>
-      <c r="AP3" s="110"/>
-      <c r="AQ3" s="110"/>
-      <c r="AR3" s="110"/>
-      <c r="AS3" s="110"/>
-      <c r="AT3" s="110"/>
-      <c r="AU3" s="135"/>
-      <c r="AV3" s="110"/>
-      <c r="AW3" s="110"/>
-      <c r="AX3" s="110"/>
-      <c r="AY3" s="110"/>
-      <c r="AZ3" s="110"/>
-      <c r="BA3" s="110"/>
-      <c r="BB3" s="110"/>
-      <c r="BC3" s="110"/>
-      <c r="BD3" s="110"/>
-      <c r="BE3" s="110"/>
-      <c r="BF3" s="110"/>
-      <c r="BG3" s="110"/>
-      <c r="BH3" s="110"/>
-      <c r="BI3" s="110"/>
-      <c r="BJ3" s="110"/>
-      <c r="BK3" s="110"/>
-      <c r="BL3" s="110"/>
-      <c r="BM3" s="110"/>
-      <c r="BN3" s="110"/>
-      <c r="BO3" s="110"/>
-      <c r="BP3" s="110"/>
-      <c r="BQ3" s="110"/>
-      <c r="BR3" s="110"/>
-      <c r="BS3" s="110"/>
-      <c r="BT3" s="110"/>
-      <c r="BU3" s="110"/>
-      <c r="BV3" s="123"/>
-      <c r="BW3" s="110"/>
-      <c r="BX3" s="110"/>
-      <c r="BY3" s="110"/>
-      <c r="BZ3" s="110"/>
-      <c r="CA3" s="110"/>
-      <c r="CB3" s="110"/>
-      <c r="CC3" s="110"/>
-      <c r="CD3" s="110"/>
-      <c r="CE3" s="110"/>
-      <c r="CF3" s="110"/>
-      <c r="CG3" s="110"/>
-      <c r="CH3" s="110"/>
-      <c r="CI3" s="110"/>
-      <c r="CJ3" s="110"/>
-      <c r="CK3" s="110"/>
-      <c r="CL3" s="110"/>
-      <c r="CM3" s="110"/>
-      <c r="CN3" s="110"/>
-      <c r="CO3" s="110"/>
-      <c r="CP3" s="110"/>
-      <c r="CQ3" s="110"/>
-      <c r="CR3" s="122"/>
-      <c r="CS3" s="114"/>
-      <c r="CT3" s="115"/>
-      <c r="CU3" s="115"/>
-      <c r="CV3" s="115"/>
-      <c r="CW3" s="116"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="113"/>
+      <c r="N3" s="113"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="165"/>
+      <c r="Q3" s="113"/>
+      <c r="R3" s="113"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="113"/>
+      <c r="V3" s="113"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="155"/>
+      <c r="Y3" s="113"/>
+      <c r="Z3" s="113"/>
+      <c r="AA3" s="113"/>
+      <c r="AB3" s="154"/>
+      <c r="AC3" s="113"/>
+      <c r="AD3" s="113"/>
+      <c r="AE3" s="113"/>
+      <c r="AF3" s="113"/>
+      <c r="AG3" s="113"/>
+      <c r="AH3" s="113"/>
+      <c r="AI3" s="113"/>
+      <c r="AJ3" s="113"/>
+      <c r="AK3" s="125"/>
+      <c r="AL3" s="112"/>
+      <c r="AM3" s="113"/>
+      <c r="AN3" s="113"/>
+      <c r="AO3" s="113"/>
+      <c r="AP3" s="113"/>
+      <c r="AQ3" s="113"/>
+      <c r="AR3" s="113"/>
+      <c r="AS3" s="113"/>
+      <c r="AT3" s="113"/>
+      <c r="AU3" s="138"/>
+      <c r="AV3" s="113"/>
+      <c r="AW3" s="113"/>
+      <c r="AX3" s="113"/>
+      <c r="AY3" s="113"/>
+      <c r="AZ3" s="113"/>
+      <c r="BA3" s="113"/>
+      <c r="BB3" s="113"/>
+      <c r="BC3" s="113"/>
+      <c r="BD3" s="113"/>
+      <c r="BE3" s="113"/>
+      <c r="BF3" s="113"/>
+      <c r="BG3" s="113"/>
+      <c r="BH3" s="113"/>
+      <c r="BI3" s="113"/>
+      <c r="BJ3" s="113"/>
+      <c r="BK3" s="113"/>
+      <c r="BL3" s="113"/>
+      <c r="BM3" s="113"/>
+      <c r="BN3" s="113"/>
+      <c r="BO3" s="113"/>
+      <c r="BP3" s="113"/>
+      <c r="BQ3" s="113"/>
+      <c r="BR3" s="113"/>
+      <c r="BS3" s="113"/>
+      <c r="BT3" s="113"/>
+      <c r="BU3" s="113"/>
+      <c r="BV3" s="126"/>
+      <c r="BW3" s="113"/>
+      <c r="BX3" s="113"/>
+      <c r="BY3" s="113"/>
+      <c r="BZ3" s="113"/>
+      <c r="CA3" s="113"/>
+      <c r="CB3" s="113"/>
+      <c r="CC3" s="113"/>
+      <c r="CD3" s="113"/>
+      <c r="CE3" s="113"/>
+      <c r="CF3" s="113"/>
+      <c r="CG3" s="113"/>
+      <c r="CH3" s="113"/>
+      <c r="CI3" s="113"/>
+      <c r="CJ3" s="113"/>
+      <c r="CK3" s="113"/>
+      <c r="CL3" s="113"/>
+      <c r="CM3" s="113"/>
+      <c r="CN3" s="113"/>
+      <c r="CO3" s="113"/>
+      <c r="CP3" s="113"/>
+      <c r="CQ3" s="113"/>
+      <c r="CR3" s="125"/>
+      <c r="CS3" s="117"/>
+      <c r="CT3" s="118"/>
+      <c r="CU3" s="118"/>
+      <c r="CV3" s="118"/>
+      <c r="CW3" s="119"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -5531,142 +5552,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="162" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="167" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="160"/>
-      <c r="G4" s="169" t="s">
+      <c r="B4" s="113"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="170" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="113"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="171"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
-      <c r="S4" s="126"/>
-      <c r="T4" s="172"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="126"/>
-      <c r="W4" s="127"/>
-      <c r="X4" s="173"/>
-      <c r="Y4" s="126"/>
-      <c r="Z4" s="126"/>
-      <c r="AA4" s="126"/>
-      <c r="AB4" s="174"/>
-      <c r="AC4" s="126"/>
-      <c r="AD4" s="126"/>
-      <c r="AE4" s="126"/>
-      <c r="AF4" s="126"/>
-      <c r="AG4" s="126"/>
-      <c r="AH4" s="126"/>
-      <c r="AI4" s="126"/>
-      <c r="AJ4" s="126"/>
-      <c r="AK4" s="127"/>
-      <c r="AL4" s="125"/>
-      <c r="AM4" s="126"/>
-      <c r="AN4" s="126"/>
-      <c r="AO4" s="126"/>
-      <c r="AP4" s="126"/>
-      <c r="AQ4" s="126"/>
-      <c r="AR4" s="126"/>
-      <c r="AS4" s="126"/>
-      <c r="AT4" s="127"/>
-      <c r="AU4" s="136"/>
-      <c r="AV4" s="126"/>
-      <c r="AW4" s="126"/>
-      <c r="AX4" s="126"/>
-      <c r="AY4" s="126"/>
-      <c r="AZ4" s="126"/>
-      <c r="BA4" s="126"/>
-      <c r="BB4" s="126"/>
-      <c r="BC4" s="126"/>
-      <c r="BD4" s="126"/>
-      <c r="BE4" s="126"/>
-      <c r="BF4" s="126"/>
-      <c r="BG4" s="126"/>
-      <c r="BH4" s="126"/>
-      <c r="BI4" s="126"/>
-      <c r="BJ4" s="126"/>
-      <c r="BK4" s="126"/>
-      <c r="BL4" s="126"/>
-      <c r="BM4" s="126"/>
-      <c r="BN4" s="126"/>
-      <c r="BO4" s="126"/>
-      <c r="BP4" s="126"/>
-      <c r="BQ4" s="126"/>
-      <c r="BR4" s="126"/>
-      <c r="BS4" s="126"/>
-      <c r="BT4" s="126"/>
-      <c r="BU4" s="126"/>
-      <c r="BV4" s="137"/>
-      <c r="BW4" s="126"/>
-      <c r="BX4" s="126"/>
-      <c r="BY4" s="126"/>
-      <c r="BZ4" s="126"/>
-      <c r="CA4" s="126"/>
-      <c r="CB4" s="126"/>
-      <c r="CC4" s="126"/>
-      <c r="CD4" s="126"/>
-      <c r="CE4" s="126"/>
-      <c r="CF4" s="126"/>
-      <c r="CG4" s="126"/>
-      <c r="CH4" s="126"/>
-      <c r="CI4" s="126"/>
-      <c r="CJ4" s="126"/>
-      <c r="CK4" s="126"/>
-      <c r="CL4" s="126"/>
-      <c r="CM4" s="126"/>
-      <c r="CN4" s="126"/>
-      <c r="CO4" s="126"/>
-      <c r="CP4" s="126"/>
-      <c r="CQ4" s="126"/>
-      <c r="CR4" s="127"/>
-      <c r="CS4" s="114"/>
-      <c r="CT4" s="115"/>
-      <c r="CU4" s="115"/>
-      <c r="CV4" s="115"/>
-      <c r="CW4" s="116"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="175"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="130"/>
+      <c r="X4" s="176"/>
+      <c r="Y4" s="129"/>
+      <c r="Z4" s="129"/>
+      <c r="AA4" s="129"/>
+      <c r="AB4" s="177"/>
+      <c r="AC4" s="129"/>
+      <c r="AD4" s="129"/>
+      <c r="AE4" s="129"/>
+      <c r="AF4" s="129"/>
+      <c r="AG4" s="129"/>
+      <c r="AH4" s="129"/>
+      <c r="AI4" s="129"/>
+      <c r="AJ4" s="129"/>
+      <c r="AK4" s="130"/>
+      <c r="AL4" s="128"/>
+      <c r="AM4" s="129"/>
+      <c r="AN4" s="129"/>
+      <c r="AO4" s="129"/>
+      <c r="AP4" s="129"/>
+      <c r="AQ4" s="129"/>
+      <c r="AR4" s="129"/>
+      <c r="AS4" s="129"/>
+      <c r="AT4" s="130"/>
+      <c r="AU4" s="139"/>
+      <c r="AV4" s="129"/>
+      <c r="AW4" s="129"/>
+      <c r="AX4" s="129"/>
+      <c r="AY4" s="129"/>
+      <c r="AZ4" s="129"/>
+      <c r="BA4" s="129"/>
+      <c r="BB4" s="129"/>
+      <c r="BC4" s="129"/>
+      <c r="BD4" s="129"/>
+      <c r="BE4" s="129"/>
+      <c r="BF4" s="129"/>
+      <c r="BG4" s="129"/>
+      <c r="BH4" s="129"/>
+      <c r="BI4" s="129"/>
+      <c r="BJ4" s="129"/>
+      <c r="BK4" s="129"/>
+      <c r="BL4" s="129"/>
+      <c r="BM4" s="129"/>
+      <c r="BN4" s="129"/>
+      <c r="BO4" s="129"/>
+      <c r="BP4" s="129"/>
+      <c r="BQ4" s="129"/>
+      <c r="BR4" s="129"/>
+      <c r="BS4" s="129"/>
+      <c r="BT4" s="129"/>
+      <c r="BU4" s="129"/>
+      <c r="BV4" s="140"/>
+      <c r="BW4" s="129"/>
+      <c r="BX4" s="129"/>
+      <c r="BY4" s="129"/>
+      <c r="BZ4" s="129"/>
+      <c r="CA4" s="129"/>
+      <c r="CB4" s="129"/>
+      <c r="CC4" s="129"/>
+      <c r="CD4" s="129"/>
+      <c r="CE4" s="129"/>
+      <c r="CF4" s="129"/>
+      <c r="CG4" s="129"/>
+      <c r="CH4" s="129"/>
+      <c r="CI4" s="129"/>
+      <c r="CJ4" s="129"/>
+      <c r="CK4" s="129"/>
+      <c r="CL4" s="129"/>
+      <c r="CM4" s="129"/>
+      <c r="CN4" s="129"/>
+      <c r="CO4" s="129"/>
+      <c r="CP4" s="129"/>
+      <c r="CQ4" s="129"/>
+      <c r="CR4" s="130"/>
+      <c r="CS4" s="117"/>
+      <c r="CT4" s="118"/>
+      <c r="CU4" s="118"/>
+      <c r="CV4" s="118"/>
+      <c r="CW4" s="119"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="131" t="s">
+      <c r="CY4" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="132"/>
-      <c r="DA4" s="133" t="s">
+      <c r="CZ4" s="135"/>
+      <c r="DA4" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="134"/>
-      <c r="DC4" s="134"/>
-      <c r="DD4" s="134"/>
-      <c r="DE4" s="134"/>
-      <c r="DF4" s="134"/>
-      <c r="DG4" s="132"/>
+      <c r="DB4" s="137"/>
+      <c r="DC4" s="137"/>
+      <c r="DD4" s="137"/>
+      <c r="DE4" s="137"/>
+      <c r="DF4" s="137"/>
+      <c r="DG4" s="135"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="131" t="s">
+      <c r="DJ4" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="132"/>
-      <c r="DL4" s="133" t="s">
+      <c r="DK4" s="135"/>
+      <c r="DL4" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="134"/>
-      <c r="DN4" s="134"/>
-      <c r="DO4" s="134"/>
-      <c r="DP4" s="134"/>
-      <c r="DQ4" s="134"/>
-      <c r="DR4" s="132"/>
+      <c r="DM4" s="137"/>
+      <c r="DN4" s="137"/>
+      <c r="DO4" s="137"/>
+      <c r="DP4" s="137"/>
+      <c r="DQ4" s="137"/>
+      <c r="DR4" s="135"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5674,112 +5695,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="159" t="s">
+      <c r="A5" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="110"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="175" t="str">
+      <c r="B5" s="113"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="178" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO JUAN LUIS LONDOÑO I.E.D. LA SALLE</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="119"/>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
-      <c r="AB5" s="117"/>
-      <c r="AC5" s="118"/>
-      <c r="AD5" s="118"/>
-      <c r="AE5" s="118"/>
-      <c r="AF5" s="118"/>
-      <c r="AG5" s="118"/>
-      <c r="AH5" s="118"/>
-      <c r="AI5" s="118"/>
-      <c r="AJ5" s="118"/>
-      <c r="AK5" s="119"/>
-      <c r="AL5" s="117"/>
-      <c r="AM5" s="118"/>
-      <c r="AN5" s="118"/>
-      <c r="AO5" s="118"/>
-      <c r="AP5" s="118"/>
-      <c r="AQ5" s="118"/>
-      <c r="AR5" s="118"/>
-      <c r="AS5" s="118"/>
-      <c r="AT5" s="119"/>
-      <c r="AU5" s="117"/>
-      <c r="AV5" s="118"/>
-      <c r="AW5" s="118"/>
-      <c r="AX5" s="118"/>
-      <c r="AY5" s="118"/>
-      <c r="AZ5" s="118"/>
-      <c r="BA5" s="118"/>
-      <c r="BB5" s="118"/>
-      <c r="BC5" s="118"/>
-      <c r="BD5" s="118"/>
-      <c r="BE5" s="118"/>
-      <c r="BF5" s="118"/>
-      <c r="BG5" s="118"/>
-      <c r="BH5" s="118"/>
-      <c r="BI5" s="118"/>
-      <c r="BJ5" s="118"/>
-      <c r="BK5" s="118"/>
-      <c r="BL5" s="118"/>
-      <c r="BM5" s="118"/>
-      <c r="BN5" s="118"/>
-      <c r="BO5" s="118"/>
-      <c r="BP5" s="118"/>
-      <c r="BQ5" s="118"/>
-      <c r="BR5" s="118"/>
-      <c r="BS5" s="118"/>
-      <c r="BT5" s="118"/>
-      <c r="BU5" s="118"/>
-      <c r="BV5" s="117"/>
-      <c r="BW5" s="118"/>
-      <c r="BX5" s="118"/>
-      <c r="BY5" s="118"/>
-      <c r="BZ5" s="118"/>
-      <c r="CA5" s="118"/>
-      <c r="CB5" s="118"/>
-      <c r="CC5" s="118"/>
-      <c r="CD5" s="118"/>
-      <c r="CE5" s="118"/>
-      <c r="CF5" s="118"/>
-      <c r="CG5" s="118"/>
-      <c r="CH5" s="118"/>
-      <c r="CI5" s="118"/>
-      <c r="CJ5" s="118"/>
-      <c r="CK5" s="118"/>
-      <c r="CL5" s="118"/>
-      <c r="CM5" s="118"/>
-      <c r="CN5" s="118"/>
-      <c r="CO5" s="118"/>
-      <c r="CP5" s="118"/>
-      <c r="CQ5" s="118"/>
-      <c r="CR5" s="119"/>
-      <c r="CS5" s="117"/>
-      <c r="CT5" s="118"/>
-      <c r="CU5" s="118"/>
-      <c r="CV5" s="118"/>
-      <c r="CW5" s="119"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="121"/>
+      <c r="S5" s="121"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="121"/>
+      <c r="W5" s="122"/>
+      <c r="X5" s="120"/>
+      <c r="Y5" s="121"/>
+      <c r="Z5" s="121"/>
+      <c r="AA5" s="121"/>
+      <c r="AB5" s="120"/>
+      <c r="AC5" s="121"/>
+      <c r="AD5" s="121"/>
+      <c r="AE5" s="121"/>
+      <c r="AF5" s="121"/>
+      <c r="AG5" s="121"/>
+      <c r="AH5" s="121"/>
+      <c r="AI5" s="121"/>
+      <c r="AJ5" s="121"/>
+      <c r="AK5" s="122"/>
+      <c r="AL5" s="120"/>
+      <c r="AM5" s="121"/>
+      <c r="AN5" s="121"/>
+      <c r="AO5" s="121"/>
+      <c r="AP5" s="121"/>
+      <c r="AQ5" s="121"/>
+      <c r="AR5" s="121"/>
+      <c r="AS5" s="121"/>
+      <c r="AT5" s="122"/>
+      <c r="AU5" s="120"/>
+      <c r="AV5" s="121"/>
+      <c r="AW5" s="121"/>
+      <c r="AX5" s="121"/>
+      <c r="AY5" s="121"/>
+      <c r="AZ5" s="121"/>
+      <c r="BA5" s="121"/>
+      <c r="BB5" s="121"/>
+      <c r="BC5" s="121"/>
+      <c r="BD5" s="121"/>
+      <c r="BE5" s="121"/>
+      <c r="BF5" s="121"/>
+      <c r="BG5" s="121"/>
+      <c r="BH5" s="121"/>
+      <c r="BI5" s="121"/>
+      <c r="BJ5" s="121"/>
+      <c r="BK5" s="121"/>
+      <c r="BL5" s="121"/>
+      <c r="BM5" s="121"/>
+      <c r="BN5" s="121"/>
+      <c r="BO5" s="121"/>
+      <c r="BP5" s="121"/>
+      <c r="BQ5" s="121"/>
+      <c r="BR5" s="121"/>
+      <c r="BS5" s="121"/>
+      <c r="BT5" s="121"/>
+      <c r="BU5" s="121"/>
+      <c r="BV5" s="120"/>
+      <c r="BW5" s="121"/>
+      <c r="BX5" s="121"/>
+      <c r="BY5" s="121"/>
+      <c r="BZ5" s="121"/>
+      <c r="CA5" s="121"/>
+      <c r="CB5" s="121"/>
+      <c r="CC5" s="121"/>
+      <c r="CD5" s="121"/>
+      <c r="CE5" s="121"/>
+      <c r="CF5" s="121"/>
+      <c r="CG5" s="121"/>
+      <c r="CH5" s="121"/>
+      <c r="CI5" s="121"/>
+      <c r="CJ5" s="121"/>
+      <c r="CK5" s="121"/>
+      <c r="CL5" s="121"/>
+      <c r="CM5" s="121"/>
+      <c r="CN5" s="121"/>
+      <c r="CO5" s="121"/>
+      <c r="CP5" s="121"/>
+      <c r="CQ5" s="121"/>
+      <c r="CR5" s="122"/>
+      <c r="CS5" s="120"/>
+      <c r="CT5" s="121"/>
+      <c r="CU5" s="121"/>
+      <c r="CV5" s="121"/>
+      <c r="CW5" s="122"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5808,11 +5829,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="159" t="s">
+      <c r="A6" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="110"/>
-      <c r="C6" s="160"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="163"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3415417</v>
@@ -5824,18 +5845,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="181" t="str">
+      <c r="G6" s="184" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 25</v>
       </c>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="126"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="126"/>
-      <c r="O6" s="177"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="129"/>
+      <c r="N6" s="129"/>
+      <c r="O6" s="180"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -6180,41 +6201,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="138" t="s">
+      <c r="CX6" s="141" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="139"/>
-      <c r="CZ6" s="139"/>
-      <c r="DA6" s="139"/>
-      <c r="DB6" s="139"/>
-      <c r="DC6" s="139"/>
-      <c r="DD6" s="139"/>
-      <c r="DE6" s="139"/>
-      <c r="DF6" s="139"/>
-      <c r="DG6" s="139"/>
-      <c r="DH6" s="139"/>
-      <c r="DI6" s="139"/>
-      <c r="DJ6" s="139"/>
-      <c r="DK6" s="139"/>
-      <c r="DL6" s="139"/>
-      <c r="DM6" s="139"/>
-      <c r="DN6" s="139"/>
-      <c r="DO6" s="139"/>
-      <c r="DP6" s="139"/>
-      <c r="DQ6" s="139"/>
-      <c r="DR6" s="139"/>
-      <c r="DS6" s="139"/>
-      <c r="DT6" s="139"/>
-      <c r="DU6" s="139"/>
-      <c r="DV6" s="139"/>
-      <c r="DW6" s="139"/>
+      <c r="CY6" s="142"/>
+      <c r="CZ6" s="142"/>
+      <c r="DA6" s="142"/>
+      <c r="DB6" s="142"/>
+      <c r="DC6" s="142"/>
+      <c r="DD6" s="142"/>
+      <c r="DE6" s="142"/>
+      <c r="DF6" s="142"/>
+      <c r="DG6" s="142"/>
+      <c r="DH6" s="142"/>
+      <c r="DI6" s="142"/>
+      <c r="DJ6" s="142"/>
+      <c r="DK6" s="142"/>
+      <c r="DL6" s="142"/>
+      <c r="DM6" s="142"/>
+      <c r="DN6" s="142"/>
+      <c r="DO6" s="142"/>
+      <c r="DP6" s="142"/>
+      <c r="DQ6" s="142"/>
+      <c r="DR6" s="142"/>
+      <c r="DS6" s="142"/>
+      <c r="DT6" s="142"/>
+      <c r="DU6" s="142"/>
+      <c r="DV6" s="142"/>
+      <c r="DW6" s="142"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="110"/>
-      <c r="C7" s="160"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="163"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46083</v>
@@ -6226,15 +6247,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46085</v>
       </c>
-      <c r="G7" s="178"/>
-      <c r="H7" s="158"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="158"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="179"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="182"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46083</v>
@@ -6579,58 +6600,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46379</v>
       </c>
-      <c r="CX7" s="140" t="s">
+      <c r="CX7" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="141"/>
-      <c r="CZ7" s="140" t="s">
+      <c r="CY7" s="144"/>
+      <c r="CZ7" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="139"/>
-      <c r="DB7" s="140" t="s">
+      <c r="DA7" s="142"/>
+      <c r="DB7" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="141"/>
-      <c r="DD7" s="140" t="s">
+      <c r="DC7" s="144"/>
+      <c r="DD7" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="141"/>
-      <c r="DF7" s="140" t="s">
+      <c r="DE7" s="144"/>
+      <c r="DF7" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="141"/>
-      <c r="DH7" s="140" t="s">
+      <c r="DG7" s="144"/>
+      <c r="DH7" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="141"/>
-      <c r="DJ7" s="140" t="s">
+      <c r="DI7" s="144"/>
+      <c r="DJ7" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="141"/>
-      <c r="DL7" s="140" t="s">
+      <c r="DK7" s="144"/>
+      <c r="DL7" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="141"/>
-      <c r="DN7" s="140" t="s">
+      <c r="DM7" s="144"/>
+      <c r="DN7" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="141"/>
-      <c r="DP7" s="140" t="s">
+      <c r="DO7" s="144"/>
+      <c r="DP7" s="143" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="141"/>
-      <c r="DR7" s="140" t="s">
+      <c r="DQ7" s="144"/>
+      <c r="DR7" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="141"/>
-      <c r="DT7" s="140" t="s">
+      <c r="DS7" s="144"/>
+      <c r="DT7" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="141"/>
-      <c r="DV7" s="142" t="s">
+      <c r="DU7" s="144"/>
+      <c r="DV7" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="139"/>
+      <c r="DW7" s="142"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -7129,7 +7150,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G44" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H44" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -7174,9 +7195,13 @@
       <c r="V9" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W9" s="35"/>
+      <c r="W9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
+      <c r="Y9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z9" s="35"/>
       <c r="AA9" s="35"/>
       <c r="AB9" s="35"/>
@@ -7315,7 +7340,7 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="4"/>
@@ -7360,9 +7385,13 @@
       <c r="V10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W10" s="35"/>
+      <c r="W10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
+      <c r="Y10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z10" s="35"/>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
@@ -7501,7 +7530,7 @@
       </c>
       <c r="G11" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" si="4"/>
@@ -7546,9 +7575,13 @@
       <c r="V11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W11" s="35"/>
+      <c r="W11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
+      <c r="Y11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z11" s="35"/>
       <c r="AA11" s="35"/>
       <c r="AB11" s="35"/>
@@ -7683,11 +7716,11 @@
       </c>
       <c r="F12" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G12" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="42">
         <f t="shared" si="4"/>
@@ -7695,7 +7728,7 @@
       </c>
       <c r="I12" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="6"/>
@@ -7719,7 +7752,7 @@
       </c>
       <c r="O12" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
@@ -7732,9 +7765,13 @@
       <c r="V12" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W12" s="35"/>
+      <c r="W12" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
+      <c r="Y12" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="Z12" s="35"/>
       <c r="AA12" s="35"/>
       <c r="AB12" s="35"/>
@@ -7873,7 +7910,7 @@
       </c>
       <c r="G13" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" si="4"/>
@@ -7918,9 +7955,13 @@
       <c r="V13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W13" s="35"/>
+      <c r="W13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
+      <c r="Y13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z13" s="35"/>
       <c r="AA13" s="35"/>
       <c r="AB13" s="35"/>
@@ -8059,7 +8100,7 @@
       </c>
       <c r="G14" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" s="42">
         <f t="shared" si="4"/>
@@ -8104,9 +8145,13 @@
       <c r="V14" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W14" s="35"/>
+      <c r="W14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
+      <c r="Y14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z14" s="35"/>
       <c r="AA14" s="35"/>
       <c r="AB14" s="35"/>
@@ -8245,7 +8290,7 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="42">
         <f t="shared" si="4"/>
@@ -8290,9 +8335,13 @@
       <c r="V15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W15" s="35"/>
+      <c r="W15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
+      <c r="Y15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
       <c r="AB15" s="35"/>
@@ -8431,7 +8480,7 @@
       </c>
       <c r="G16" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="42">
         <f t="shared" si="4"/>
@@ -8476,9 +8525,13 @@
       <c r="V16" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W16" s="35"/>
+      <c r="W16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
+      <c r="Y16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
       <c r="AB16" s="35"/>
@@ -8617,7 +8670,7 @@
       </c>
       <c r="G17" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="42">
         <f t="shared" si="4"/>
@@ -8662,9 +8715,13 @@
       <c r="V17" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W17" s="35"/>
+      <c r="W17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
+      <c r="Y17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z17" s="35"/>
       <c r="AA17" s="35"/>
       <c r="AB17" s="35"/>
@@ -8803,7 +8860,7 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="4"/>
@@ -8848,9 +8905,13 @@
       <c r="V18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W18" s="35"/>
+      <c r="W18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
+      <c r="Y18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z18" s="35"/>
       <c r="AA18" s="35"/>
       <c r="AB18" s="35"/>
@@ -8989,7 +9050,7 @@
       </c>
       <c r="G19" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="42">
         <f t="shared" si="4"/>
@@ -9034,9 +9095,13 @@
       <c r="V19" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W19" s="35"/>
+      <c r="W19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
+      <c r="Y19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z19" s="35"/>
       <c r="AA19" s="35"/>
       <c r="AB19" s="35"/>
@@ -9175,7 +9240,7 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="4"/>
@@ -9220,9 +9285,13 @@
       <c r="V20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W20" s="35"/>
+      <c r="W20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
+      <c r="Y20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z20" s="35"/>
       <c r="AA20" s="35"/>
       <c r="AB20" s="35"/>
@@ -9361,7 +9430,7 @@
       </c>
       <c r="G21" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="4"/>
@@ -9406,9 +9475,13 @@
       <c r="V21" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W21" s="35"/>
+      <c r="W21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
+      <c r="Y21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z21" s="35"/>
       <c r="AA21" s="35"/>
       <c r="AB21" s="35"/>
@@ -9545,7 +9618,7 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="4"/>
@@ -9590,9 +9663,13 @@
       <c r="V22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W22" s="35"/>
+      <c r="W22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
+      <c r="Y22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z22" s="35"/>
       <c r="AA22" s="35"/>
       <c r="AB22" s="35"/>
@@ -9729,7 +9806,7 @@
       </c>
       <c r="G23" s="41">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" s="42">
         <f t="shared" si="4"/>
@@ -9761,7 +9838,7 @@
       </c>
       <c r="O23" s="43">
         <f t="shared" si="11"/>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
@@ -9774,9 +9851,13 @@
       <c r="V23" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="W23" s="35"/>
+      <c r="W23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
+      <c r="Y23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z23" s="35"/>
       <c r="AA23" s="35"/>
       <c r="AB23" s="35"/>
@@ -9913,7 +9994,7 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="4"/>
@@ -9958,9 +10039,13 @@
       <c r="V24" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W24" s="35"/>
+      <c r="W24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
+      <c r="Y24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z24" s="35"/>
       <c r="AA24" s="35"/>
       <c r="AB24" s="35"/>
@@ -10097,7 +10182,7 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="42">
         <f t="shared" si="4"/>
@@ -10142,9 +10227,13 @@
       <c r="V25" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W25" s="35"/>
+      <c r="W25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
+      <c r="Y25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z25" s="35"/>
       <c r="AA25" s="35"/>
       <c r="AB25" s="35"/>
@@ -10281,7 +10370,7 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="4"/>
@@ -10326,9 +10415,13 @@
       <c r="V26" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W26" s="35"/>
+      <c r="W26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
+      <c r="Y26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z26" s="35"/>
       <c r="AA26" s="35"/>
       <c r="AB26" s="35"/>
@@ -10465,7 +10558,7 @@
       </c>
       <c r="G27" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="42">
         <f t="shared" si="4"/>
@@ -10510,9 +10603,13 @@
       <c r="V27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W27" s="35"/>
+      <c r="W27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
+      <c r="Y27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z27" s="35"/>
       <c r="AA27" s="35"/>
       <c r="AB27" s="35"/>
@@ -10649,7 +10746,7 @@
       </c>
       <c r="G28" s="41">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="4"/>
@@ -10657,7 +10754,7 @@
       </c>
       <c r="I28" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="42">
         <f t="shared" si="6"/>
@@ -10694,9 +10791,13 @@
       <c r="V28" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="W28" s="35"/>
+      <c r="W28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
+      <c r="Y28" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="Z28" s="35"/>
       <c r="AA28" s="35"/>
       <c r="AB28" s="35"/>
@@ -10833,7 +10934,7 @@
       </c>
       <c r="G29" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="42">
         <f t="shared" si="4"/>
@@ -10878,9 +10979,13 @@
       <c r="V29" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W29" s="35"/>
+      <c r="W29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
+      <c r="Y29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z29" s="35"/>
       <c r="AA29" s="35"/>
       <c r="AB29" s="35"/>
@@ -11017,7 +11122,7 @@
       </c>
       <c r="G30" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="42">
         <f t="shared" si="4"/>
@@ -11062,9 +11167,13 @@
       <c r="V30" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W30" s="35"/>
+      <c r="W30" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
+      <c r="Y30" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z30" s="35"/>
       <c r="AA30" s="35"/>
       <c r="AB30" s="35"/>
@@ -11201,7 +11310,7 @@
       </c>
       <c r="G31" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="42">
         <f t="shared" si="4"/>
@@ -11246,9 +11355,13 @@
       <c r="V31" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W31" s="35"/>
+      <c r="W31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
+      <c r="Y31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z31" s="35"/>
       <c r="AA31" s="35"/>
       <c r="AB31" s="35"/>
@@ -11384,7 +11497,7 @@
       </c>
       <c r="G32" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="4"/>
@@ -11429,9 +11542,13 @@
       <c r="V32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W32" s="35"/>
+      <c r="W32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
+      <c r="Y32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z32" s="35"/>
       <c r="AA32" s="35"/>
       <c r="AB32" s="35"/>
@@ -11567,7 +11684,7 @@
       </c>
       <c r="G33" s="41">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="42">
         <f t="shared" si="4"/>
@@ -11575,7 +11692,7 @@
       </c>
       <c r="I33" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="42">
         <f t="shared" si="6"/>
@@ -11612,9 +11729,13 @@
       <c r="V33" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="W33" s="35"/>
+      <c r="W33" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X33" s="35"/>
-      <c r="Y33" s="35"/>
+      <c r="Y33" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="Z33" s="35"/>
       <c r="AA33" s="35"/>
       <c r="AB33" s="35"/>
@@ -11750,7 +11871,7 @@
       </c>
       <c r="G34" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H34" s="42">
         <f t="shared" si="4"/>
@@ -11795,9 +11916,13 @@
       <c r="V34" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W34" s="35"/>
+      <c r="W34" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X34" s="35"/>
-      <c r="Y34" s="35"/>
+      <c r="Y34" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z34" s="35"/>
       <c r="AA34" s="35"/>
       <c r="AB34" s="35"/>
@@ -11925,7 +12050,7 @@
         <v>Lizeth Tatiana Martínez Ramírez</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F35" s="30" t="str">
         <f t="shared" si="2"/>
@@ -11933,7 +12058,7 @@
       </c>
       <c r="G35" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H35" s="42">
         <f t="shared" si="4"/>
@@ -11978,9 +12103,13 @@
       <c r="V35" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W35" s="35"/>
+      <c r="W35" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X35" s="35"/>
-      <c r="Y35" s="35"/>
+      <c r="Y35" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z35" s="35"/>
       <c r="AA35" s="35"/>
       <c r="AB35" s="35"/>
@@ -12116,7 +12245,7 @@
       </c>
       <c r="G36" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H36" s="42">
         <f t="shared" si="4"/>
@@ -12161,9 +12290,13 @@
       <c r="V36" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W36" s="35"/>
+      <c r="W36" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
+      <c r="Y36" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z36" s="35"/>
       <c r="AA36" s="35"/>
       <c r="AB36" s="35"/>
@@ -12299,7 +12432,7 @@
       </c>
       <c r="G37" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H37" s="42">
         <f t="shared" si="4"/>
@@ -12344,9 +12477,13 @@
       <c r="V37" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W37" s="35"/>
+      <c r="W37" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X37" s="35"/>
-      <c r="Y37" s="35"/>
+      <c r="Y37" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z37" s="35"/>
       <c r="AA37" s="35"/>
       <c r="AB37" s="35"/>
@@ -12482,7 +12619,7 @@
       </c>
       <c r="G38" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="42">
         <f t="shared" si="4"/>
@@ -12527,9 +12664,13 @@
       <c r="V38" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W38" s="35"/>
+      <c r="W38" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X38" s="35"/>
-      <c r="Y38" s="35"/>
+      <c r="Y38" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z38" s="35"/>
       <c r="AA38" s="35"/>
       <c r="AB38" s="35"/>
@@ -12665,7 +12806,7 @@
       </c>
       <c r="G39" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" s="42">
         <f t="shared" si="4"/>
@@ -12710,9 +12851,13 @@
       <c r="V39" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W39" s="35"/>
+      <c r="W39" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X39" s="35"/>
-      <c r="Y39" s="35"/>
+      <c r="Y39" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z39" s="35"/>
       <c r="AA39" s="35"/>
       <c r="AB39" s="35"/>
@@ -12848,7 +12993,7 @@
       </c>
       <c r="G40" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" s="42">
         <f t="shared" si="4"/>
@@ -12893,9 +13038,13 @@
       <c r="V40" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W40" s="35"/>
+      <c r="W40" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X40" s="35"/>
-      <c r="Y40" s="35"/>
+      <c r="Y40" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z40" s="35"/>
       <c r="AA40" s="35"/>
       <c r="AB40" s="35"/>
@@ -13031,7 +13180,7 @@
       </c>
       <c r="G41" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="42">
         <f t="shared" si="4"/>
@@ -13076,9 +13225,13 @@
       <c r="V41" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W41" s="35"/>
+      <c r="W41" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X41" s="35"/>
-      <c r="Y41" s="35"/>
+      <c r="Y41" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z41" s="35"/>
       <c r="AA41" s="35"/>
       <c r="AB41" s="35"/>
@@ -13214,7 +13367,7 @@
       </c>
       <c r="G42" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" s="42">
         <f t="shared" si="4"/>
@@ -13259,9 +13412,13 @@
       <c r="V42" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W42" s="35"/>
+      <c r="W42" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X42" s="35"/>
-      <c r="Y42" s="35"/>
+      <c r="Y42" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z42" s="35"/>
       <c r="AA42" s="35"/>
       <c r="AB42" s="35"/>
@@ -13397,7 +13554,7 @@
       </c>
       <c r="G43" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="42">
         <f t="shared" si="4"/>
@@ -13442,9 +13599,13 @@
       <c r="V43" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W43" s="35"/>
+      <c r="W43" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X43" s="35"/>
-      <c r="Y43" s="35"/>
+      <c r="Y43" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z43" s="35"/>
       <c r="AA43" s="35"/>
       <c r="AB43" s="35"/>
@@ -13580,7 +13741,7 @@
       </c>
       <c r="G44" s="89">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" s="90">
         <f t="shared" si="4"/>
@@ -13625,9 +13786,13 @@
       <c r="V44" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W44" s="35"/>
+      <c r="W44" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X44" s="35"/>
-      <c r="Y44" s="35"/>
+      <c r="Y44" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z44" s="35"/>
       <c r="AA44" s="35"/>
       <c r="AB44" s="35"/>
@@ -13760,7 +13925,7 @@
       <c r="F45" s="87"/>
       <c r="G45" s="89">
         <f t="shared" ref="G45:G49" si="49">COUNTIF(P45:CR45,"A")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" s="90">
         <f t="shared" ref="H45:H49" si="50">COUNTIF(P45:CR45,"CE")</f>
@@ -13805,9 +13970,13 @@
       <c r="V45" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W45" s="35"/>
+      <c r="W45" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X45" s="35"/>
-      <c r="Y45" s="35"/>
+      <c r="Y45" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z45" s="35"/>
       <c r="AA45" s="35"/>
       <c r="AB45" s="35"/>
@@ -13934,7 +14103,7 @@
       <c r="F46" s="87"/>
       <c r="G46" s="89">
         <f t="shared" si="49"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" s="90">
         <f t="shared" si="50"/>
@@ -13979,9 +14148,13 @@
       <c r="V46" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W46" s="35"/>
+      <c r="W46" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X46" s="35"/>
-      <c r="Y46" s="35"/>
+      <c r="Y46" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z46" s="35"/>
       <c r="AA46" s="35"/>
       <c r="AB46" s="35"/>
@@ -14108,7 +14281,7 @@
       <c r="F47" s="87"/>
       <c r="G47" s="89">
         <f t="shared" si="49"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="90">
         <f t="shared" si="50"/>
@@ -14153,9 +14326,13 @@
       <c r="V47" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W47" s="35"/>
+      <c r="W47" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X47" s="35"/>
-      <c r="Y47" s="35"/>
+      <c r="Y47" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z47" s="35"/>
       <c r="AA47" s="35"/>
       <c r="AB47" s="35"/>
@@ -14282,7 +14459,7 @@
       <c r="F48" s="87"/>
       <c r="G48" s="89">
         <f t="shared" si="49"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" s="90">
         <f t="shared" si="50"/>
@@ -14314,7 +14491,7 @@
       </c>
       <c r="O48" s="95">
         <f t="shared" si="57"/>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="P48" s="96"/>
       <c r="Q48" s="88"/>
@@ -14327,9 +14504,13 @@
       <c r="V48" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="W48" s="35"/>
+      <c r="W48" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X48" s="35"/>
-      <c r="Y48" s="35"/>
+      <c r="Y48" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z48" s="35"/>
       <c r="AA48" s="35"/>
       <c r="AB48" s="35"/>
@@ -14456,7 +14637,7 @@
       <c r="F49" s="87"/>
       <c r="G49" s="89">
         <f t="shared" si="49"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" s="90">
         <f t="shared" si="50"/>
@@ -14501,9 +14682,13 @@
       <c r="V49" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="W49" s="35"/>
+      <c r="W49" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="X49" s="35"/>
-      <c r="Y49" s="35"/>
+      <c r="Y49" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z49" s="35"/>
       <c r="AA49" s="35"/>
       <c r="AB49" s="35"/>
@@ -14614,20 +14799,20 @@
       <c r="D50" s="76"/>
       <c r="E50" s="76"/>
       <c r="F50" s="75"/>
-      <c r="G50" s="183" t="s">
-        <v>60</v>
-      </c>
-      <c r="H50" s="184"/>
-      <c r="I50" s="184"/>
-      <c r="J50" s="184"/>
-      <c r="K50" s="184"/>
-      <c r="L50" s="184"/>
-      <c r="M50" s="185"/>
-      <c r="N50" s="186" t="str">
+      <c r="G50" s="186" t="s">
+        <v>59</v>
+      </c>
+      <c r="H50" s="187"/>
+      <c r="I50" s="187"/>
+      <c r="J50" s="187"/>
+      <c r="K50" s="187"/>
+      <c r="L50" s="187"/>
+      <c r="M50" s="188"/>
+      <c r="N50" s="189" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O50" s="187"/>
+      <c r="O50" s="190"/>
       <c r="P50" s="94">
         <f t="shared" ref="P50:AU50" si="58">COUNTIF(P9:P44,"A")</f>
         <v>0</v>
@@ -14658,7 +14843,7 @@
       </c>
       <c r="W50" s="44">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X50" s="44">
         <f t="shared" si="58"/>
@@ -14666,7 +14851,7 @@
       </c>
       <c r="Y50" s="44">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Z50" s="44">
         <f t="shared" si="58"/>
@@ -15012,20 +15197,20 @@
       <c r="D51" s="76"/>
       <c r="E51" s="76"/>
       <c r="F51" s="75"/>
-      <c r="G51" s="153" t="s">
+      <c r="G51" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="144"/>
-      <c r="I51" s="144"/>
-      <c r="J51" s="144"/>
-      <c r="K51" s="144"/>
-      <c r="L51" s="144"/>
-      <c r="M51" s="145"/>
-      <c r="N51" s="146" t="str">
+      <c r="H51" s="147"/>
+      <c r="I51" s="147"/>
+      <c r="J51" s="147"/>
+      <c r="K51" s="147"/>
+      <c r="L51" s="147"/>
+      <c r="M51" s="148"/>
+      <c r="N51" s="149" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O51" s="147"/>
+      <c r="O51" s="150"/>
       <c r="P51" s="44">
         <f t="shared" ref="P51:AU51" si="62">COUNTIF(P9:P44,"CE")</f>
         <v>0</v>
@@ -15410,20 +15595,20 @@
       <c r="D52" s="76"/>
       <c r="E52" s="76"/>
       <c r="F52" s="75"/>
-      <c r="G52" s="154" t="s">
+      <c r="G52" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="144"/>
-      <c r="I52" s="144"/>
-      <c r="J52" s="144"/>
-      <c r="K52" s="144"/>
-      <c r="L52" s="144"/>
-      <c r="M52" s="145"/>
-      <c r="N52" s="146" t="str">
+      <c r="H52" s="147"/>
+      <c r="I52" s="147"/>
+      <c r="J52" s="147"/>
+      <c r="K52" s="147"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="148"/>
+      <c r="N52" s="149" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O52" s="147"/>
+      <c r="O52" s="150"/>
       <c r="P52" s="44">
         <f t="shared" ref="P52:AU52" si="66">COUNTIF(P9:P44,"SE")</f>
         <v>0</v>
@@ -15462,7 +15647,7 @@
       </c>
       <c r="Y52" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z52" s="44">
         <f t="shared" si="66"/>
@@ -15808,20 +15993,20 @@
       <c r="D53" s="76"/>
       <c r="E53" s="76"/>
       <c r="F53" s="45"/>
-      <c r="G53" s="155" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" s="144"/>
-      <c r="I53" s="144"/>
-      <c r="J53" s="144"/>
-      <c r="K53" s="144"/>
-      <c r="L53" s="144"/>
-      <c r="M53" s="145"/>
-      <c r="N53" s="146" t="str">
+      <c r="G53" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="H53" s="147"/>
+      <c r="I53" s="147"/>
+      <c r="J53" s="147"/>
+      <c r="K53" s="147"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="148"/>
+      <c r="N53" s="149" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O53" s="147"/>
+      <c r="O53" s="150"/>
       <c r="P53" s="44">
         <f t="shared" ref="P53:AU53" si="70">COUNTIF(P9:P44,"INC")</f>
         <v>0</v>
@@ -16206,20 +16391,20 @@
       <c r="D54" s="76"/>
       <c r="E54" s="76"/>
       <c r="F54" s="75"/>
-      <c r="G54" s="150" t="s">
-        <v>62</v>
-      </c>
-      <c r="H54" s="144"/>
-      <c r="I54" s="144"/>
-      <c r="J54" s="144"/>
-      <c r="K54" s="144"/>
-      <c r="L54" s="144"/>
-      <c r="M54" s="145"/>
-      <c r="N54" s="146" t="str">
+      <c r="G54" s="153" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54" s="147"/>
+      <c r="I54" s="147"/>
+      <c r="J54" s="147"/>
+      <c r="K54" s="147"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="148"/>
+      <c r="N54" s="149" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O54" s="147"/>
+      <c r="O54" s="150"/>
       <c r="P54" s="44">
         <f t="shared" ref="P54:AU54" si="74">COUNTIF(P9:P44,"LIC")</f>
         <v>0</v>
@@ -16604,20 +16789,20 @@
       <c r="D55" s="76"/>
       <c r="E55" s="76"/>
       <c r="F55" s="75"/>
-      <c r="G55" s="143" t="s">
-        <v>63</v>
-      </c>
-      <c r="H55" s="144"/>
-      <c r="I55" s="144"/>
-      <c r="J55" s="144"/>
-      <c r="K55" s="144"/>
-      <c r="L55" s="144"/>
-      <c r="M55" s="145"/>
-      <c r="N55" s="146" t="str">
+      <c r="G55" s="146" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="147"/>
+      <c r="I55" s="147"/>
+      <c r="J55" s="147"/>
+      <c r="K55" s="147"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="148"/>
+      <c r="N55" s="149" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O55" s="147"/>
+      <c r="O55" s="150"/>
       <c r="P55" s="44">
         <f t="shared" ref="P55:AU55" si="78">COUNTIF(P9:P44,"CLM")</f>
         <v>0</v>
@@ -17002,20 +17187,20 @@
       <c r="D56" s="76"/>
       <c r="E56" s="76"/>
       <c r="F56" s="75"/>
-      <c r="G56" s="148" t="s">
-        <v>64</v>
-      </c>
-      <c r="H56" s="144"/>
-      <c r="I56" s="144"/>
-      <c r="J56" s="144"/>
-      <c r="K56" s="144"/>
-      <c r="L56" s="144"/>
-      <c r="M56" s="145"/>
-      <c r="N56" s="146" t="str">
+      <c r="G56" s="151" t="s">
+        <v>63</v>
+      </c>
+      <c r="H56" s="147"/>
+      <c r="I56" s="147"/>
+      <c r="J56" s="147"/>
+      <c r="K56" s="147"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="148"/>
+      <c r="N56" s="149" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O56" s="147"/>
+      <c r="O56" s="150"/>
       <c r="P56" s="44">
         <f t="shared" ref="P56:AU56" si="82">COUNTIF(P9:P44,"SFF")</f>
         <v>0</v>
@@ -17400,20 +17585,20 @@
       <c r="D57" s="76"/>
       <c r="E57" s="76"/>
       <c r="F57" s="75"/>
-      <c r="G57" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="H57" s="144"/>
-      <c r="I57" s="144"/>
-      <c r="J57" s="144"/>
-      <c r="K57" s="144"/>
-      <c r="L57" s="144"/>
-      <c r="M57" s="145"/>
-      <c r="N57" s="146" t="str">
+      <c r="G57" s="152" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" s="147"/>
+      <c r="I57" s="147"/>
+      <c r="J57" s="147"/>
+      <c r="K57" s="147"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="148"/>
+      <c r="N57" s="149" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O57" s="147"/>
+      <c r="O57" s="150"/>
       <c r="P57" s="44">
         <f t="shared" ref="P57:AU57" si="86">COUNTIF(P9:P44,"RET")</f>
         <v>0</v>
@@ -43234,18 +43419,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="194">
-        <v>0</v>
-      </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="116"/>
+      <c r="A1" s="197">
+        <v>0</v>
+      </c>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="119"/>
       <c r="L1" s="49"/>
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
@@ -43263,16 +43448,16 @@
       <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="130"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="116"/>
+      <c r="A2" s="133"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="119"/>
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
@@ -43290,15 +43475,15 @@
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="1:26" ht="15.75">
-      <c r="A3" s="188" t="s">
+      <c r="A3" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="195" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="198" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="110"/>
-      <c r="E3" s="160"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="163"/>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="51"/>
@@ -43322,23 +43507,23 @@
       <c r="Z3" s="49"/>
     </row>
     <row r="4" spans="1:26" ht="15.75">
-      <c r="A4" s="188" t="s">
+      <c r="A4" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="160"/>
-      <c r="C4" s="196">
+      <c r="B4" s="163"/>
+      <c r="C4" s="199">
         <v>3415417</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="160"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="163"/>
       <c r="F4" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" s="53">
         <v>2</v>
       </c>
       <c r="H4" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="51"/>
       <c r="J4" s="49"/>
@@ -43360,17 +43545,17 @@
       <c r="Z4" s="49"/>
     </row>
     <row r="5" spans="1:26" ht="15.75">
-      <c r="A5" s="188" t="s">
+      <c r="A5" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="160"/>
-      <c r="C5" s="193" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="110"/>
-      <c r="E5" s="160"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="196" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="113"/>
+      <c r="E5" s="163"/>
       <c r="F5" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="54">
         <v>46083</v>
@@ -43396,17 +43581,17 @@
       <c r="Z5" s="49"/>
     </row>
     <row r="6" spans="1:26" ht="15.75">
-      <c r="A6" s="188" t="s">
+      <c r="A6" s="191" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="163"/>
+      <c r="C6" s="192" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="113"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="52" t="s">
         <v>69</v>
-      </c>
-      <c r="B6" s="160"/>
-      <c r="C6" s="189" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="110"/>
-      <c r="E6" s="160"/>
-      <c r="F6" s="52" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="55">
         <v>46085</v>
@@ -43432,17 +43617,17 @@
       <c r="Z6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="15.75">
-      <c r="A7" s="188" t="s">
+      <c r="A7" s="191" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="160"/>
-      <c r="C7" s="190" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="110"/>
-      <c r="E7" s="160"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="193" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="113"/>
+      <c r="E7" s="163"/>
       <c r="F7" s="56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="57">
         <v>10</v>
@@ -43468,17 +43653,17 @@
       <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="191" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="160"/>
-      <c r="C8" s="192" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="160"/>
+      <c r="A8" s="194" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="163"/>
+      <c r="C8" s="195" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="163"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
       <c r="J8" s="49"/>
@@ -43504,34 +43689,34 @@
         <v>32</v>
       </c>
       <c r="B9" s="59" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="J9" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="59" t="s">
         <v>306</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>309</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="59" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="59" t="s">
-        <v>307</v>
-      </c>
-      <c r="J9" s="59" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" s="59" t="s">
-        <v>308</v>
       </c>
       <c r="L9" s="49"/>
       <c r="M9" s="49"/>
@@ -43554,32 +43739,32 @@
         <v>1</v>
       </c>
       <c r="B10" s="97" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D10" s="98">
         <v>1011210598</v>
       </c>
       <c r="E10" s="79"/>
-      <c r="F10" s="201" t="s">
-        <v>138</v>
+      <c r="F10" s="104" t="s">
+        <v>136</v>
       </c>
       <c r="G10" s="99">
         <v>3222767816</v>
       </c>
       <c r="H10" s="97" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I10" s="97" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J10" s="99">
         <v>3142904958</v>
       </c>
       <c r="K10" s="98" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L10" s="49"/>
       <c r="M10" s="49"/>
@@ -43603,32 +43788,32 @@
         <v>2</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D11" s="98">
         <v>1021683093</v>
       </c>
       <c r="E11" s="79"/>
-      <c r="F11" s="201" t="s">
-        <v>139</v>
+      <c r="F11" s="104" t="s">
+        <v>137</v>
       </c>
       <c r="G11" s="99" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H11" s="97" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I11" s="97" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J11" s="99" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K11" s="98" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L11" s="49"/>
       <c r="M11" s="49"/>
@@ -43652,32 +43837,32 @@
         <v>3</v>
       </c>
       <c r="B12" s="97" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D12" s="98">
         <v>1028867289</v>
       </c>
       <c r="E12" s="79"/>
-      <c r="F12" s="201" t="s">
-        <v>140</v>
+      <c r="F12" s="104" t="s">
+        <v>138</v>
       </c>
       <c r="G12" s="99">
         <v>3203910222</v>
       </c>
       <c r="H12" s="97" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I12" s="97" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J12" s="99">
         <v>3212365995</v>
       </c>
       <c r="K12" s="98" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="L12" s="49"/>
       <c r="M12" s="49"/>
@@ -43701,32 +43886,32 @@
         <v>4</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D13" s="98">
         <v>1016718433</v>
       </c>
       <c r="E13" s="82"/>
-      <c r="F13" s="201" t="s">
-        <v>141</v>
+      <c r="F13" s="104" t="s">
+        <v>139</v>
       </c>
       <c r="G13" s="99">
         <v>3106733741</v>
       </c>
       <c r="H13" s="97" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I13" s="97" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J13" s="99">
         <v>3176890350</v>
       </c>
       <c r="K13" s="98" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L13" s="49"/>
       <c r="M13" s="49"/>
@@ -43750,36 +43935,36 @@
         <v>5</v>
       </c>
       <c r="B14" s="97" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D14" s="98">
         <v>1013128025</v>
       </c>
       <c r="E14" s="79"/>
-      <c r="F14" s="201" t="s">
-        <v>142</v>
+      <c r="F14" s="104" t="s">
+        <v>140</v>
       </c>
       <c r="G14" s="99">
         <v>3132017680</v>
       </c>
       <c r="H14" s="97" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I14" s="97" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J14" s="99">
         <v>3125014620</v>
       </c>
       <c r="K14" s="98" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L14" s="49"/>
       <c r="M14" s="49" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N14" s="49"/>
       <c r="O14" s="49"/>
@@ -43801,36 +43986,36 @@
         <v>6</v>
       </c>
       <c r="B15" s="97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C15" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D15" s="98">
         <v>1028800301</v>
       </c>
       <c r="E15" s="79"/>
-      <c r="F15" s="201" t="s">
-        <v>143</v>
+      <c r="F15" s="104" t="s">
+        <v>141</v>
       </c>
       <c r="G15" s="99">
         <v>3025240303</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I15" s="97" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J15" s="99">
         <v>3504932778</v>
       </c>
       <c r="K15" s="103" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L15" s="49"/>
       <c r="M15" s="49" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N15" s="49"/>
       <c r="O15" s="49"/>
@@ -43852,32 +44037,32 @@
         <v>7</v>
       </c>
       <c r="B16" s="97" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16" s="98">
         <v>1028620587</v>
       </c>
       <c r="E16" s="79"/>
-      <c r="F16" s="201" t="s">
-        <v>144</v>
+      <c r="F16" s="104" t="s">
+        <v>142</v>
       </c>
       <c r="G16" s="99">
         <v>3053207465</v>
       </c>
       <c r="H16" s="97" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I16" s="97" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J16" s="99">
         <v>3103392133</v>
       </c>
       <c r="K16" s="103" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L16" s="49"/>
       <c r="M16" s="49"/>
@@ -43901,32 +44086,32 @@
         <v>8</v>
       </c>
       <c r="B17" s="97" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C17" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D17" s="98">
         <v>1011205992</v>
       </c>
       <c r="E17" s="79"/>
-      <c r="F17" s="201" t="s">
-        <v>145</v>
+      <c r="F17" s="104" t="s">
+        <v>143</v>
       </c>
       <c r="G17" s="99">
         <v>3228937839</v>
       </c>
       <c r="H17" s="97" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I17" s="97" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J17" s="99">
         <v>3212444943</v>
       </c>
       <c r="K17" s="98" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L17" s="49"/>
       <c r="M17" s="49"/>
@@ -43950,32 +44135,32 @@
         <v>9</v>
       </c>
       <c r="B18" s="97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C18" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D18" s="98">
         <v>1140923876</v>
       </c>
       <c r="E18" s="79"/>
-      <c r="F18" s="201" t="s">
-        <v>146</v>
+      <c r="F18" s="104" t="s">
+        <v>144</v>
       </c>
       <c r="G18" s="99" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H18" s="97" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I18" s="97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J18" s="99">
         <v>3138278299</v>
       </c>
       <c r="K18" s="98" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L18" s="49"/>
       <c r="M18" s="49"/>
@@ -43999,32 +44184,32 @@
         <v>10</v>
       </c>
       <c r="B19" s="97" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C19" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D19" s="98">
         <v>1047345388</v>
       </c>
       <c r="E19" s="79"/>
-      <c r="F19" s="201" t="s">
-        <v>147</v>
+      <c r="F19" s="104" t="s">
+        <v>145</v>
       </c>
       <c r="G19" s="99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I19" s="97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J19" s="99">
         <v>3236991408</v>
       </c>
       <c r="K19" s="98" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
@@ -44048,32 +44233,32 @@
         <v>11</v>
       </c>
       <c r="B20" s="97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C20" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D20" s="98">
         <v>1013132921</v>
       </c>
       <c r="E20" s="80"/>
-      <c r="F20" s="201" t="s">
-        <v>332</v>
+      <c r="F20" s="104" t="s">
+        <v>330</v>
       </c>
       <c r="G20" s="99">
         <v>3228955345</v>
       </c>
       <c r="H20" s="97" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I20" s="97" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J20" s="99">
         <v>3204764313</v>
       </c>
       <c r="K20" s="98" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L20" s="49"/>
       <c r="M20" s="49"/>
@@ -44097,32 +44282,32 @@
         <v>12</v>
       </c>
       <c r="B21" s="97" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C21" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D21" s="98">
         <v>1025148041</v>
       </c>
       <c r="E21" s="80"/>
-      <c r="F21" s="201" t="s">
-        <v>148</v>
+      <c r="F21" s="104" t="s">
+        <v>146</v>
       </c>
       <c r="G21" s="99">
         <v>3112069421</v>
       </c>
       <c r="H21" s="97" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I21" s="97" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J21" s="99">
         <v>3185432699</v>
       </c>
       <c r="K21" s="98" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L21" s="49"/>
       <c r="M21" s="49"/>
@@ -44146,32 +44331,32 @@
         <v>13</v>
       </c>
       <c r="B22" s="97" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C22" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D22" s="98">
         <v>1028869164</v>
       </c>
       <c r="E22" s="80"/>
-      <c r="F22" s="201" t="s">
-        <v>149</v>
+      <c r="F22" s="104" t="s">
+        <v>147</v>
       </c>
       <c r="G22" s="99">
         <v>3213262115</v>
       </c>
       <c r="H22" s="97" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I22" s="97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J22" s="99">
         <v>3202000148</v>
       </c>
       <c r="K22" s="98" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L22" s="49"/>
       <c r="M22" s="49"/>
@@ -44195,32 +44380,32 @@
         <v>14</v>
       </c>
       <c r="B23" s="97" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C23" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D23" s="98">
         <v>1025546752</v>
       </c>
       <c r="E23" s="79"/>
-      <c r="F23" s="201" t="s">
-        <v>150</v>
+      <c r="F23" s="104" t="s">
+        <v>148</v>
       </c>
       <c r="G23" s="99">
         <v>3213987383</v>
       </c>
       <c r="H23" s="97" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I23" s="97" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J23" s="99">
         <v>3214064142</v>
       </c>
       <c r="K23" s="98" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L23" s="49"/>
       <c r="M23" s="49"/>
@@ -44244,32 +44429,32 @@
         <v>15</v>
       </c>
       <c r="B24" s="97" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D24" s="98">
         <v>1033748632</v>
       </c>
       <c r="E24" s="82"/>
-      <c r="F24" s="201" t="s">
-        <v>151</v>
+      <c r="F24" s="104" t="s">
+        <v>149</v>
       </c>
       <c r="G24" s="99">
         <v>3108834649</v>
       </c>
       <c r="H24" s="97" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I24" s="97" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J24" s="99">
         <v>3112673683</v>
       </c>
       <c r="K24" s="98" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L24" s="49"/>
       <c r="M24" s="49"/>
@@ -44293,32 +44478,32 @@
         <v>16</v>
       </c>
       <c r="B25" s="97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C25" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D25" s="98">
         <v>1120738374</v>
       </c>
       <c r="E25" s="79"/>
-      <c r="F25" s="201" t="s">
-        <v>152</v>
+      <c r="F25" s="104" t="s">
+        <v>150</v>
       </c>
       <c r="G25" s="99">
         <v>3105331732</v>
       </c>
       <c r="H25" s="97" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I25" s="97" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J25" s="99">
         <v>3015851134</v>
       </c>
-      <c r="K25" s="201" t="s">
-        <v>395</v>
+      <c r="K25" s="104" t="s">
+        <v>390</v>
       </c>
       <c r="L25" s="60"/>
       <c r="M25" s="60"/>
@@ -44342,32 +44527,32 @@
         <v>17</v>
       </c>
       <c r="B26" s="97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C26" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D26" s="98">
         <v>1027530989</v>
       </c>
       <c r="E26" s="79"/>
-      <c r="F26" s="201" t="s">
-        <v>153</v>
+      <c r="F26" s="104" t="s">
+        <v>151</v>
       </c>
       <c r="G26" s="99" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H26" s="97" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I26" s="97" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J26" s="99">
         <v>3213079806</v>
       </c>
       <c r="K26" s="98" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L26" s="49"/>
       <c r="M26" s="49"/>
@@ -44391,32 +44576,32 @@
         <v>18</v>
       </c>
       <c r="B27" s="97" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C27" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D27" s="98">
         <v>1027530471</v>
       </c>
       <c r="E27" s="80"/>
-      <c r="F27" s="201" t="s">
-        <v>154</v>
+      <c r="F27" s="104" t="s">
+        <v>152</v>
       </c>
       <c r="G27" s="99">
         <v>3114743873</v>
       </c>
       <c r="H27" s="97" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I27" s="97" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J27" s="99">
         <v>3208433510</v>
       </c>
       <c r="K27" s="98" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L27" s="49"/>
       <c r="M27" s="49"/>
@@ -44440,32 +44625,32 @@
         <v>19</v>
       </c>
       <c r="B28" s="97" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C28" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D28" s="98">
         <v>1022968721</v>
       </c>
       <c r="E28" s="80"/>
-      <c r="F28" s="201" t="s">
-        <v>155</v>
+      <c r="F28" s="104" t="s">
+        <v>153</v>
       </c>
       <c r="G28" s="99">
         <v>3112233931</v>
       </c>
       <c r="H28" s="97" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I28" s="97" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J28" s="99">
         <v>3114878243</v>
       </c>
       <c r="K28" s="98" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L28" s="49"/>
       <c r="M28" s="49"/>
@@ -44489,32 +44674,32 @@
         <v>20</v>
       </c>
       <c r="B29" s="97" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D29" s="98">
         <v>1027530856</v>
       </c>
       <c r="E29" s="79"/>
-      <c r="F29" s="201" t="s">
-        <v>156</v>
+      <c r="F29" s="104" t="s">
+        <v>154</v>
       </c>
       <c r="G29" s="99">
         <v>3053389920</v>
       </c>
       <c r="H29" s="97" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I29" s="97" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J29" s="99">
         <v>3177700430</v>
       </c>
       <c r="K29" s="98" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L29" s="49"/>
       <c r="M29" s="49"/>
@@ -44538,32 +44723,32 @@
         <v>21</v>
       </c>
       <c r="B30" s="97" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C30" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D30" s="98">
         <v>1019766188</v>
       </c>
       <c r="E30" s="81"/>
-      <c r="F30" s="201" t="s">
-        <v>157</v>
+      <c r="F30" s="104" t="s">
+        <v>155</v>
       </c>
       <c r="G30" s="99">
         <v>3008784404</v>
       </c>
       <c r="H30" s="97" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I30" s="97" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J30" s="99">
         <v>3046381817</v>
       </c>
       <c r="K30" s="98" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L30" s="49"/>
       <c r="M30" s="49"/>
@@ -44587,32 +44772,32 @@
         <v>22</v>
       </c>
       <c r="B31" s="97" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C31" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D31" s="98">
         <v>1013637824</v>
       </c>
       <c r="E31" s="81"/>
-      <c r="F31" s="201" t="s">
-        <v>158</v>
+      <c r="F31" s="104" t="s">
+        <v>156</v>
       </c>
       <c r="G31" s="99">
         <v>3132274010</v>
       </c>
       <c r="H31" s="97" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I31" s="97" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J31" s="99">
         <v>3006024133</v>
       </c>
       <c r="K31" s="98" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L31" s="60"/>
       <c r="M31" s="60"/>
@@ -44636,32 +44821,32 @@
         <v>23</v>
       </c>
       <c r="B32" s="97" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D32" s="98">
         <v>1018451032</v>
       </c>
       <c r="E32" s="81"/>
-      <c r="F32" s="201" t="s">
-        <v>159</v>
+      <c r="F32" s="104" t="s">
+        <v>157</v>
       </c>
       <c r="G32" s="99">
         <v>3125566819</v>
       </c>
       <c r="H32" s="97" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I32" s="97" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J32" s="99">
         <v>3135109952</v>
       </c>
       <c r="K32" s="98" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L32" s="60"/>
       <c r="M32" s="60"/>
@@ -44685,32 +44870,32 @@
         <v>24</v>
       </c>
       <c r="B33" s="97" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C33" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D33" s="98">
         <v>1140921303</v>
       </c>
       <c r="E33" s="79"/>
-      <c r="F33" s="201" t="s">
-        <v>160</v>
+      <c r="F33" s="104" t="s">
+        <v>158</v>
       </c>
       <c r="G33" s="99">
         <v>3157117898</v>
       </c>
       <c r="H33" s="97" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I33" s="97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J33" s="99">
         <v>3106745993</v>
       </c>
       <c r="K33" s="98" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="L33" s="49"/>
       <c r="M33" s="49"/>
@@ -44734,32 +44919,32 @@
         <v>25</v>
       </c>
       <c r="B34" s="97" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D34" s="98">
         <v>1018428656</v>
       </c>
       <c r="E34" s="80"/>
       <c r="F34" s="98" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G34" s="99">
         <v>3134172632</v>
       </c>
       <c r="H34" s="97" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I34" s="97" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J34" s="99">
         <v>3214064142</v>
       </c>
       <c r="K34" s="98" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L34" s="49"/>
       <c r="M34" s="49"/>
@@ -44783,32 +44968,32 @@
         <v>26</v>
       </c>
       <c r="B35" s="97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C35" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D35" s="98">
         <v>1140923149</v>
       </c>
       <c r="E35" s="80"/>
-      <c r="F35" s="201" t="s">
-        <v>162</v>
+      <c r="F35" s="104" t="s">
+        <v>160</v>
       </c>
       <c r="G35" s="99">
         <v>3104833651</v>
       </c>
       <c r="H35" s="97" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I35" s="97" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J35" s="99">
         <v>3013930753</v>
       </c>
       <c r="K35" s="98" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L35" s="49"/>
       <c r="M35" s="49"/>
@@ -44832,32 +45017,32 @@
         <v>27</v>
       </c>
       <c r="B36" s="97" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C36" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D36" s="98">
         <v>1027532372</v>
       </c>
       <c r="E36" s="79"/>
-      <c r="F36" s="201" t="s">
-        <v>163</v>
+      <c r="F36" s="104" t="s">
+        <v>161</v>
       </c>
       <c r="G36" s="99">
         <v>3245284047</v>
       </c>
       <c r="H36" s="97" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I36" s="97" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J36" s="99">
         <v>3125311107</v>
       </c>
       <c r="K36" s="98" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L36" s="49"/>
       <c r="M36" s="49"/>
@@ -44881,32 +45066,32 @@
         <v>28</v>
       </c>
       <c r="B37" s="97" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C37" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D37" s="98">
         <v>1056613175</v>
       </c>
       <c r="E37" s="80"/>
-      <c r="F37" s="201" t="s">
-        <v>164</v>
+      <c r="F37" s="104" t="s">
+        <v>162</v>
       </c>
       <c r="G37" s="99">
         <v>3177940362</v>
       </c>
       <c r="H37" s="97" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I37" s="97" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J37" s="99">
         <v>3132773117</v>
       </c>
       <c r="K37" s="98" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L37" s="49"/>
       <c r="M37" s="49"/>
@@ -44930,32 +45115,32 @@
         <v>29</v>
       </c>
       <c r="B38" s="97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C38" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D38" s="98">
         <v>1140923878</v>
       </c>
       <c r="E38" s="80"/>
-      <c r="F38" s="201" t="s">
-        <v>165</v>
+      <c r="F38" s="104" t="s">
+        <v>163</v>
       </c>
       <c r="G38" s="99">
         <v>3223041395</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I38" s="97" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J38" s="99">
         <v>3193169122</v>
       </c>
       <c r="K38" s="98" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L38" s="49"/>
       <c r="M38" s="49"/>
@@ -44979,32 +45164,32 @@
         <v>30</v>
       </c>
       <c r="B39" s="97" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C39" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D39" s="98">
         <v>1022971433</v>
       </c>
       <c r="E39" s="80"/>
-      <c r="F39" s="201" t="s">
-        <v>166</v>
+      <c r="F39" s="104" t="s">
+        <v>164</v>
       </c>
       <c r="G39" s="99">
         <v>3112245080</v>
       </c>
       <c r="H39" s="97" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I39" s="97" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J39" s="99">
         <v>3123632278</v>
       </c>
       <c r="K39" s="98" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L39" s="49"/>
       <c r="M39" s="49"/>
@@ -45028,32 +45213,32 @@
         <v>31</v>
       </c>
       <c r="B40" s="97" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C40" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D40" s="98">
         <v>1012921788</v>
       </c>
       <c r="E40" s="79"/>
       <c r="F40" s="98" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G40" s="99">
         <v>3134844084</v>
       </c>
       <c r="H40" s="97" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I40" s="97" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J40" s="99">
         <v>3143239415</v>
       </c>
       <c r="K40" s="98" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L40" s="49"/>
       <c r="M40" s="49"/>
@@ -45077,32 +45262,32 @@
         <v>32</v>
       </c>
       <c r="B41" s="97" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C41" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D41" s="98">
         <v>1188215179</v>
       </c>
       <c r="E41" s="79"/>
-      <c r="F41" s="201" t="s">
-        <v>168</v>
+      <c r="F41" s="104" t="s">
+        <v>166</v>
       </c>
       <c r="G41" s="99" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H41" s="97" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I41" s="97" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J41" s="99" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K41" s="98" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L41" s="49"/>
       <c r="M41" s="49"/>
@@ -45126,32 +45311,32 @@
         <v>33</v>
       </c>
       <c r="B42" s="97" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D42" s="98">
         <v>1033733815</v>
       </c>
       <c r="E42" s="79"/>
-      <c r="F42" s="201" t="s">
-        <v>169</v>
+      <c r="F42" s="104" t="s">
+        <v>167</v>
       </c>
       <c r="G42" s="99">
         <v>3209260931</v>
       </c>
       <c r="H42" s="97" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I42" s="97" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J42" s="99">
         <v>3195162596</v>
       </c>
       <c r="K42" s="98" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L42" s="49"/>
       <c r="M42" s="49"/>
@@ -45175,32 +45360,32 @@
         <v>34</v>
       </c>
       <c r="B43" s="97" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D43" s="98">
         <v>1025066944</v>
       </c>
       <c r="E43" s="79"/>
-      <c r="F43" s="201" t="s">
-        <v>170</v>
+      <c r="F43" s="104" t="s">
+        <v>168</v>
       </c>
       <c r="G43" s="99">
         <v>3118763312</v>
       </c>
       <c r="H43" s="97" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I43" s="97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J43" s="99">
         <v>3108870470</v>
       </c>
       <c r="K43" s="98" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L43" s="49"/>
       <c r="M43" s="49"/>
@@ -45224,32 +45409,32 @@
         <v>35</v>
       </c>
       <c r="B44" s="97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C44" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D44" s="98">
         <v>1033749725</v>
       </c>
       <c r="E44" s="79"/>
-      <c r="F44" s="201" t="s">
-        <v>171</v>
+      <c r="F44" s="104" t="s">
+        <v>169</v>
       </c>
       <c r="G44" s="99">
         <v>3219727458</v>
       </c>
       <c r="H44" s="97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I44" s="97" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J44" s="99" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K44" s="98" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L44" s="49"/>
       <c r="M44" s="49"/>
@@ -45273,32 +45458,32 @@
         <v>36</v>
       </c>
       <c r="B45" s="97" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D45" s="98">
         <v>1018447155</v>
       </c>
       <c r="E45" s="79"/>
-      <c r="F45" s="201" t="s">
-        <v>172</v>
+      <c r="F45" s="104" t="s">
+        <v>170</v>
       </c>
       <c r="G45" s="99">
         <v>3163797259</v>
       </c>
       <c r="H45" s="97" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I45" s="97" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J45" s="99">
         <v>3163797259</v>
       </c>
       <c r="K45" s="98" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L45" s="49"/>
       <c r="M45" s="49"/>
@@ -45321,32 +45506,32 @@
         <v>37</v>
       </c>
       <c r="B46" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="78" t="s">
         <v>135</v>
-      </c>
-      <c r="C46" s="78" t="s">
-        <v>137</v>
       </c>
       <c r="D46" s="98">
         <v>1140923124</v>
       </c>
       <c r="E46" s="84"/>
-      <c r="F46" s="201" t="s">
-        <v>173</v>
+      <c r="F46" s="104" t="s">
+        <v>171</v>
       </c>
       <c r="G46" s="99" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H46" s="97" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I46" s="97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J46" s="99" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K46" s="98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L46" s="62"/>
       <c r="M46" s="62"/>
@@ -45369,32 +45554,32 @@
         <v>38</v>
       </c>
       <c r="B47" s="97" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D47" s="98">
         <v>1022980809</v>
       </c>
       <c r="E47" s="84"/>
-      <c r="F47" s="201" t="s">
-        <v>174</v>
+      <c r="F47" s="104" t="s">
+        <v>172</v>
       </c>
       <c r="G47" s="99">
         <v>3134318441</v>
       </c>
       <c r="H47" s="97" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I47" s="97" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J47" s="99">
         <v>3134318441</v>
       </c>
       <c r="K47" s="98" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L47" s="49"/>
       <c r="M47" s="49"/>
@@ -45417,32 +45602,32 @@
         <v>39</v>
       </c>
       <c r="B48" s="97" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C48" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D48" s="98">
         <v>1016913212</v>
       </c>
       <c r="E48" s="84"/>
-      <c r="F48" s="201" t="s">
-        <v>175</v>
+      <c r="F48" s="104" t="s">
+        <v>173</v>
       </c>
       <c r="G48" s="99">
         <v>3135998322</v>
       </c>
       <c r="H48" s="97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I48" s="97" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J48" s="99">
         <v>3147952260</v>
       </c>
       <c r="K48" s="98" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L48" s="49"/>
       <c r="M48" s="49"/>
@@ -45465,32 +45650,32 @@
         <v>40</v>
       </c>
       <c r="B49" s="97" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C49" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D49" s="98">
         <v>1140921453</v>
       </c>
       <c r="E49" s="84"/>
-      <c r="F49" s="201" t="s">
-        <v>176</v>
+      <c r="F49" s="104" t="s">
+        <v>174</v>
       </c>
       <c r="G49" s="99">
         <v>3107171532</v>
       </c>
       <c r="H49" s="97" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I49" s="97" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J49" s="99">
         <v>3107171532</v>
       </c>
       <c r="K49" s="98" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L49" s="49"/>
       <c r="M49" s="49"/>
@@ -45513,32 +45698,32 @@
         <v>41</v>
       </c>
       <c r="B50" s="97" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C50" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D50" s="98">
         <v>1033749129</v>
       </c>
       <c r="E50" s="84"/>
-      <c r="F50" s="201" t="s">
-        <v>177</v>
+      <c r="F50" s="104" t="s">
+        <v>175</v>
       </c>
       <c r="G50" s="99">
         <v>3238465105</v>
       </c>
       <c r="H50" s="97" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I50" s="97" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J50" s="99">
         <v>3053938095</v>
       </c>
       <c r="K50" s="98" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L50" s="49"/>
       <c r="M50" s="49"/>
@@ -45563,7 +45748,7 @@
       <c r="D51" s="49"/>
       <c r="E51" s="49"/>
       <c r="F51" s="49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G51" s="49"/>
       <c r="H51" s="49"/>
@@ -53997,74 +54182,74 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="A1" s="200" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
+        <v>79</v>
+      </c>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
       <c r="E1" s="63"/>
       <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6" ht="15.75">
       <c r="A2" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="C2" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="D2" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="197" t="s">
-        <v>85</v>
+      <c r="A3" s="201" t="s">
+        <v>393</v>
       </c>
       <c r="B3" s="67" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="105" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="A4" s="202"/>
+      <c r="B4" s="67" t="s">
         <v>312</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C4" s="67" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="202" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="198"/>
-      <c r="B4" s="67" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>315</v>
-      </c>
-      <c r="D4" s="202" t="s">
-        <v>160</v>
+      <c r="D4" s="105" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="198"/>
+      <c r="A5" s="202"/>
       <c r="B5" s="67" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>383</v>
-      </c>
-      <c r="D5" s="202" t="s">
-        <v>174</v>
+        <v>380</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="198"/>
+      <c r="A6" s="202"/>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
       <c r="D6" s="68"/>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="199"/>
+      <c r="A7" s="203"/>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
       <c r="D7" s="70"/>
@@ -54074,590 +54259,588 @@
     </row>
     <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="D9" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="197" t="s">
-        <v>85</v>
+      <c r="A10" s="201" t="s">
+        <v>391</v>
       </c>
       <c r="B10" s="67" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="105" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75">
+      <c r="A11" s="202"/>
+      <c r="B11" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C11" s="67" t="s">
         <v>317</v>
       </c>
-      <c r="D10" s="202" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="198"/>
-      <c r="B11" s="67" t="s">
+      <c r="D11" s="105" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75">
+      <c r="A12" s="202"/>
+      <c r="B12" s="67" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C12" s="67" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="202" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="198"/>
-      <c r="B12" s="67" t="s">
+      <c r="D12" s="105" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75">
+      <c r="A13" s="202"/>
+      <c r="B13" s="67" t="s">
         <v>320</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C13" s="67" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="202" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="198"/>
-      <c r="B13" s="67" t="s">
+      <c r="D13" s="105" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75">
+      <c r="A14" s="203"/>
+      <c r="B14" s="69" t="s">
         <v>322</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C14" s="69" t="s">
         <v>323</v>
       </c>
-      <c r="D13" s="202" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="199"/>
-      <c r="B14" s="69" t="s">
-        <v>324</v>
-      </c>
-      <c r="C14" s="69" t="s">
-        <v>325</v>
-      </c>
-      <c r="D14" s="203" t="s">
-        <v>153</v>
+      <c r="D14" s="106" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="D16" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="197" t="s">
-        <v>85</v>
+      <c r="A17" s="201" t="s">
+        <v>397</v>
       </c>
       <c r="B17" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="D17" s="105" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75">
+      <c r="A18" s="202"/>
+      <c r="B18" s="67" t="s">
         <v>328</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C18" s="67" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="202" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="198"/>
-      <c r="B18" s="67" t="s">
+      <c r="D18" s="105" t="s">
         <v>330</v>
       </c>
-      <c r="C18" s="67" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="15.75">
+      <c r="A19" s="202"/>
+      <c r="B19" s="67" t="s">
         <v>331</v>
       </c>
-      <c r="D18" s="202" t="s">
+      <c r="C19" s="67" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="198"/>
-      <c r="B19" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="202" t="s">
-        <v>170</v>
+      <c r="D19" s="105" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="198"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="67"/>
       <c r="C20" s="67"/>
       <c r="D20" s="68"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="199"/>
+      <c r="A21" s="203"/>
       <c r="B21" s="69"/>
       <c r="C21" s="69"/>
       <c r="D21" s="70"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B23" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="D23" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="197" t="s">
-        <v>85</v>
+      <c r="A24" s="201" t="s">
+        <v>392</v>
       </c>
       <c r="B24" s="67" t="s">
+        <v>333</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="D24" s="105" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75">
+      <c r="A25" s="202"/>
+      <c r="B25" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C25" s="67" t="s">
         <v>336</v>
       </c>
-      <c r="D24" s="202" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="198"/>
-      <c r="B25" s="67" t="s">
+      <c r="D25" s="105" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75">
+      <c r="A26" s="202"/>
+      <c r="B26" s="67" t="s">
         <v>337</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C26" s="67" t="s">
         <v>338</v>
       </c>
-      <c r="D25" s="202" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="198"/>
-      <c r="B26" s="67" t="s">
+      <c r="D26" s="105" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75">
+      <c r="A27" s="202"/>
+      <c r="B27" s="67" t="s">
         <v>339</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C27" s="67" t="s">
         <v>340</v>
       </c>
-      <c r="D26" s="202" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="198"/>
-      <c r="B27" s="67" t="s">
+      <c r="D27" s="105" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75">
+      <c r="A28" s="203"/>
+      <c r="B28" s="69" t="s">
         <v>341</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C28" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="D27" s="202" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="199"/>
-      <c r="B28" s="69" t="s">
-        <v>343</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>344</v>
-      </c>
-      <c r="D28" s="203" t="s">
-        <v>162</v>
+      <c r="D28" s="106" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75">
       <c r="A30" s="64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B30" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="65" t="s">
+      <c r="D30" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="197" t="s">
-        <v>85</v>
+      <c r="A31" s="201" t="s">
+        <v>394</v>
       </c>
       <c r="B31" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="D31" s="105" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75">
+      <c r="A32" s="202"/>
+      <c r="B32" s="67" t="s">
         <v>345</v>
       </c>
-      <c r="C31" s="67" t="s">
+      <c r="C32" s="67" t="s">
         <v>346</v>
       </c>
-      <c r="D31" s="202" t="s">
+      <c r="D32" s="105" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="198"/>
-      <c r="B32" s="67" t="s">
+    <row r="33" spans="1:4" ht="15.75">
+      <c r="A33" s="202"/>
+      <c r="B33" s="67" t="s">
         <v>347</v>
       </c>
-      <c r="C32" s="67" t="s">
+      <c r="C33" s="67" t="s">
         <v>348</v>
       </c>
-      <c r="D32" s="202" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="198"/>
-      <c r="B33" s="67" t="s">
-        <v>349</v>
-      </c>
-      <c r="C33" s="67" t="s">
-        <v>350</v>
-      </c>
-      <c r="D33" s="202" t="s">
-        <v>155</v>
+      <c r="D33" s="105" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="198"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="67"/>
+      <c r="A34" s="202"/>
+      <c r="B34" s="67" t="s">
+        <v>401</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>402</v>
+      </c>
       <c r="D34" s="68"/>
     </row>
     <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="199"/>
+      <c r="A35" s="203"/>
       <c r="B35" s="69"/>
       <c r="C35" s="69"/>
       <c r="D35" s="70"/>
     </row>
     <row r="37" spans="1:4" ht="15.75">
       <c r="A37" s="64" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B37" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="65" t="s">
+      <c r="D37" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="197" t="s">
-        <v>85</v>
+      <c r="A38" s="201" t="s">
+        <v>396</v>
       </c>
       <c r="B38" s="67" t="s">
+        <v>349</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="D38" s="105" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75">
+      <c r="A39" s="202"/>
+      <c r="B39" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" s="67" t="s">
         <v>351</v>
       </c>
-      <c r="C38" s="67" t="s">
+      <c r="D39" s="105" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75">
+      <c r="A40" s="202"/>
+      <c r="B40" s="67" t="s">
         <v>352</v>
       </c>
-      <c r="D38" s="202" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="198"/>
-      <c r="B39" s="67" t="s">
+      <c r="C40" s="67" t="s">
         <v>353</v>
       </c>
-      <c r="C39" s="67" t="s">
+      <c r="D40" s="105" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75">
+      <c r="A41" s="202"/>
+      <c r="B41" s="67" t="s">
         <v>354</v>
       </c>
-      <c r="D39" s="202" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="198"/>
-      <c r="B40" s="67" t="s">
+      <c r="C41" s="67" t="s">
         <v>355</v>
       </c>
-      <c r="C40" s="67" t="s">
+      <c r="D41" s="105" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75">
+      <c r="A42" s="203"/>
+      <c r="B42" s="69" t="s">
         <v>356</v>
       </c>
-      <c r="D40" s="202" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="198"/>
-      <c r="B41" s="67" t="s">
+      <c r="C42" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="C41" s="67" t="s">
-        <v>358</v>
-      </c>
-      <c r="D41" s="202" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="199"/>
-      <c r="B42" s="69" t="s">
-        <v>359</v>
-      </c>
-      <c r="C42" s="69" t="s">
-        <v>360</v>
-      </c>
-      <c r="D42" s="203" t="s">
-        <v>157</v>
+      <c r="D42" s="106" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
     <row r="44" spans="1:4" ht="15" customHeight="1">
       <c r="A44" s="64" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B44" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="65" t="s">
+      <c r="D44" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1">
-      <c r="A45" s="197" t="s">
-        <v>85</v>
+      <c r="A45" s="201" t="s">
+        <v>398</v>
       </c>
       <c r="B45" s="67" t="s">
+        <v>358</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>359</v>
+      </c>
+      <c r="D45" s="105" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1">
+      <c r="A46" s="202"/>
+      <c r="B46" s="67" t="s">
+        <v>360</v>
+      </c>
+      <c r="C46" s="67" t="s">
         <v>361</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="D46" s="105" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1">
+      <c r="A47" s="202"/>
+      <c r="B47" s="67" t="s">
         <v>362</v>
       </c>
-      <c r="D45" s="202" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="198"/>
-      <c r="B46" s="67" t="s">
+      <c r="C47" s="67" t="s">
         <v>363</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="D47" s="105" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1">
+      <c r="A48" s="202"/>
+      <c r="B48" s="67" t="s">
         <v>364</v>
       </c>
-      <c r="D46" s="202" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="198"/>
-      <c r="B47" s="67" t="s">
+      <c r="C48" s="67" t="s">
         <v>365</v>
       </c>
-      <c r="C47" s="67" t="s">
+      <c r="D48" s="105" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A49" s="203"/>
+      <c r="B49" s="69" t="s">
         <v>366</v>
       </c>
-      <c r="D47" s="202" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="198"/>
-      <c r="B48" s="67" t="s">
+      <c r="C49" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="C48" s="67" t="s">
-        <v>368</v>
-      </c>
-      <c r="D48" s="202" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="199"/>
-      <c r="B49" s="69" t="s">
-        <v>369</v>
-      </c>
-      <c r="C49" s="69" t="s">
-        <v>370</v>
-      </c>
-      <c r="D49" s="203" t="s">
-        <v>173</v>
+      <c r="D49" s="106" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
     <row r="51" spans="1:4" ht="15" customHeight="1">
       <c r="A51" s="64" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B51" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="D51" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D51" s="66" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
-      <c r="A52" s="197" t="s">
-        <v>85</v>
+      <c r="A52" s="201" t="s">
+        <v>399</v>
       </c>
       <c r="B52" s="67" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="67" t="s">
+        <v>369</v>
+      </c>
+      <c r="D52" s="105" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1">
+      <c r="A53" s="202"/>
+      <c r="B53" s="67" t="s">
+        <v>370</v>
+      </c>
+      <c r="C53" s="67" t="s">
         <v>371</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="D53" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1">
+      <c r="A54" s="202"/>
+      <c r="B54" s="67" t="s">
         <v>372</v>
       </c>
-      <c r="D52" s="202" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1">
-      <c r="A53" s="198"/>
-      <c r="B53" s="67" t="s">
+      <c r="C54" s="67" t="s">
         <v>373</v>
       </c>
-      <c r="C53" s="67" t="s">
-        <v>374</v>
-      </c>
-      <c r="D53" s="202" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1">
-      <c r="A54" s="198"/>
-      <c r="B54" s="67" t="s">
+      <c r="D54" s="105" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1">
+      <c r="A55" s="202"/>
+      <c r="B55" s="67" t="s">
         <v>375</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C55" s="67" t="s">
         <v>376</v>
       </c>
-      <c r="D54" s="202" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1">
-      <c r="A55" s="198"/>
-      <c r="B55" s="67" t="s">
+      <c r="D55" s="105" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A56" s="203"/>
+      <c r="B56" s="69" t="s">
+        <v>377</v>
+      </c>
+      <c r="C56" s="69" t="s">
         <v>378</v>
       </c>
-      <c r="C55" s="67" t="s">
-        <v>379</v>
-      </c>
-      <c r="D55" s="202" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="199"/>
-      <c r="B56" s="69" t="s">
-        <v>380</v>
-      </c>
-      <c r="C56" s="69" t="s">
-        <v>381</v>
-      </c>
-      <c r="D56" s="203" t="s">
-        <v>175</v>
+      <c r="D56" s="106" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
     <row r="58" spans="1:4" ht="15" customHeight="1">
       <c r="A58" s="64" t="s">
+        <v>381</v>
+      </c>
+      <c r="B58" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="D58" s="66" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15" customHeight="1">
+      <c r="A59" s="201" t="s">
+        <v>400</v>
+      </c>
+      <c r="B59" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="C59" s="67" t="s">
+        <v>383</v>
+      </c>
+      <c r="D59" s="105" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" customHeight="1">
+      <c r="A60" s="202"/>
+      <c r="B60" s="67" t="s">
         <v>384</v>
       </c>
-      <c r="B58" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" s="65" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="66" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="197" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" s="67" t="s">
+      <c r="C60" s="67" t="s">
         <v>385</v>
       </c>
-      <c r="C59" s="67" t="s">
+      <c r="D60" s="105" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1">
+      <c r="A61" s="202"/>
+      <c r="B61" s="67" t="s">
         <v>386</v>
       </c>
-      <c r="D59" s="202" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="15" customHeight="1">
-      <c r="A60" s="198"/>
-      <c r="B60" s="67" t="s">
+      <c r="C61" s="67" t="s">
         <v>387</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="D61" s="105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15" customHeight="1">
+      <c r="A62" s="202"/>
+      <c r="B62" s="67" t="s">
         <v>388</v>
       </c>
-      <c r="D60" s="202" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15" customHeight="1">
-      <c r="A61" s="198"/>
-      <c r="B61" s="67" t="s">
+      <c r="C62" s="67" t="s">
         <v>389</v>
       </c>
-      <c r="C61" s="67" t="s">
-        <v>390</v>
-      </c>
-      <c r="D61" s="202" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15" customHeight="1">
-      <c r="A62" s="198"/>
-      <c r="B62" s="67" t="s">
-        <v>391</v>
-      </c>
-      <c r="C62" s="67" t="s">
-        <v>392</v>
-      </c>
-      <c r="D62" s="202" t="s">
-        <v>169</v>
+      <c r="D62" s="105" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="199"/>
-      <c r="B63" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="C63" s="69" t="s">
-        <v>394</v>
-      </c>
-      <c r="D63" s="203" t="s">
-        <v>156</v>
-      </c>
+      <c r="A63" s="203"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -54711,7 +54894,6 @@
     <hyperlink ref="D60" r:id="rId36" xr:uid="{C49ABC81-DB8E-4F2E-9C85-2D624440584B}"/>
     <hyperlink ref="D61" r:id="rId37" xr:uid="{C4482557-B698-4542-81E9-63BE65D1CD80}"/>
     <hyperlink ref="D62" r:id="rId38" xr:uid="{E4C328B2-4566-46A1-ADF6-DEFB234BD68A}"/>
-    <hyperlink ref="D63" r:id="rId39" xr:uid="{0A7A2C8D-9372-4EB0-9362-43DC252D30DF}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>

--- a/assets/Listados/CJLL - 3415417 - 2026.xlsx
+++ b/assets/Listados/CJLL - 3415417 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A84F680-8436-41BC-BBC6-BD7C86F99F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361D8AD4-4A64-4ED4-9E33-EF657D90B15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="405">
   <si>
     <r>
       <rPr>
@@ -1436,6 +1436,12 @@
   <si>
     <t>Ochoa Bayona</t>
   </si>
+  <si>
+    <t>Laura Camila</t>
+  </si>
+  <si>
+    <t>Gómez Beltrán</t>
+  </si>
 </sst>
 </file>
 
@@ -1924,7 +1930,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="81">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -2884,12 +2890,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3157,84 +3176,95 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3243,17 +3273,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3267,86 +3291,93 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3360,263 +3391,22 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="81" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="104">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10.5"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Roboto"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF2E75B5"/>
@@ -4808,6 +4598,237 @@
       </fill>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="10.5"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -4909,17 +4930,17 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla_1" displayName="Tabla_1" ref="A9:K50">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo de documento" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="No de documento de identidad" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Correo electrónico @soy.sena.edu.co" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Correo  electrónico alterno" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Teléfono de contacto" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nombres completos del acudiente" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Correo_Acudiente" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Teléfono de Acudiente" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ID_Drive" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No" dataDxfId="99"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo de documento" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="No de documento de identidad" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Correo electrónico @soy.sena.edu.co" dataDxfId="95"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Correo  electrónico alterno" dataDxfId="94"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Teléfono de contacto" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nombres completos del acudiente" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Correo_Acudiente" dataDxfId="91"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Teléfono de Acudiente" dataDxfId="90"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ID_Drive" dataDxfId="89"/>
   </tableColumns>
   <tableStyleInfo name="BASE DE DATOS-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5146,125 +5167,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="179"/>
-      <c r="B1" s="180"/>
-      <c r="C1" s="183" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="180"/>
-      <c r="G1" s="159" t="s">
+      <c r="A1" s="143"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="144" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="166"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="163"/>
-      <c r="T1" s="167"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="168"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
-      <c r="AA1" s="108"/>
-      <c r="AB1" s="167"/>
-      <c r="AC1" s="108"/>
-      <c r="AD1" s="108"/>
-      <c r="AE1" s="108"/>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
-      <c r="AI1" s="108"/>
-      <c r="AJ1" s="108"/>
-      <c r="AK1" s="111"/>
-      <c r="AL1" s="107"/>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="108"/>
-      <c r="AO1" s="108"/>
-      <c r="AP1" s="108"/>
-      <c r="AQ1" s="108"/>
-      <c r="AR1" s="108"/>
-      <c r="AS1" s="108"/>
-      <c r="AT1" s="108"/>
-      <c r="AU1" s="109"/>
-      <c r="AV1" s="108"/>
-      <c r="AW1" s="108"/>
-      <c r="AX1" s="108"/>
-      <c r="AY1" s="108"/>
-      <c r="AZ1" s="108"/>
-      <c r="BA1" s="108"/>
-      <c r="BB1" s="108"/>
-      <c r="BC1" s="108"/>
-      <c r="BD1" s="108"/>
-      <c r="BE1" s="108"/>
-      <c r="BF1" s="108"/>
-      <c r="BG1" s="108"/>
-      <c r="BH1" s="108"/>
-      <c r="BI1" s="108"/>
-      <c r="BJ1" s="108"/>
-      <c r="BK1" s="108"/>
-      <c r="BL1" s="108"/>
-      <c r="BM1" s="108"/>
-      <c r="BN1" s="108"/>
-      <c r="BO1" s="108"/>
-      <c r="BP1" s="108"/>
-      <c r="BQ1" s="108"/>
-      <c r="BR1" s="108"/>
-      <c r="BS1" s="108"/>
-      <c r="BT1" s="108"/>
-      <c r="BU1" s="108"/>
-      <c r="BV1" s="110"/>
-      <c r="BW1" s="108"/>
-      <c r="BX1" s="108"/>
-      <c r="BY1" s="108"/>
-      <c r="BZ1" s="108"/>
-      <c r="CA1" s="108"/>
-      <c r="CB1" s="108"/>
-      <c r="CC1" s="108"/>
-      <c r="CD1" s="108"/>
-      <c r="CE1" s="108"/>
-      <c r="CF1" s="108"/>
-      <c r="CG1" s="108"/>
-      <c r="CH1" s="108"/>
-      <c r="CI1" s="108"/>
-      <c r="CJ1" s="108"/>
-      <c r="CK1" s="108"/>
-      <c r="CL1" s="108"/>
-      <c r="CM1" s="108"/>
-      <c r="CN1" s="108"/>
-      <c r="CO1" s="108"/>
-      <c r="CP1" s="108"/>
-      <c r="CQ1" s="108"/>
-      <c r="CR1" s="111"/>
-      <c r="CS1" s="114" t="s">
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="123"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="123"/>
+      <c r="AD1" s="123"/>
+      <c r="AE1" s="123"/>
+      <c r="AF1" s="123"/>
+      <c r="AG1" s="123"/>
+      <c r="AH1" s="123"/>
+      <c r="AI1" s="123"/>
+      <c r="AJ1" s="123"/>
+      <c r="AK1" s="125"/>
+      <c r="AL1" s="179"/>
+      <c r="AM1" s="123"/>
+      <c r="AN1" s="123"/>
+      <c r="AO1" s="123"/>
+      <c r="AP1" s="123"/>
+      <c r="AQ1" s="123"/>
+      <c r="AR1" s="123"/>
+      <c r="AS1" s="123"/>
+      <c r="AT1" s="123"/>
+      <c r="AU1" s="180"/>
+      <c r="AV1" s="123"/>
+      <c r="AW1" s="123"/>
+      <c r="AX1" s="123"/>
+      <c r="AY1" s="123"/>
+      <c r="AZ1" s="123"/>
+      <c r="BA1" s="123"/>
+      <c r="BB1" s="123"/>
+      <c r="BC1" s="123"/>
+      <c r="BD1" s="123"/>
+      <c r="BE1" s="123"/>
+      <c r="BF1" s="123"/>
+      <c r="BG1" s="123"/>
+      <c r="BH1" s="123"/>
+      <c r="BI1" s="123"/>
+      <c r="BJ1" s="123"/>
+      <c r="BK1" s="123"/>
+      <c r="BL1" s="123"/>
+      <c r="BM1" s="123"/>
+      <c r="BN1" s="123"/>
+      <c r="BO1" s="123"/>
+      <c r="BP1" s="123"/>
+      <c r="BQ1" s="123"/>
+      <c r="BR1" s="123"/>
+      <c r="BS1" s="123"/>
+      <c r="BT1" s="123"/>
+      <c r="BU1" s="123"/>
+      <c r="BV1" s="181"/>
+      <c r="BW1" s="123"/>
+      <c r="BX1" s="123"/>
+      <c r="BY1" s="123"/>
+      <c r="BZ1" s="123"/>
+      <c r="CA1" s="123"/>
+      <c r="CB1" s="123"/>
+      <c r="CC1" s="123"/>
+      <c r="CD1" s="123"/>
+      <c r="CE1" s="123"/>
+      <c r="CF1" s="123"/>
+      <c r="CG1" s="123"/>
+      <c r="CH1" s="123"/>
+      <c r="CI1" s="123"/>
+      <c r="CJ1" s="123"/>
+      <c r="CK1" s="123"/>
+      <c r="CL1" s="123"/>
+      <c r="CM1" s="123"/>
+      <c r="CN1" s="123"/>
+      <c r="CO1" s="123"/>
+      <c r="CP1" s="123"/>
+      <c r="CQ1" s="123"/>
+      <c r="CR1" s="125"/>
+      <c r="CS1" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="115"/>
-      <c r="CU1" s="115"/>
-      <c r="CV1" s="115"/>
-      <c r="CW1" s="116"/>
+      <c r="CT1" s="184"/>
+      <c r="CU1" s="184"/>
+      <c r="CV1" s="184"/>
+      <c r="CW1" s="185"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="131" t="s">
+      <c r="CY1" s="173" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="118"/>
-      <c r="DA1" s="118"/>
-      <c r="DB1" s="118"/>
-      <c r="DC1" s="118"/>
-      <c r="DD1" s="118"/>
-      <c r="DE1" s="118"/>
-      <c r="DF1" s="118"/>
-      <c r="DG1" s="118"/>
+      <c r="CZ1" s="174"/>
+      <c r="DA1" s="174"/>
+      <c r="DB1" s="174"/>
+      <c r="DC1" s="174"/>
+      <c r="DD1" s="174"/>
+      <c r="DE1" s="174"/>
+      <c r="DF1" s="174"/>
+      <c r="DG1" s="174"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -5283,122 +5304,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="181"/>
-      <c r="B2" s="182"/>
-      <c r="C2" s="181"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="159" t="s">
+      <c r="A2" s="113"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
       <c r="P2" s="160"/>
-      <c r="Q2" s="161"/>
-      <c r="R2" s="161"/>
-      <c r="S2" s="161"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="125"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="169"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
-      <c r="AE2" s="113"/>
-      <c r="AF2" s="113"/>
-      <c r="AG2" s="113"/>
-      <c r="AH2" s="113"/>
-      <c r="AI2" s="113"/>
-      <c r="AJ2" s="113"/>
-      <c r="AK2" s="125"/>
-      <c r="AL2" s="127"/>
-      <c r="AM2" s="113"/>
-      <c r="AN2" s="113"/>
-      <c r="AO2" s="113"/>
-      <c r="AP2" s="113"/>
-      <c r="AQ2" s="113"/>
-      <c r="AR2" s="113"/>
-      <c r="AS2" s="113"/>
-      <c r="AT2" s="113"/>
-      <c r="AU2" s="123"/>
-      <c r="AV2" s="113"/>
-      <c r="AW2" s="113"/>
-      <c r="AX2" s="113"/>
-      <c r="AY2" s="113"/>
-      <c r="AZ2" s="113"/>
-      <c r="BA2" s="113"/>
-      <c r="BB2" s="113"/>
-      <c r="BC2" s="113"/>
-      <c r="BD2" s="113"/>
-      <c r="BE2" s="113"/>
-      <c r="BF2" s="113"/>
-      <c r="BG2" s="113"/>
-      <c r="BH2" s="113"/>
-      <c r="BI2" s="113"/>
-      <c r="BJ2" s="113"/>
-      <c r="BK2" s="113"/>
-      <c r="BL2" s="113"/>
-      <c r="BM2" s="113"/>
-      <c r="BN2" s="113"/>
-      <c r="BO2" s="113"/>
-      <c r="BP2" s="113"/>
-      <c r="BQ2" s="113"/>
-      <c r="BR2" s="113"/>
-      <c r="BS2" s="113"/>
-      <c r="BT2" s="113"/>
-      <c r="BU2" s="113"/>
-      <c r="BV2" s="124"/>
-      <c r="BW2" s="113"/>
-      <c r="BX2" s="113"/>
-      <c r="BY2" s="113"/>
-      <c r="BZ2" s="113"/>
-      <c r="CA2" s="113"/>
-      <c r="CB2" s="113"/>
-      <c r="CC2" s="113"/>
-      <c r="CD2" s="113"/>
-      <c r="CE2" s="113"/>
-      <c r="CF2" s="113"/>
-      <c r="CG2" s="113"/>
-      <c r="CH2" s="113"/>
-      <c r="CI2" s="113"/>
-      <c r="CJ2" s="113"/>
-      <c r="CK2" s="113"/>
-      <c r="CL2" s="113"/>
-      <c r="CM2" s="113"/>
-      <c r="CN2" s="113"/>
-      <c r="CO2" s="113"/>
-      <c r="CP2" s="113"/>
-      <c r="CQ2" s="113"/>
-      <c r="CR2" s="125"/>
-      <c r="CS2" s="117"/>
-      <c r="CT2" s="118"/>
-      <c r="CU2" s="118"/>
-      <c r="CV2" s="118"/>
-      <c r="CW2" s="119"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="108"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="108"/>
+      <c r="Z2" s="108"/>
+      <c r="AA2" s="108"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="108"/>
+      <c r="AD2" s="108"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
+      <c r="AG2" s="108"/>
+      <c r="AH2" s="108"/>
+      <c r="AI2" s="108"/>
+      <c r="AJ2" s="108"/>
+      <c r="AK2" s="127"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="108"/>
+      <c r="AO2" s="108"/>
+      <c r="AP2" s="108"/>
+      <c r="AQ2" s="108"/>
+      <c r="AR2" s="108"/>
+      <c r="AS2" s="108"/>
+      <c r="AT2" s="108"/>
+      <c r="AU2" s="154"/>
+      <c r="AV2" s="108"/>
+      <c r="AW2" s="108"/>
+      <c r="AX2" s="108"/>
+      <c r="AY2" s="108"/>
+      <c r="AZ2" s="108"/>
+      <c r="BA2" s="108"/>
+      <c r="BB2" s="108"/>
+      <c r="BC2" s="108"/>
+      <c r="BD2" s="108"/>
+      <c r="BE2" s="108"/>
+      <c r="BF2" s="108"/>
+      <c r="BG2" s="108"/>
+      <c r="BH2" s="108"/>
+      <c r="BI2" s="108"/>
+      <c r="BJ2" s="108"/>
+      <c r="BK2" s="108"/>
+      <c r="BL2" s="108"/>
+      <c r="BM2" s="108"/>
+      <c r="BN2" s="108"/>
+      <c r="BO2" s="108"/>
+      <c r="BP2" s="108"/>
+      <c r="BQ2" s="108"/>
+      <c r="BR2" s="108"/>
+      <c r="BS2" s="108"/>
+      <c r="BT2" s="108"/>
+      <c r="BU2" s="108"/>
+      <c r="BV2" s="188"/>
+      <c r="BW2" s="108"/>
+      <c r="BX2" s="108"/>
+      <c r="BY2" s="108"/>
+      <c r="BZ2" s="108"/>
+      <c r="CA2" s="108"/>
+      <c r="CB2" s="108"/>
+      <c r="CC2" s="108"/>
+      <c r="CD2" s="108"/>
+      <c r="CE2" s="108"/>
+      <c r="CF2" s="108"/>
+      <c r="CG2" s="108"/>
+      <c r="CH2" s="108"/>
+      <c r="CI2" s="108"/>
+      <c r="CJ2" s="108"/>
+      <c r="CK2" s="108"/>
+      <c r="CL2" s="108"/>
+      <c r="CM2" s="108"/>
+      <c r="CN2" s="108"/>
+      <c r="CO2" s="108"/>
+      <c r="CP2" s="108"/>
+      <c r="CQ2" s="108"/>
+      <c r="CR2" s="127"/>
+      <c r="CS2" s="186"/>
+      <c r="CT2" s="174"/>
+      <c r="CU2" s="174"/>
+      <c r="CV2" s="174"/>
+      <c r="CW2" s="187"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="132">
+      <c r="CY2" s="175">
         <f>COUNTA('BASE DE DATOS'!B26:B50)</f>
         <v>25</v>
       </c>
-      <c r="CZ2" s="133"/>
-      <c r="DA2" s="133"/>
-      <c r="DB2" s="133"/>
-      <c r="DC2" s="133"/>
-      <c r="DD2" s="133"/>
-      <c r="DE2" s="133"/>
-      <c r="DF2" s="133"/>
-      <c r="DG2" s="133"/>
+      <c r="CZ2" s="132"/>
+      <c r="DA2" s="132"/>
+      <c r="DB2" s="132"/>
+      <c r="DC2" s="132"/>
+      <c r="DD2" s="132"/>
+      <c r="DE2" s="132"/>
+      <c r="DF2" s="132"/>
+      <c r="DG2" s="132"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -5417,113 +5438,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="113"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="164" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="113"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="171" t="s">
+      <c r="E3" s="108"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="113"/>
-      <c r="I3" s="113"/>
-      <c r="J3" s="113"/>
-      <c r="K3" s="113"/>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="165"/>
-      <c r="Q3" s="113"/>
-      <c r="R3" s="113"/>
-      <c r="S3" s="113"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="113"/>
-      <c r="V3" s="113"/>
-      <c r="W3" s="125"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="113"/>
-      <c r="Z3" s="113"/>
-      <c r="AA3" s="113"/>
-      <c r="AB3" s="154"/>
-      <c r="AC3" s="113"/>
-      <c r="AD3" s="113"/>
-      <c r="AE3" s="113"/>
-      <c r="AF3" s="113"/>
-      <c r="AG3" s="113"/>
-      <c r="AH3" s="113"/>
-      <c r="AI3" s="113"/>
-      <c r="AJ3" s="113"/>
-      <c r="AK3" s="125"/>
-      <c r="AL3" s="112"/>
-      <c r="AM3" s="113"/>
-      <c r="AN3" s="113"/>
-      <c r="AO3" s="113"/>
-      <c r="AP3" s="113"/>
-      <c r="AQ3" s="113"/>
-      <c r="AR3" s="113"/>
-      <c r="AS3" s="113"/>
-      <c r="AT3" s="113"/>
-      <c r="AU3" s="138"/>
-      <c r="AV3" s="113"/>
-      <c r="AW3" s="113"/>
-      <c r="AX3" s="113"/>
-      <c r="AY3" s="113"/>
-      <c r="AZ3" s="113"/>
-      <c r="BA3" s="113"/>
-      <c r="BB3" s="113"/>
-      <c r="BC3" s="113"/>
-      <c r="BD3" s="113"/>
-      <c r="BE3" s="113"/>
-      <c r="BF3" s="113"/>
-      <c r="BG3" s="113"/>
-      <c r="BH3" s="113"/>
-      <c r="BI3" s="113"/>
-      <c r="BJ3" s="113"/>
-      <c r="BK3" s="113"/>
-      <c r="BL3" s="113"/>
-      <c r="BM3" s="113"/>
-      <c r="BN3" s="113"/>
-      <c r="BO3" s="113"/>
-      <c r="BP3" s="113"/>
-      <c r="BQ3" s="113"/>
-      <c r="BR3" s="113"/>
-      <c r="BS3" s="113"/>
-      <c r="BT3" s="113"/>
-      <c r="BU3" s="113"/>
-      <c r="BV3" s="126"/>
-      <c r="BW3" s="113"/>
-      <c r="BX3" s="113"/>
-      <c r="BY3" s="113"/>
-      <c r="BZ3" s="113"/>
-      <c r="CA3" s="113"/>
-      <c r="CB3" s="113"/>
-      <c r="CC3" s="113"/>
-      <c r="CD3" s="113"/>
-      <c r="CE3" s="113"/>
-      <c r="CF3" s="113"/>
-      <c r="CG3" s="113"/>
-      <c r="CH3" s="113"/>
-      <c r="CI3" s="113"/>
-      <c r="CJ3" s="113"/>
-      <c r="CK3" s="113"/>
-      <c r="CL3" s="113"/>
-      <c r="CM3" s="113"/>
-      <c r="CN3" s="113"/>
-      <c r="CO3" s="113"/>
-      <c r="CP3" s="113"/>
-      <c r="CQ3" s="113"/>
-      <c r="CR3" s="125"/>
-      <c r="CS3" s="117"/>
-      <c r="CT3" s="118"/>
-      <c r="CU3" s="118"/>
-      <c r="CV3" s="118"/>
-      <c r="CW3" s="119"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="146"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="142"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="156"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="142"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="108"/>
+      <c r="AF3" s="108"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="108"/>
+      <c r="AI3" s="108"/>
+      <c r="AJ3" s="108"/>
+      <c r="AK3" s="127"/>
+      <c r="AL3" s="182"/>
+      <c r="AM3" s="108"/>
+      <c r="AN3" s="108"/>
+      <c r="AO3" s="108"/>
+      <c r="AP3" s="108"/>
+      <c r="AQ3" s="108"/>
+      <c r="AR3" s="108"/>
+      <c r="AS3" s="108"/>
+      <c r="AT3" s="108"/>
+      <c r="AU3" s="176"/>
+      <c r="AV3" s="108"/>
+      <c r="AW3" s="108"/>
+      <c r="AX3" s="108"/>
+      <c r="AY3" s="108"/>
+      <c r="AZ3" s="108"/>
+      <c r="BA3" s="108"/>
+      <c r="BB3" s="108"/>
+      <c r="BC3" s="108"/>
+      <c r="BD3" s="108"/>
+      <c r="BE3" s="108"/>
+      <c r="BF3" s="108"/>
+      <c r="BG3" s="108"/>
+      <c r="BH3" s="108"/>
+      <c r="BI3" s="108"/>
+      <c r="BJ3" s="108"/>
+      <c r="BK3" s="108"/>
+      <c r="BL3" s="108"/>
+      <c r="BM3" s="108"/>
+      <c r="BN3" s="108"/>
+      <c r="BO3" s="108"/>
+      <c r="BP3" s="108"/>
+      <c r="BQ3" s="108"/>
+      <c r="BR3" s="108"/>
+      <c r="BS3" s="108"/>
+      <c r="BT3" s="108"/>
+      <c r="BU3" s="108"/>
+      <c r="BV3" s="189"/>
+      <c r="BW3" s="108"/>
+      <c r="BX3" s="108"/>
+      <c r="BY3" s="108"/>
+      <c r="BZ3" s="108"/>
+      <c r="CA3" s="108"/>
+      <c r="CB3" s="108"/>
+      <c r="CC3" s="108"/>
+      <c r="CD3" s="108"/>
+      <c r="CE3" s="108"/>
+      <c r="CF3" s="108"/>
+      <c r="CG3" s="108"/>
+      <c r="CH3" s="108"/>
+      <c r="CI3" s="108"/>
+      <c r="CJ3" s="108"/>
+      <c r="CK3" s="108"/>
+      <c r="CL3" s="108"/>
+      <c r="CM3" s="108"/>
+      <c r="CN3" s="108"/>
+      <c r="CO3" s="108"/>
+      <c r="CP3" s="108"/>
+      <c r="CQ3" s="108"/>
+      <c r="CR3" s="127"/>
+      <c r="CS3" s="186"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="187"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -5552,142 +5573,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="162" t="s">
+      <c r="A4" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="113"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="170" t="s">
+      <c r="B4" s="108"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="113"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="172" t="s">
+      <c r="E4" s="108"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="129"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="129"/>
-      <c r="N4" s="129"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="129"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="175"/>
-      <c r="U4" s="129"/>
-      <c r="V4" s="129"/>
-      <c r="W4" s="130"/>
-      <c r="X4" s="176"/>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
-      <c r="AB4" s="177"/>
-      <c r="AC4" s="129"/>
-      <c r="AD4" s="129"/>
-      <c r="AE4" s="129"/>
-      <c r="AF4" s="129"/>
-      <c r="AG4" s="129"/>
-      <c r="AH4" s="129"/>
-      <c r="AI4" s="129"/>
-      <c r="AJ4" s="129"/>
-      <c r="AK4" s="130"/>
-      <c r="AL4" s="128"/>
-      <c r="AM4" s="129"/>
-      <c r="AN4" s="129"/>
-      <c r="AO4" s="129"/>
-      <c r="AP4" s="129"/>
-      <c r="AQ4" s="129"/>
-      <c r="AR4" s="129"/>
-      <c r="AS4" s="129"/>
-      <c r="AT4" s="130"/>
-      <c r="AU4" s="139"/>
-      <c r="AV4" s="129"/>
-      <c r="AW4" s="129"/>
-      <c r="AX4" s="129"/>
-      <c r="AY4" s="129"/>
-      <c r="AZ4" s="129"/>
-      <c r="BA4" s="129"/>
-      <c r="BB4" s="129"/>
-      <c r="BC4" s="129"/>
-      <c r="BD4" s="129"/>
-      <c r="BE4" s="129"/>
-      <c r="BF4" s="129"/>
-      <c r="BG4" s="129"/>
-      <c r="BH4" s="129"/>
-      <c r="BI4" s="129"/>
-      <c r="BJ4" s="129"/>
-      <c r="BK4" s="129"/>
-      <c r="BL4" s="129"/>
-      <c r="BM4" s="129"/>
-      <c r="BN4" s="129"/>
-      <c r="BO4" s="129"/>
-      <c r="BP4" s="129"/>
-      <c r="BQ4" s="129"/>
-      <c r="BR4" s="129"/>
-      <c r="BS4" s="129"/>
-      <c r="BT4" s="129"/>
-      <c r="BU4" s="129"/>
-      <c r="BV4" s="140"/>
-      <c r="BW4" s="129"/>
-      <c r="BX4" s="129"/>
-      <c r="BY4" s="129"/>
-      <c r="BZ4" s="129"/>
-      <c r="CA4" s="129"/>
-      <c r="CB4" s="129"/>
-      <c r="CC4" s="129"/>
-      <c r="CD4" s="129"/>
-      <c r="CE4" s="129"/>
-      <c r="CF4" s="129"/>
-      <c r="CG4" s="129"/>
-      <c r="CH4" s="129"/>
-      <c r="CI4" s="129"/>
-      <c r="CJ4" s="129"/>
-      <c r="CK4" s="129"/>
-      <c r="CL4" s="129"/>
-      <c r="CM4" s="129"/>
-      <c r="CN4" s="129"/>
-      <c r="CO4" s="129"/>
-      <c r="CP4" s="129"/>
-      <c r="CQ4" s="129"/>
-      <c r="CR4" s="130"/>
-      <c r="CS4" s="117"/>
-      <c r="CT4" s="118"/>
-      <c r="CU4" s="118"/>
-      <c r="CV4" s="118"/>
-      <c r="CW4" s="119"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="136"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="137"/>
+      <c r="X4" s="139"/>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="140"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="111"/>
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="137"/>
+      <c r="AL4" s="190"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="111"/>
+      <c r="AQ4" s="111"/>
+      <c r="AR4" s="111"/>
+      <c r="AS4" s="111"/>
+      <c r="AT4" s="137"/>
+      <c r="AU4" s="177"/>
+      <c r="AV4" s="111"/>
+      <c r="AW4" s="111"/>
+      <c r="AX4" s="111"/>
+      <c r="AY4" s="111"/>
+      <c r="AZ4" s="111"/>
+      <c r="BA4" s="111"/>
+      <c r="BB4" s="111"/>
+      <c r="BC4" s="111"/>
+      <c r="BD4" s="111"/>
+      <c r="BE4" s="111"/>
+      <c r="BF4" s="111"/>
+      <c r="BG4" s="111"/>
+      <c r="BH4" s="111"/>
+      <c r="BI4" s="111"/>
+      <c r="BJ4" s="111"/>
+      <c r="BK4" s="111"/>
+      <c r="BL4" s="111"/>
+      <c r="BM4" s="111"/>
+      <c r="BN4" s="111"/>
+      <c r="BO4" s="111"/>
+      <c r="BP4" s="111"/>
+      <c r="BQ4" s="111"/>
+      <c r="BR4" s="111"/>
+      <c r="BS4" s="111"/>
+      <c r="BT4" s="111"/>
+      <c r="BU4" s="111"/>
+      <c r="BV4" s="178"/>
+      <c r="BW4" s="111"/>
+      <c r="BX4" s="111"/>
+      <c r="BY4" s="111"/>
+      <c r="BZ4" s="111"/>
+      <c r="CA4" s="111"/>
+      <c r="CB4" s="111"/>
+      <c r="CC4" s="111"/>
+      <c r="CD4" s="111"/>
+      <c r="CE4" s="111"/>
+      <c r="CF4" s="111"/>
+      <c r="CG4" s="111"/>
+      <c r="CH4" s="111"/>
+      <c r="CI4" s="111"/>
+      <c r="CJ4" s="111"/>
+      <c r="CK4" s="111"/>
+      <c r="CL4" s="111"/>
+      <c r="CM4" s="111"/>
+      <c r="CN4" s="111"/>
+      <c r="CO4" s="111"/>
+      <c r="CP4" s="111"/>
+      <c r="CQ4" s="111"/>
+      <c r="CR4" s="137"/>
+      <c r="CS4" s="186"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="187"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="134" t="s">
+      <c r="CY4" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="135"/>
-      <c r="DA4" s="136" t="s">
+      <c r="CZ4" s="165"/>
+      <c r="DA4" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="137"/>
-      <c r="DC4" s="137"/>
-      <c r="DD4" s="137"/>
-      <c r="DE4" s="137"/>
-      <c r="DF4" s="137"/>
-      <c r="DG4" s="135"/>
+      <c r="DB4" s="167"/>
+      <c r="DC4" s="167"/>
+      <c r="DD4" s="167"/>
+      <c r="DE4" s="167"/>
+      <c r="DF4" s="167"/>
+      <c r="DG4" s="165"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="134" t="s">
+      <c r="DJ4" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="135"/>
-      <c r="DL4" s="136" t="s">
+      <c r="DK4" s="165"/>
+      <c r="DL4" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="137"/>
-      <c r="DN4" s="137"/>
-      <c r="DO4" s="137"/>
-      <c r="DP4" s="137"/>
-      <c r="DQ4" s="137"/>
-      <c r="DR4" s="135"/>
+      <c r="DM4" s="167"/>
+      <c r="DN4" s="167"/>
+      <c r="DO4" s="167"/>
+      <c r="DP4" s="167"/>
+      <c r="DQ4" s="167"/>
+      <c r="DR4" s="165"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5695,112 +5716,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="178" t="str">
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="141" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO JUAN LUIS LONDOÑO I.E.D. LA SALLE</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="121"/>
-      <c r="S5" s="121"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="121"/>
-      <c r="W5" s="122"/>
-      <c r="X5" s="120"/>
-      <c r="Y5" s="121"/>
-      <c r="Z5" s="121"/>
-      <c r="AA5" s="121"/>
-      <c r="AB5" s="120"/>
-      <c r="AC5" s="121"/>
-      <c r="AD5" s="121"/>
-      <c r="AE5" s="121"/>
-      <c r="AF5" s="121"/>
-      <c r="AG5" s="121"/>
-      <c r="AH5" s="121"/>
-      <c r="AI5" s="121"/>
-      <c r="AJ5" s="121"/>
-      <c r="AK5" s="122"/>
-      <c r="AL5" s="120"/>
-      <c r="AM5" s="121"/>
-      <c r="AN5" s="121"/>
-      <c r="AO5" s="121"/>
-      <c r="AP5" s="121"/>
-      <c r="AQ5" s="121"/>
-      <c r="AR5" s="121"/>
-      <c r="AS5" s="121"/>
-      <c r="AT5" s="122"/>
-      <c r="AU5" s="120"/>
-      <c r="AV5" s="121"/>
-      <c r="AW5" s="121"/>
-      <c r="AX5" s="121"/>
-      <c r="AY5" s="121"/>
-      <c r="AZ5" s="121"/>
-      <c r="BA5" s="121"/>
-      <c r="BB5" s="121"/>
-      <c r="BC5" s="121"/>
-      <c r="BD5" s="121"/>
-      <c r="BE5" s="121"/>
-      <c r="BF5" s="121"/>
-      <c r="BG5" s="121"/>
-      <c r="BH5" s="121"/>
-      <c r="BI5" s="121"/>
-      <c r="BJ5" s="121"/>
-      <c r="BK5" s="121"/>
-      <c r="BL5" s="121"/>
-      <c r="BM5" s="121"/>
-      <c r="BN5" s="121"/>
-      <c r="BO5" s="121"/>
-      <c r="BP5" s="121"/>
-      <c r="BQ5" s="121"/>
-      <c r="BR5" s="121"/>
-      <c r="BS5" s="121"/>
-      <c r="BT5" s="121"/>
-      <c r="BU5" s="121"/>
-      <c r="BV5" s="120"/>
-      <c r="BW5" s="121"/>
-      <c r="BX5" s="121"/>
-      <c r="BY5" s="121"/>
-      <c r="BZ5" s="121"/>
-      <c r="CA5" s="121"/>
-      <c r="CB5" s="121"/>
-      <c r="CC5" s="121"/>
-      <c r="CD5" s="121"/>
-      <c r="CE5" s="121"/>
-      <c r="CF5" s="121"/>
-      <c r="CG5" s="121"/>
-      <c r="CH5" s="121"/>
-      <c r="CI5" s="121"/>
-      <c r="CJ5" s="121"/>
-      <c r="CK5" s="121"/>
-      <c r="CL5" s="121"/>
-      <c r="CM5" s="121"/>
-      <c r="CN5" s="121"/>
-      <c r="CO5" s="121"/>
-      <c r="CP5" s="121"/>
-      <c r="CQ5" s="121"/>
-      <c r="CR5" s="122"/>
-      <c r="CS5" s="120"/>
-      <c r="CT5" s="121"/>
-      <c r="CU5" s="121"/>
-      <c r="CV5" s="121"/>
-      <c r="CW5" s="122"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="132"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="135"/>
+      <c r="R5" s="135"/>
+      <c r="S5" s="135"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="135"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="138"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="135"/>
+      <c r="Z5" s="135"/>
+      <c r="AA5" s="135"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="135"/>
+      <c r="AD5" s="135"/>
+      <c r="AE5" s="135"/>
+      <c r="AF5" s="135"/>
+      <c r="AG5" s="135"/>
+      <c r="AH5" s="135"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
+      <c r="AK5" s="138"/>
+      <c r="AL5" s="134"/>
+      <c r="AM5" s="135"/>
+      <c r="AN5" s="135"/>
+      <c r="AO5" s="135"/>
+      <c r="AP5" s="135"/>
+      <c r="AQ5" s="135"/>
+      <c r="AR5" s="135"/>
+      <c r="AS5" s="135"/>
+      <c r="AT5" s="138"/>
+      <c r="AU5" s="134"/>
+      <c r="AV5" s="135"/>
+      <c r="AW5" s="135"/>
+      <c r="AX5" s="135"/>
+      <c r="AY5" s="135"/>
+      <c r="AZ5" s="135"/>
+      <c r="BA5" s="135"/>
+      <c r="BB5" s="135"/>
+      <c r="BC5" s="135"/>
+      <c r="BD5" s="135"/>
+      <c r="BE5" s="135"/>
+      <c r="BF5" s="135"/>
+      <c r="BG5" s="135"/>
+      <c r="BH5" s="135"/>
+      <c r="BI5" s="135"/>
+      <c r="BJ5" s="135"/>
+      <c r="BK5" s="135"/>
+      <c r="BL5" s="135"/>
+      <c r="BM5" s="135"/>
+      <c r="BN5" s="135"/>
+      <c r="BO5" s="135"/>
+      <c r="BP5" s="135"/>
+      <c r="BQ5" s="135"/>
+      <c r="BR5" s="135"/>
+      <c r="BS5" s="135"/>
+      <c r="BT5" s="135"/>
+      <c r="BU5" s="135"/>
+      <c r="BV5" s="134"/>
+      <c r="BW5" s="135"/>
+      <c r="BX5" s="135"/>
+      <c r="BY5" s="135"/>
+      <c r="BZ5" s="135"/>
+      <c r="CA5" s="135"/>
+      <c r="CB5" s="135"/>
+      <c r="CC5" s="135"/>
+      <c r="CD5" s="135"/>
+      <c r="CE5" s="135"/>
+      <c r="CF5" s="135"/>
+      <c r="CG5" s="135"/>
+      <c r="CH5" s="135"/>
+      <c r="CI5" s="135"/>
+      <c r="CJ5" s="135"/>
+      <c r="CK5" s="135"/>
+      <c r="CL5" s="135"/>
+      <c r="CM5" s="135"/>
+      <c r="CN5" s="135"/>
+      <c r="CO5" s="135"/>
+      <c r="CP5" s="135"/>
+      <c r="CQ5" s="135"/>
+      <c r="CR5" s="138"/>
+      <c r="CS5" s="134"/>
+      <c r="CT5" s="135"/>
+      <c r="CU5" s="135"/>
+      <c r="CV5" s="135"/>
+      <c r="CW5" s="138"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5829,11 +5850,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="163"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="109"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3415417</v>
@@ -5845,18 +5866,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="184" t="str">
+      <c r="G6" s="110" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 25</v>
       </c>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="129"/>
-      <c r="N6" s="129"/>
-      <c r="O6" s="180"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="112"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -6201,41 +6222,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="141" t="s">
+      <c r="CX6" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="142"/>
-      <c r="CZ6" s="142"/>
-      <c r="DA6" s="142"/>
-      <c r="DB6" s="142"/>
-      <c r="DC6" s="142"/>
-      <c r="DD6" s="142"/>
-      <c r="DE6" s="142"/>
-      <c r="DF6" s="142"/>
-      <c r="DG6" s="142"/>
-      <c r="DH6" s="142"/>
-      <c r="DI6" s="142"/>
-      <c r="DJ6" s="142"/>
-      <c r="DK6" s="142"/>
-      <c r="DL6" s="142"/>
-      <c r="DM6" s="142"/>
-      <c r="DN6" s="142"/>
-      <c r="DO6" s="142"/>
-      <c r="DP6" s="142"/>
-      <c r="DQ6" s="142"/>
-      <c r="DR6" s="142"/>
-      <c r="DS6" s="142"/>
-      <c r="DT6" s="142"/>
-      <c r="DU6" s="142"/>
-      <c r="DV6" s="142"/>
-      <c r="DW6" s="142"/>
+      <c r="CY6" s="169"/>
+      <c r="CZ6" s="169"/>
+      <c r="DA6" s="169"/>
+      <c r="DB6" s="169"/>
+      <c r="DC6" s="169"/>
+      <c r="DD6" s="169"/>
+      <c r="DE6" s="169"/>
+      <c r="DF6" s="169"/>
+      <c r="DG6" s="169"/>
+      <c r="DH6" s="169"/>
+      <c r="DI6" s="169"/>
+      <c r="DJ6" s="169"/>
+      <c r="DK6" s="169"/>
+      <c r="DL6" s="169"/>
+      <c r="DM6" s="169"/>
+      <c r="DN6" s="169"/>
+      <c r="DO6" s="169"/>
+      <c r="DP6" s="169"/>
+      <c r="DQ6" s="169"/>
+      <c r="DR6" s="169"/>
+      <c r="DS6" s="169"/>
+      <c r="DT6" s="169"/>
+      <c r="DU6" s="169"/>
+      <c r="DV6" s="169"/>
+      <c r="DW6" s="169"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="185" t="s">
+      <c r="A7" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="113"/>
-      <c r="C7" s="163"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46083</v>
@@ -6247,15 +6268,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46085</v>
       </c>
-      <c r="G7" s="181"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="161"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="182"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="114"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="115"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46083</v>
@@ -6600,58 +6621,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46379</v>
       </c>
-      <c r="CX7" s="143" t="s">
+      <c r="CX7" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="144"/>
-      <c r="CZ7" s="143" t="s">
+      <c r="CY7" s="171"/>
+      <c r="CZ7" s="170" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="142"/>
-      <c r="DB7" s="143" t="s">
+      <c r="DA7" s="169"/>
+      <c r="DB7" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="144"/>
-      <c r="DD7" s="143" t="s">
+      <c r="DC7" s="171"/>
+      <c r="DD7" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="144"/>
-      <c r="DF7" s="143" t="s">
+      <c r="DE7" s="171"/>
+      <c r="DF7" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="144"/>
-      <c r="DH7" s="143" t="s">
+      <c r="DG7" s="171"/>
+      <c r="DH7" s="170" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="144"/>
-      <c r="DJ7" s="143" t="s">
+      <c r="DI7" s="171"/>
+      <c r="DJ7" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="144"/>
-      <c r="DL7" s="143" t="s">
+      <c r="DK7" s="171"/>
+      <c r="DL7" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="144"/>
-      <c r="DN7" s="143" t="s">
+      <c r="DM7" s="171"/>
+      <c r="DN7" s="170" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="144"/>
-      <c r="DP7" s="143" t="s">
+      <c r="DO7" s="171"/>
+      <c r="DP7" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="144"/>
-      <c r="DR7" s="143" t="s">
+      <c r="DQ7" s="171"/>
+      <c r="DR7" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="144"/>
-      <c r="DT7" s="143" t="s">
+      <c r="DS7" s="171"/>
+      <c r="DT7" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="144"/>
-      <c r="DV7" s="145" t="s">
+      <c r="DU7" s="171"/>
+      <c r="DV7" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="142"/>
+      <c r="DW7" s="169"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -7150,7 +7171,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G44" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H44" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -7199,11 +7220,13 @@
         <v>38</v>
       </c>
       <c r="X9" s="35"/>
-      <c r="Y9" s="35" t="s">
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
+      <c r="AA9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB9" s="35"/>
       <c r="AC9" s="35"/>
       <c r="AD9" s="35"/>
@@ -7340,7 +7363,7 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="4"/>
@@ -7389,11 +7412,13 @@
         <v>38</v>
       </c>
       <c r="X10" s="35"/>
-      <c r="Y10" s="35" t="s">
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
+      <c r="AA10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
       <c r="AD10" s="35"/>
@@ -7530,7 +7555,7 @@
       </c>
       <c r="G11" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" si="4"/>
@@ -7579,11 +7604,13 @@
         <v>38</v>
       </c>
       <c r="X11" s="35"/>
-      <c r="Y11" s="35" t="s">
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
+      <c r="AA11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB11" s="35"/>
       <c r="AC11" s="35"/>
       <c r="AD11" s="35"/>
@@ -7728,7 +7755,7 @@
       </c>
       <c r="I12" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="6"/>
@@ -7752,7 +7779,7 @@
       </c>
       <c r="O12" s="43">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
@@ -7769,11 +7796,13 @@
         <v>38</v>
       </c>
       <c r="X12" s="35"/>
-      <c r="Y12" s="35" t="s">
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
+      <c r="AA12" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35"/>
@@ -7910,7 +7939,7 @@
       </c>
       <c r="G13" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" si="4"/>
@@ -7959,11 +7988,13 @@
         <v>38</v>
       </c>
       <c r="X13" s="35"/>
-      <c r="Y13" s="35" t="s">
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
+      <c r="AA13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB13" s="35"/>
       <c r="AC13" s="35"/>
       <c r="AD13" s="35"/>
@@ -8100,7 +8131,7 @@
       </c>
       <c r="G14" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="42">
         <f t="shared" si="4"/>
@@ -8149,11 +8180,13 @@
         <v>38</v>
       </c>
       <c r="X14" s="35"/>
-      <c r="Y14" s="35" t="s">
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
+      <c r="AA14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
       <c r="AD14" s="35"/>
@@ -8290,7 +8323,7 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="42">
         <f t="shared" si="4"/>
@@ -8339,11 +8372,13 @@
         <v>38</v>
       </c>
       <c r="X15" s="35"/>
-      <c r="Y15" s="35" t="s">
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
+      <c r="AA15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB15" s="35"/>
       <c r="AC15" s="35"/>
       <c r="AD15" s="35"/>
@@ -8480,7 +8515,7 @@
       </c>
       <c r="G16" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="42">
         <f t="shared" si="4"/>
@@ -8529,11 +8564,13 @@
         <v>38</v>
       </c>
       <c r="X16" s="35"/>
-      <c r="Y16" s="35" t="s">
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
+      <c r="AA16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
       <c r="AD16" s="35"/>
@@ -8670,7 +8707,7 @@
       </c>
       <c r="G17" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="42">
         <f t="shared" si="4"/>
@@ -8719,11 +8756,13 @@
         <v>38</v>
       </c>
       <c r="X17" s="35"/>
-      <c r="Y17" s="35" t="s">
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
+      <c r="AA17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB17" s="35"/>
       <c r="AC17" s="35"/>
       <c r="AD17" s="35"/>
@@ -8860,7 +8899,7 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="4"/>
@@ -8909,11 +8948,13 @@
         <v>38</v>
       </c>
       <c r="X18" s="35"/>
-      <c r="Y18" s="35" t="s">
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
+      <c r="AA18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
       <c r="AD18" s="35"/>
@@ -9050,7 +9091,7 @@
       </c>
       <c r="G19" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="42">
         <f t="shared" si="4"/>
@@ -9099,11 +9140,13 @@
         <v>38</v>
       </c>
       <c r="X19" s="35"/>
-      <c r="Y19" s="35" t="s">
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
+      <c r="AA19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB19" s="35"/>
       <c r="AC19" s="35"/>
       <c r="AD19" s="35"/>
@@ -9240,7 +9283,7 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="4"/>
@@ -9289,11 +9332,13 @@
         <v>38</v>
       </c>
       <c r="X20" s="35"/>
-      <c r="Y20" s="35" t="s">
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
+      <c r="AA20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB20" s="35"/>
       <c r="AC20" s="35"/>
       <c r="AD20" s="35"/>
@@ -9430,7 +9475,7 @@
       </c>
       <c r="G21" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="4"/>
@@ -9479,11 +9524,13 @@
         <v>38</v>
       </c>
       <c r="X21" s="35"/>
-      <c r="Y21" s="35" t="s">
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="35"/>
+      <c r="AA21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB21" s="35"/>
       <c r="AC21" s="35"/>
       <c r="AD21" s="35"/>
@@ -9618,7 +9665,7 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="4"/>
@@ -9667,11 +9714,13 @@
         <v>38</v>
       </c>
       <c r="X22" s="35"/>
-      <c r="Y22" s="35" t="s">
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
+      <c r="AA22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB22" s="35"/>
       <c r="AC22" s="35"/>
       <c r="AD22" s="35"/>
@@ -9806,7 +9855,7 @@
       </c>
       <c r="G23" s="41">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="42">
         <f t="shared" si="4"/>
@@ -9838,7 +9887,7 @@
       </c>
       <c r="O23" s="43">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
@@ -9855,11 +9904,13 @@
         <v>38</v>
       </c>
       <c r="X23" s="35"/>
-      <c r="Y23" s="35" t="s">
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="35"/>
+      <c r="AA23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB23" s="35"/>
       <c r="AC23" s="35"/>
       <c r="AD23" s="35"/>
@@ -9994,7 +10045,7 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="4"/>
@@ -10043,11 +10094,13 @@
         <v>38</v>
       </c>
       <c r="X24" s="35"/>
-      <c r="Y24" s="35" t="s">
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
+      <c r="AA24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB24" s="35"/>
       <c r="AC24" s="35"/>
       <c r="AD24" s="35"/>
@@ -10182,7 +10235,7 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="42">
         <f t="shared" si="4"/>
@@ -10231,11 +10284,13 @@
         <v>38</v>
       </c>
       <c r="X25" s="35"/>
-      <c r="Y25" s="35" t="s">
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
+      <c r="AA25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB25" s="35"/>
       <c r="AC25" s="35"/>
       <c r="AD25" s="35"/>
@@ -10370,7 +10425,7 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="4"/>
@@ -10419,11 +10474,13 @@
         <v>38</v>
       </c>
       <c r="X26" s="35"/>
-      <c r="Y26" s="35" t="s">
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
+      <c r="AA26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB26" s="35"/>
       <c r="AC26" s="35"/>
       <c r="AD26" s="35"/>
@@ -10558,7 +10615,7 @@
       </c>
       <c r="G27" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="42">
         <f t="shared" si="4"/>
@@ -10607,11 +10664,13 @@
         <v>38</v>
       </c>
       <c r="X27" s="35"/>
-      <c r="Y27" s="35" t="s">
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
+      <c r="AA27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB27" s="35"/>
       <c r="AC27" s="35"/>
       <c r="AD27" s="35"/>
@@ -10746,15 +10805,15 @@
       </c>
       <c r="G28" s="41">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="42">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="42">
         <f t="shared" si="6"/>
@@ -10778,7 +10837,7 @@
       </c>
       <c r="O28" s="43">
         <f t="shared" si="11"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
@@ -10795,11 +10854,13 @@
         <v>38</v>
       </c>
       <c r="X28" s="35"/>
-      <c r="Y28" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB28" s="35"/>
       <c r="AC28" s="35"/>
       <c r="AD28" s="35"/>
@@ -10934,7 +10995,7 @@
       </c>
       <c r="G29" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="42">
         <f t="shared" si="4"/>
@@ -10983,11 +11044,13 @@
         <v>38</v>
       </c>
       <c r="X29" s="35"/>
-      <c r="Y29" s="35" t="s">
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="35"/>
+      <c r="AA29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB29" s="35"/>
       <c r="AC29" s="35"/>
       <c r="AD29" s="35"/>
@@ -11122,7 +11185,7 @@
       </c>
       <c r="G30" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="42">
         <f t="shared" si="4"/>
@@ -11171,11 +11234,13 @@
         <v>38</v>
       </c>
       <c r="X30" s="35"/>
-      <c r="Y30" s="35" t="s">
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
+      <c r="AA30" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB30" s="35"/>
       <c r="AC30" s="35"/>
       <c r="AD30" s="35"/>
@@ -11310,7 +11375,7 @@
       </c>
       <c r="G31" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="42">
         <f t="shared" si="4"/>
@@ -11359,11 +11424,13 @@
         <v>38</v>
       </c>
       <c r="X31" s="35"/>
-      <c r="Y31" s="35" t="s">
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
+      <c r="AA31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB31" s="35"/>
       <c r="AC31" s="35"/>
       <c r="AD31" s="35"/>
@@ -11497,7 +11564,7 @@
       </c>
       <c r="G32" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="4"/>
@@ -11546,11 +11613,13 @@
         <v>38</v>
       </c>
       <c r="X32" s="35"/>
-      <c r="Y32" s="35" t="s">
+      <c r="Y32" s="35"/>
+      <c r="Z32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z32" s="35"/>
-      <c r="AA32" s="35"/>
+      <c r="AA32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB32" s="35"/>
       <c r="AC32" s="35"/>
       <c r="AD32" s="35"/>
@@ -11680,7 +11749,7 @@
       </c>
       <c r="F33" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>CON FALTAS</v>
+        <v>REVISAR FALTAS</v>
       </c>
       <c r="G33" s="41">
         <f t="shared" si="3"/>
@@ -11692,7 +11761,7 @@
       </c>
       <c r="I33" s="42">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="42">
         <f t="shared" si="6"/>
@@ -11716,7 +11785,7 @@
       </c>
       <c r="O33" s="43">
         <f t="shared" si="11"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
@@ -11733,11 +11802,13 @@
         <v>38</v>
       </c>
       <c r="X33" s="35"/>
-      <c r="Y33" s="35" t="s">
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="Z33" s="35"/>
-      <c r="AA33" s="35"/>
+      <c r="AA33" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AB33" s="35"/>
       <c r="AC33" s="35"/>
       <c r="AD33" s="35"/>
@@ -11871,7 +11942,7 @@
       </c>
       <c r="G34" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="42">
         <f t="shared" si="4"/>
@@ -11920,11 +11991,13 @@
         <v>38</v>
       </c>
       <c r="X34" s="35"/>
-      <c r="Y34" s="35" t="s">
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z34" s="35"/>
-      <c r="AA34" s="35"/>
+      <c r="AA34" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB34" s="35"/>
       <c r="AC34" s="35"/>
       <c r="AD34" s="35"/>
@@ -12058,7 +12131,7 @@
       </c>
       <c r="G35" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="42">
         <f t="shared" si="4"/>
@@ -12107,11 +12180,13 @@
         <v>38</v>
       </c>
       <c r="X35" s="35"/>
-      <c r="Y35" s="35" t="s">
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z35" s="35"/>
-      <c r="AA35" s="35"/>
+      <c r="AA35" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB35" s="35"/>
       <c r="AC35" s="35"/>
       <c r="AD35" s="35"/>
@@ -12245,7 +12320,7 @@
       </c>
       <c r="G36" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H36" s="42">
         <f t="shared" si="4"/>
@@ -12294,11 +12369,13 @@
         <v>38</v>
       </c>
       <c r="X36" s="35"/>
-      <c r="Y36" s="35" t="s">
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
+      <c r="AA36" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB36" s="35"/>
       <c r="AC36" s="35"/>
       <c r="AD36" s="35"/>
@@ -12432,7 +12509,7 @@
       </c>
       <c r="G37" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" s="42">
         <f t="shared" si="4"/>
@@ -12481,11 +12558,13 @@
         <v>38</v>
       </c>
       <c r="X37" s="35"/>
-      <c r="Y37" s="35" t="s">
+      <c r="Y37" s="35"/>
+      <c r="Z37" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z37" s="35"/>
-      <c r="AA37" s="35"/>
+      <c r="AA37" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB37" s="35"/>
       <c r="AC37" s="35"/>
       <c r="AD37" s="35"/>
@@ -12619,7 +12698,7 @@
       </c>
       <c r="G38" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H38" s="42">
         <f t="shared" si="4"/>
@@ -12668,11 +12747,13 @@
         <v>38</v>
       </c>
       <c r="X38" s="35"/>
-      <c r="Y38" s="35" t="s">
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z38" s="35"/>
-      <c r="AA38" s="35"/>
+      <c r="AA38" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB38" s="35"/>
       <c r="AC38" s="35"/>
       <c r="AD38" s="35"/>
@@ -12806,7 +12887,7 @@
       </c>
       <c r="G39" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H39" s="42">
         <f t="shared" si="4"/>
@@ -12855,11 +12936,13 @@
         <v>38</v>
       </c>
       <c r="X39" s="35"/>
-      <c r="Y39" s="35" t="s">
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z39" s="35"/>
-      <c r="AA39" s="35"/>
+      <c r="AA39" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB39" s="35"/>
       <c r="AC39" s="35"/>
       <c r="AD39" s="35"/>
@@ -12993,7 +13076,7 @@
       </c>
       <c r="G40" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" s="42">
         <f t="shared" si="4"/>
@@ -13042,11 +13125,13 @@
         <v>38</v>
       </c>
       <c r="X40" s="35"/>
-      <c r="Y40" s="35" t="s">
+      <c r="Y40" s="35"/>
+      <c r="Z40" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z40" s="35"/>
-      <c r="AA40" s="35"/>
+      <c r="AA40" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB40" s="35"/>
       <c r="AC40" s="35"/>
       <c r="AD40" s="35"/>
@@ -13180,7 +13265,7 @@
       </c>
       <c r="G41" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H41" s="42">
         <f t="shared" si="4"/>
@@ -13229,11 +13314,13 @@
         <v>38</v>
       </c>
       <c r="X41" s="35"/>
-      <c r="Y41" s="35" t="s">
+      <c r="Y41" s="35"/>
+      <c r="Z41" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z41" s="35"/>
-      <c r="AA41" s="35"/>
+      <c r="AA41" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB41" s="35"/>
       <c r="AC41" s="35"/>
       <c r="AD41" s="35"/>
@@ -13367,7 +13454,7 @@
       </c>
       <c r="G42" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" s="42">
         <f t="shared" si="4"/>
@@ -13416,11 +13503,13 @@
         <v>38</v>
       </c>
       <c r="X42" s="35"/>
-      <c r="Y42" s="35" t="s">
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z42" s="35"/>
-      <c r="AA42" s="35"/>
+      <c r="AA42" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB42" s="35"/>
       <c r="AC42" s="35"/>
       <c r="AD42" s="35"/>
@@ -13554,7 +13643,7 @@
       </c>
       <c r="G43" s="41">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43" s="42">
         <f t="shared" si="4"/>
@@ -13603,11 +13692,13 @@
         <v>38</v>
       </c>
       <c r="X43" s="35"/>
-      <c r="Y43" s="35" t="s">
+      <c r="Y43" s="35"/>
+      <c r="Z43" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z43" s="35"/>
-      <c r="AA43" s="35"/>
+      <c r="AA43" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB43" s="35"/>
       <c r="AC43" s="35"/>
       <c r="AD43" s="35"/>
@@ -13741,7 +13832,7 @@
       </c>
       <c r="G44" s="89">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H44" s="90">
         <f t="shared" si="4"/>
@@ -13790,11 +13881,13 @@
         <v>38</v>
       </c>
       <c r="X44" s="35"/>
-      <c r="Y44" s="35" t="s">
+      <c r="Y44" s="35"/>
+      <c r="Z44" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z44" s="35"/>
-      <c r="AA44" s="35"/>
+      <c r="AA44" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB44" s="35"/>
       <c r="AC44" s="35"/>
       <c r="AD44" s="35"/>
@@ -13925,7 +14018,7 @@
       <c r="F45" s="87"/>
       <c r="G45" s="89">
         <f t="shared" ref="G45:G49" si="49">COUNTIF(P45:CR45,"A")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" s="90">
         <f t="shared" ref="H45:H49" si="50">COUNTIF(P45:CR45,"CE")</f>
@@ -13974,11 +14067,13 @@
         <v>38</v>
       </c>
       <c r="X45" s="35"/>
-      <c r="Y45" s="35" t="s">
+      <c r="Y45" s="35"/>
+      <c r="Z45" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="35"/>
+      <c r="AA45" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB45" s="35"/>
       <c r="AC45" s="35"/>
       <c r="AD45" s="35"/>
@@ -14103,7 +14198,7 @@
       <c r="F46" s="87"/>
       <c r="G46" s="89">
         <f t="shared" si="49"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" s="90">
         <f t="shared" si="50"/>
@@ -14152,11 +14247,13 @@
         <v>38</v>
       </c>
       <c r="X46" s="35"/>
-      <c r="Y46" s="35" t="s">
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="35"/>
+      <c r="AA46" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB46" s="35"/>
       <c r="AC46" s="35"/>
       <c r="AD46" s="35"/>
@@ -14281,7 +14378,7 @@
       <c r="F47" s="87"/>
       <c r="G47" s="89">
         <f t="shared" si="49"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H47" s="90">
         <f t="shared" si="50"/>
@@ -14330,11 +14427,13 @@
         <v>38</v>
       </c>
       <c r="X47" s="35"/>
-      <c r="Y47" s="35" t="s">
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="35"/>
+      <c r="AA47" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB47" s="35"/>
       <c r="AC47" s="35"/>
       <c r="AD47" s="35"/>
@@ -14459,7 +14558,7 @@
       <c r="F48" s="87"/>
       <c r="G48" s="89">
         <f t="shared" si="49"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="90">
         <f t="shared" si="50"/>
@@ -14491,7 +14590,7 @@
       </c>
       <c r="O48" s="95">
         <f t="shared" si="57"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P48" s="96"/>
       <c r="Q48" s="88"/>
@@ -14508,11 +14607,13 @@
         <v>38</v>
       </c>
       <c r="X48" s="35"/>
-      <c r="Y48" s="35" t="s">
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z48" s="35"/>
-      <c r="AA48" s="35"/>
+      <c r="AA48" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB48" s="35"/>
       <c r="AC48" s="35"/>
       <c r="AD48" s="35"/>
@@ -14637,7 +14738,7 @@
       <c r="F49" s="87"/>
       <c r="G49" s="89">
         <f t="shared" si="49"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H49" s="90">
         <f t="shared" si="50"/>
@@ -14686,11 +14787,13 @@
         <v>38</v>
       </c>
       <c r="X49" s="35"/>
-      <c r="Y49" s="35" t="s">
+      <c r="Y49" s="35"/>
+      <c r="Z49" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="35"/>
+      <c r="AA49" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AB49" s="35"/>
       <c r="AC49" s="35"/>
       <c r="AD49" s="35"/>
@@ -14799,20 +14902,20 @@
       <c r="D50" s="76"/>
       <c r="E50" s="76"/>
       <c r="F50" s="75"/>
-      <c r="G50" s="186" t="s">
+      <c r="G50" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="H50" s="187"/>
-      <c r="I50" s="187"/>
-      <c r="J50" s="187"/>
-      <c r="K50" s="187"/>
-      <c r="L50" s="187"/>
-      <c r="M50" s="188"/>
-      <c r="N50" s="189" t="str">
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="118"/>
+      <c r="L50" s="118"/>
+      <c r="M50" s="119"/>
+      <c r="N50" s="120" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O50" s="190"/>
+      <c r="O50" s="121"/>
       <c r="P50" s="94">
         <f t="shared" ref="P50:AU50" si="58">COUNTIF(P9:P44,"A")</f>
         <v>0</v>
@@ -14851,15 +14954,15 @@
       </c>
       <c r="Y50" s="44">
         <f t="shared" si="58"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="44">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AA50" s="44">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB50" s="44">
         <f t="shared" si="58"/>
@@ -15197,20 +15300,20 @@
       <c r="D51" s="76"/>
       <c r="E51" s="76"/>
       <c r="F51" s="75"/>
-      <c r="G51" s="156" t="s">
+      <c r="G51" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="147"/>
-      <c r="I51" s="147"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="147"/>
-      <c r="L51" s="147"/>
-      <c r="M51" s="148"/>
-      <c r="N51" s="149" t="str">
+      <c r="H51" s="150"/>
+      <c r="I51" s="150"/>
+      <c r="J51" s="150"/>
+      <c r="K51" s="150"/>
+      <c r="L51" s="150"/>
+      <c r="M51" s="151"/>
+      <c r="N51" s="152" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O51" s="150"/>
+      <c r="O51" s="153"/>
       <c r="P51" s="44">
         <f t="shared" ref="P51:AU51" si="62">COUNTIF(P9:P44,"CE")</f>
         <v>0</v>
@@ -15253,7 +15356,7 @@
       </c>
       <c r="Z51" s="44">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="44">
         <f t="shared" si="62"/>
@@ -15595,20 +15698,20 @@
       <c r="D52" s="76"/>
       <c r="E52" s="76"/>
       <c r="F52" s="75"/>
-      <c r="G52" s="157" t="s">
+      <c r="G52" s="158" t="s">
         <v>12</v>
       </c>
-      <c r="H52" s="147"/>
-      <c r="I52" s="147"/>
-      <c r="J52" s="147"/>
-      <c r="K52" s="147"/>
-      <c r="L52" s="147"/>
-      <c r="M52" s="148"/>
-      <c r="N52" s="149" t="str">
+      <c r="H52" s="150"/>
+      <c r="I52" s="150"/>
+      <c r="J52" s="150"/>
+      <c r="K52" s="150"/>
+      <c r="L52" s="150"/>
+      <c r="M52" s="151"/>
+      <c r="N52" s="152" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O52" s="150"/>
+      <c r="O52" s="153"/>
       <c r="P52" s="44">
         <f t="shared" ref="P52:AU52" si="66">COUNTIF(P9:P44,"SE")</f>
         <v>0</v>
@@ -15647,15 +15750,15 @@
       </c>
       <c r="Y52" s="44">
         <f t="shared" si="66"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA52" s="44">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" s="44">
         <f t="shared" si="66"/>
@@ -15993,20 +16096,20 @@
       <c r="D53" s="76"/>
       <c r="E53" s="76"/>
       <c r="F53" s="45"/>
-      <c r="G53" s="158" t="s">
+      <c r="G53" s="159" t="s">
         <v>60</v>
       </c>
-      <c r="H53" s="147"/>
-      <c r="I53" s="147"/>
-      <c r="J53" s="147"/>
-      <c r="K53" s="147"/>
-      <c r="L53" s="147"/>
-      <c r="M53" s="148"/>
-      <c r="N53" s="149" t="str">
+      <c r="H53" s="150"/>
+      <c r="I53" s="150"/>
+      <c r="J53" s="150"/>
+      <c r="K53" s="150"/>
+      <c r="L53" s="150"/>
+      <c r="M53" s="151"/>
+      <c r="N53" s="152" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O53" s="150"/>
+      <c r="O53" s="153"/>
       <c r="P53" s="44">
         <f t="shared" ref="P53:AU53" si="70">COUNTIF(P9:P44,"INC")</f>
         <v>0</v>
@@ -16391,20 +16494,20 @@
       <c r="D54" s="76"/>
       <c r="E54" s="76"/>
       <c r="F54" s="75"/>
-      <c r="G54" s="153" t="s">
+      <c r="G54" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="H54" s="147"/>
-      <c r="I54" s="147"/>
-      <c r="J54" s="147"/>
-      <c r="K54" s="147"/>
-      <c r="L54" s="147"/>
-      <c r="M54" s="148"/>
-      <c r="N54" s="149" t="str">
+      <c r="H54" s="150"/>
+      <c r="I54" s="150"/>
+      <c r="J54" s="150"/>
+      <c r="K54" s="150"/>
+      <c r="L54" s="150"/>
+      <c r="M54" s="151"/>
+      <c r="N54" s="152" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O54" s="150"/>
+      <c r="O54" s="153"/>
       <c r="P54" s="44">
         <f t="shared" ref="P54:AU54" si="74">COUNTIF(P9:P44,"LIC")</f>
         <v>0</v>
@@ -16789,20 +16892,20 @@
       <c r="D55" s="76"/>
       <c r="E55" s="76"/>
       <c r="F55" s="75"/>
-      <c r="G55" s="146" t="s">
+      <c r="G55" s="161" t="s">
         <v>62</v>
       </c>
-      <c r="H55" s="147"/>
-      <c r="I55" s="147"/>
-      <c r="J55" s="147"/>
-      <c r="K55" s="147"/>
-      <c r="L55" s="147"/>
-      <c r="M55" s="148"/>
-      <c r="N55" s="149" t="str">
+      <c r="H55" s="150"/>
+      <c r="I55" s="150"/>
+      <c r="J55" s="150"/>
+      <c r="K55" s="150"/>
+      <c r="L55" s="150"/>
+      <c r="M55" s="151"/>
+      <c r="N55" s="152" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O55" s="150"/>
+      <c r="O55" s="153"/>
       <c r="P55" s="44">
         <f t="shared" ref="P55:AU55" si="78">COUNTIF(P9:P44,"CLM")</f>
         <v>0</v>
@@ -17187,20 +17290,20 @@
       <c r="D56" s="76"/>
       <c r="E56" s="76"/>
       <c r="F56" s="75"/>
-      <c r="G56" s="151" t="s">
+      <c r="G56" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="H56" s="147"/>
-      <c r="I56" s="147"/>
-      <c r="J56" s="147"/>
-      <c r="K56" s="147"/>
-      <c r="L56" s="147"/>
-      <c r="M56" s="148"/>
-      <c r="N56" s="149" t="str">
+      <c r="H56" s="150"/>
+      <c r="I56" s="150"/>
+      <c r="J56" s="150"/>
+      <c r="K56" s="150"/>
+      <c r="L56" s="150"/>
+      <c r="M56" s="151"/>
+      <c r="N56" s="152" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O56" s="150"/>
+      <c r="O56" s="153"/>
       <c r="P56" s="44">
         <f t="shared" ref="P56:AU56" si="82">COUNTIF(P9:P44,"SFF")</f>
         <v>0</v>
@@ -17585,20 +17688,20 @@
       <c r="D57" s="76"/>
       <c r="E57" s="76"/>
       <c r="F57" s="75"/>
-      <c r="G57" s="152" t="s">
+      <c r="G57" s="163" t="s">
         <v>64</v>
       </c>
-      <c r="H57" s="147"/>
-      <c r="I57" s="147"/>
-      <c r="J57" s="147"/>
-      <c r="K57" s="147"/>
-      <c r="L57" s="147"/>
-      <c r="M57" s="148"/>
-      <c r="N57" s="149" t="str">
+      <c r="H57" s="150"/>
+      <c r="I57" s="150"/>
+      <c r="J57" s="150"/>
+      <c r="K57" s="150"/>
+      <c r="L57" s="150"/>
+      <c r="M57" s="151"/>
+      <c r="N57" s="152" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O57" s="150"/>
+      <c r="O57" s="153"/>
       <c r="P57" s="44">
         <f t="shared" ref="P57:AU57" si="86">COUNTIF(P9:P44,"RET")</f>
         <v>0</v>
@@ -42939,11 +43042,65 @@
   </sheetData>
   <autoFilter ref="A8:DW57" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:O7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G50:M50"/>
-    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="AL1:AT1"/>
+    <mergeCell ref="AU1:BU1"/>
+    <mergeCell ref="BV1:CR1"/>
+    <mergeCell ref="AL3:AT3"/>
+    <mergeCell ref="CS1:CW5"/>
+    <mergeCell ref="AU2:BU2"/>
+    <mergeCell ref="BV2:CR2"/>
+    <mergeCell ref="BV3:CR3"/>
+    <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="CY1:DG1"/>
+    <mergeCell ref="CY2:DG2"/>
+    <mergeCell ref="CY4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="AU3:BU3"/>
+    <mergeCell ref="AU4:BU5"/>
+    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="DJ4:DK4"/>
+    <mergeCell ref="DL4:DR4"/>
+    <mergeCell ref="CX6:DW6"/>
+    <mergeCell ref="DL7:DM7"/>
+    <mergeCell ref="DN7:DO7"/>
+    <mergeCell ref="DP7:DQ7"/>
+    <mergeCell ref="DR7:DS7"/>
+    <mergeCell ref="DT7:DU7"/>
+    <mergeCell ref="DV7:DW7"/>
+    <mergeCell ref="CX7:CY7"/>
+    <mergeCell ref="CZ7:DA7"/>
+    <mergeCell ref="DB7:DC7"/>
+    <mergeCell ref="DD7:DE7"/>
+    <mergeCell ref="DF7:DG7"/>
+    <mergeCell ref="DH7:DI7"/>
+    <mergeCell ref="DJ7:DK7"/>
+    <mergeCell ref="G55:M55"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="G56:M56"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="G57:M57"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="G54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="G51:M51"/>
+    <mergeCell ref="G52:M52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="G53:M53"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="X1:AA1"/>
     <mergeCell ref="AB1:AK1"/>
     <mergeCell ref="AB2:AK2"/>
@@ -42960,425 +43117,371 @@
     <mergeCell ref="AB3:AK3"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="G1:O1"/>
-    <mergeCell ref="G54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="G51:M51"/>
-    <mergeCell ref="G52:M52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="G53:M53"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="G55:M55"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="G56:M56"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="G57:M57"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="DJ4:DK4"/>
-    <mergeCell ref="DL4:DR4"/>
-    <mergeCell ref="CX6:DW6"/>
-    <mergeCell ref="DL7:DM7"/>
-    <mergeCell ref="DN7:DO7"/>
-    <mergeCell ref="DP7:DQ7"/>
-    <mergeCell ref="DR7:DS7"/>
-    <mergeCell ref="DT7:DU7"/>
-    <mergeCell ref="DV7:DW7"/>
-    <mergeCell ref="CX7:CY7"/>
-    <mergeCell ref="CZ7:DA7"/>
-    <mergeCell ref="DB7:DC7"/>
-    <mergeCell ref="DD7:DE7"/>
-    <mergeCell ref="DF7:DG7"/>
-    <mergeCell ref="DH7:DI7"/>
-    <mergeCell ref="DJ7:DK7"/>
-    <mergeCell ref="CY1:DG1"/>
-    <mergeCell ref="CY2:DG2"/>
-    <mergeCell ref="CY4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="AU3:BU3"/>
-    <mergeCell ref="AU4:BU5"/>
-    <mergeCell ref="BV4:CR5"/>
-    <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:BU1"/>
-    <mergeCell ref="BV1:CR1"/>
-    <mergeCell ref="AL3:AT3"/>
-    <mergeCell ref="CS1:CW5"/>
-    <mergeCell ref="AU2:BU2"/>
-    <mergeCell ref="BV2:CR2"/>
-    <mergeCell ref="BV3:CR3"/>
-    <mergeCell ref="AL2:AT2"/>
-    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:O7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G50:M50"/>
+    <mergeCell ref="N50:O50"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E49">
-    <cfRule type="containsText" dxfId="99" priority="1" operator="containsText" text="RETIRADO">
+    <cfRule type="containsText" dxfId="88" priority="1" operator="containsText" text="RETIRADO">
       <formula>NOT(ISERROR(SEARCH(("RETIRADO"),(E9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E49">
-    <cfRule type="containsText" dxfId="98" priority="2" operator="containsText" text="EN FORMACIÓN">
+    <cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="EN FORMACIÓN">
       <formula>NOT(ISERROR(SEARCH(("EN FORMACIÓN"),(E9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F49">
-    <cfRule type="cellIs" dxfId="97" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="3" operator="equal">
       <formula>"REVISAR FALTAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F49">
-    <cfRule type="cellIs" dxfId="96" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="4" operator="equal">
       <formula>"CON FALTAS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F49">
-    <cfRule type="cellIs" dxfId="95" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="5" operator="equal">
       <formula>"FALTAS INTERMITENTES"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="94" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="6" operator="equal">
       <formula>"RET"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="93" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="7" operator="equal">
       <formula>"SFF"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="92" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="8" operator="equal">
       <formula>"CLM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="91" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="9" operator="equal">
       <formula>"LIC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="90" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="10" operator="equal">
       <formula>"INC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="89" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="11" operator="equal">
       <formula>"SE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="88" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="12" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:N8">
-    <cfRule type="cellIs" dxfId="87" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="13" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P50:CW57 G9:O49">
-    <cfRule type="cellIs" dxfId="86" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="14" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="85" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="15" operator="equal">
       <formula>"RET"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="84" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="16" operator="equal">
       <formula>"SFF"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="83" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="17" operator="equal">
       <formula>"CLM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="82" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="18" operator="equal">
       <formula>"LIC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="81" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="19" operator="equal">
       <formula>"INC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="80" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="20" operator="equal">
       <formula>"SE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="79" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="21" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N50:O57">
-    <cfRule type="cellIs" dxfId="78" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="22" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O49">
-    <cfRule type="cellIs" dxfId="77" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="23" operator="greaterThan">
       <formula>0.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O49">
-    <cfRule type="cellIs" dxfId="76" priority="24" operator="between">
+    <cfRule type="cellIs" dxfId="65" priority="24" operator="between">
       <formula>0.21</formula>
       <formula>0.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O49">
-    <cfRule type="cellIs" dxfId="75" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="64" priority="25" operator="between">
       <formula>0</formula>
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="74" priority="26" operator="containsText" text="dic">
+    <cfRule type="containsText" dxfId="63" priority="26" operator="containsText" text="dic">
       <formula>NOT(ISERROR(SEARCH(("dic"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="73" priority="27" operator="containsText" text="oct">
+    <cfRule type="containsText" dxfId="62" priority="27" operator="containsText" text="oct">
       <formula>NOT(ISERROR(SEARCH(("oct"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="72" priority="28" operator="containsText" text="ago">
+    <cfRule type="containsText" dxfId="61" priority="28" operator="containsText" text="ago">
       <formula>NOT(ISERROR(SEARCH(("ago"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="71" priority="29" operator="containsText" text="jun">
+    <cfRule type="containsText" dxfId="60" priority="29" operator="containsText" text="jun">
       <formula>NOT(ISERROR(SEARCH(("jun"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="70" priority="30" operator="containsText" text="abr">
+    <cfRule type="containsText" dxfId="59" priority="30" operator="containsText" text="abr">
       <formula>NOT(ISERROR(SEARCH(("abr"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="69" priority="31" operator="containsText" text="feb">
+    <cfRule type="containsText" dxfId="58" priority="31" operator="containsText" text="feb">
       <formula>NOT(ISERROR(SEARCH(("feb"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="68" priority="32" operator="containsText" text="jul">
+    <cfRule type="containsText" dxfId="57" priority="32" operator="containsText" text="jul">
       <formula>NOT(ISERROR(SEARCH(("jul"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="67" priority="33" operator="containsText" text="nov">
+    <cfRule type="containsText" dxfId="56" priority="33" operator="containsText" text="nov">
       <formula>NOT(ISERROR(SEARCH(("nov"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="66" priority="34" operator="containsText" text="sep">
+    <cfRule type="containsText" dxfId="55" priority="34" operator="containsText" text="sep">
       <formula>NOT(ISERROR(SEARCH(("sep"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="65" priority="35" operator="containsText" text="may">
+    <cfRule type="containsText" dxfId="54" priority="35" operator="containsText" text="may">
       <formula>NOT(ISERROR(SEARCH(("may"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="64" priority="36" operator="containsText" text="mar">
+    <cfRule type="containsText" dxfId="53" priority="36" operator="containsText" text="mar">
       <formula>NOT(ISERROR(SEARCH(("mar"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:CW6">
-    <cfRule type="containsText" dxfId="63" priority="37" operator="containsText" text="ene">
+    <cfRule type="containsText" dxfId="52" priority="37" operator="containsText" text="ene">
       <formula>NOT(ISERROR(SEARCH(("ene"),(P6))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:CW8">
-    <cfRule type="cellIs" dxfId="62" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="38" operator="equal">
       <formula>"Fest"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:CW8">
-    <cfRule type="cellIs" dxfId="61" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="39" operator="equal">
       <formula>"Rec"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:CW8">
-    <cfRule type="cellIs" dxfId="60" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="40" operator="equal">
       <formula>"S.S."</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="59" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="41" operator="equal">
       <formula>"RET"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="58" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="42" operator="equal">
       <formula>"SFF"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="57" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="43" operator="equal">
       <formula>"CLM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="56" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="44" operator="equal">
       <formula>"LIC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="55" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="45" operator="equal">
       <formula>"INC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="54" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="46" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="53" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="47" operator="equal">
       <formula>"SE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:CW49">
-    <cfRule type="cellIs" dxfId="52" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="48" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="51" priority="49" operator="containsText" text="dic">
+    <cfRule type="containsText" dxfId="40" priority="49" operator="containsText" text="dic">
       <formula>NOT(ISERROR(SEARCH(("dic"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="50" priority="50" operator="containsText" text="oct">
+    <cfRule type="containsText" dxfId="39" priority="50" operator="containsText" text="oct">
       <formula>NOT(ISERROR(SEARCH(("oct"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="49" priority="51" operator="containsText" text="ago">
+    <cfRule type="containsText" dxfId="38" priority="51" operator="containsText" text="ago">
       <formula>NOT(ISERROR(SEARCH(("ago"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="48" priority="52" operator="containsText" text="jun">
+    <cfRule type="containsText" dxfId="37" priority="52" operator="containsText" text="jun">
       <formula>NOT(ISERROR(SEARCH(("jun"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="47" priority="53" operator="containsText" text="abr">
+    <cfRule type="containsText" dxfId="36" priority="53" operator="containsText" text="abr">
       <formula>NOT(ISERROR(SEARCH(("abr"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="46" priority="54" operator="containsText" text="feb">
+    <cfRule type="containsText" dxfId="35" priority="54" operator="containsText" text="feb">
       <formula>NOT(ISERROR(SEARCH(("feb"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="45" priority="55" operator="containsText" text="jul">
+    <cfRule type="containsText" dxfId="34" priority="55" operator="containsText" text="jul">
       <formula>NOT(ISERROR(SEARCH(("jul"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="44" priority="56" operator="containsText" text="nov">
+    <cfRule type="containsText" dxfId="33" priority="56" operator="containsText" text="nov">
       <formula>NOT(ISERROR(SEARCH(("nov"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="43" priority="57" operator="containsText" text="sep">
+    <cfRule type="containsText" dxfId="32" priority="57" operator="containsText" text="sep">
       <formula>NOT(ISERROR(SEARCH(("sep"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="42" priority="58" operator="containsText" text="may">
+    <cfRule type="containsText" dxfId="31" priority="58" operator="containsText" text="may">
       <formula>NOT(ISERROR(SEARCH(("may"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="41" priority="59" operator="containsText" text="mar">
+    <cfRule type="containsText" dxfId="30" priority="59" operator="containsText" text="mar">
       <formula>NOT(ISERROR(SEARCH(("mar"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX7 CZ7 DB7 DD7 DF7 DH7 DJ7 DL7 DN7 DP7 DR7 DT7">
-    <cfRule type="containsText" dxfId="40" priority="60" operator="containsText" text="ene">
+    <cfRule type="containsText" dxfId="29" priority="60" operator="containsText" text="ene">
       <formula>NOT(ISERROR(SEARCH(("ene"),(CX7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX8:DU8">
-    <cfRule type="cellIs" dxfId="39" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="61" operator="equal">
       <formula>"INC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX8:DU8">
-    <cfRule type="cellIs" dxfId="38" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="62" operator="equal">
       <formula>"CNC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX8:DU8">
-    <cfRule type="cellIs" dxfId="37" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="63" operator="equal">
       <formula>"SE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX8:DU8">
-    <cfRule type="cellIs" dxfId="36" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="64" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX8:DU8">
-    <cfRule type="cellIs" dxfId="35" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="65" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CX9:DW57">
-    <cfRule type="cellIs" dxfId="34" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="66" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY4 DJ4">
-    <cfRule type="cellIs" dxfId="33" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="67" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY4 DJ4">
-    <cfRule type="cellIs" dxfId="32" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="68" operator="equal">
       <formula>"INC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY4 DJ4">
-    <cfRule type="cellIs" dxfId="31" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="69" operator="equal">
       <formula>"CNC"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY4 DJ4">
-    <cfRule type="cellIs" dxfId="30" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="70" operator="equal">
       <formula>"SE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CY4 DJ4">
-    <cfRule type="cellIs" dxfId="29" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="71" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DV8:DW8">
-    <cfRule type="cellIs" dxfId="28" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="72" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43419,18 +43522,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="197">
-        <v>0</v>
-      </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="119"/>
+      <c r="A1" s="193">
+        <v>0</v>
+      </c>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="187"/>
       <c r="L1" s="49"/>
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
@@ -43448,16 +43551,16 @@
       <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="133"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="119"/>
+      <c r="A2" s="132"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="132"/>
+      <c r="J2" s="187"/>
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
@@ -43478,12 +43581,12 @@
       <c r="A3" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="163"/>
-      <c r="C3" s="198" t="s">
+      <c r="B3" s="109"/>
+      <c r="C3" s="194" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="163"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="109"/>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="51"/>
@@ -43510,12 +43613,12 @@
       <c r="A4" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="199">
+      <c r="B4" s="109"/>
+      <c r="C4" s="195">
         <v>3415417</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="163"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="109"/>
       <c r="F4" s="52" t="s">
         <v>65</v>
       </c>
@@ -43548,12 +43651,12 @@
       <c r="A5" s="191" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="163"/>
-      <c r="C5" s="196" t="s">
+      <c r="B5" s="109"/>
+      <c r="C5" s="192" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="163"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="109"/>
       <c r="F5" s="52" t="s">
         <v>67</v>
       </c>
@@ -43584,12 +43687,12 @@
       <c r="A6" s="191" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="163"/>
-      <c r="C6" s="192" t="s">
+      <c r="B6" s="109"/>
+      <c r="C6" s="196" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="113"/>
-      <c r="E6" s="163"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
       <c r="F6" s="52" t="s">
         <v>69</v>
       </c>
@@ -43620,12 +43723,12 @@
       <c r="A7" s="191" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="163"/>
-      <c r="C7" s="193" t="s">
+      <c r="B7" s="109"/>
+      <c r="C7" s="197" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="163"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
       <c r="F7" s="56" t="s">
         <v>70</v>
       </c>
@@ -43653,17 +43756,17 @@
       <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="194" t="s">
+      <c r="A8" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="163"/>
-      <c r="C8" s="195" t="s">
+      <c r="B8" s="109"/>
+      <c r="C8" s="199" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="163"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="109"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
       <c r="J8" s="49"/>
@@ -53998,6 +54101,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A1:J2"/>
@@ -54005,95 +54114,89 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="26" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="25" priority="4">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="24" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="23" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="22" priority="9">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="21" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51:B1001">
-    <cfRule type="expression" dxfId="20" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B1001">
-    <cfRule type="expression" dxfId="19" priority="74">
+    <cfRule type="expression" dxfId="8" priority="74">
       <formula>OR($P51=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B1001">
-    <cfRule type="expression" dxfId="18" priority="84">
+    <cfRule type="expression" dxfId="7" priority="84">
       <formula>OR($R51=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68:B1001">
-    <cfRule type="expression" dxfId="17" priority="88">
+    <cfRule type="expression" dxfId="6" priority="88">
       <formula>OR($P51=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="16" priority="99">
+    <cfRule type="expression" dxfId="5" priority="99">
       <formula>OR($P50=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B67">
-    <cfRule type="expression" dxfId="15" priority="101">
+    <cfRule type="expression" dxfId="4" priority="101">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="14" priority="103">
+    <cfRule type="expression" dxfId="3" priority="103">
       <formula>OR($R50=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B67">
-    <cfRule type="expression" dxfId="13" priority="105">
+    <cfRule type="expression" dxfId="2" priority="105">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="12" priority="107">
+    <cfRule type="expression" dxfId="1" priority="107">
       <formula>OR($P50=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B67">
-    <cfRule type="expression" dxfId="11" priority="109">
+    <cfRule type="expression" dxfId="0" priority="109">
       <formula>OR(#REF!=#REF!,#REF!=#REF!,#REF!=#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54172,21 +54275,21 @@
     <tabColor rgb="FF00B050"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.125" customWidth="1"/>
     <col min="3" max="3" width="24.375" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="4" max="4" width="36.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
       <c r="E1" s="63"/>
       <c r="F1" s="63"/>
     </row>
@@ -54205,7 +54308,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="201" t="s">
+      <c r="A3" s="200" t="s">
         <v>393</v>
       </c>
       <c r="B3" s="67" t="s">
@@ -54219,7 +54322,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="202"/>
+      <c r="A4" s="201"/>
       <c r="B4" s="67" t="s">
         <v>312</v>
       </c>
@@ -54231,7 +54334,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="202"/>
+      <c r="A5" s="201"/>
       <c r="B5" s="67" t="s">
         <v>379</v>
       </c>
@@ -54243,13 +54346,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="202"/>
+      <c r="A6" s="201"/>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
       <c r="D6" s="68"/>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="203"/>
+      <c r="A7" s="202"/>
       <c r="B7" s="69"/>
       <c r="C7" s="69"/>
       <c r="D7" s="70"/>
@@ -54272,7 +54375,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="201" t="s">
+      <c r="A10" s="200" t="s">
         <v>391</v>
       </c>
       <c r="B10" s="67" t="s">
@@ -54286,7 +54389,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="202"/>
+      <c r="A11" s="201"/>
       <c r="B11" s="67" t="s">
         <v>316</v>
       </c>
@@ -54298,7 +54401,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="202"/>
+      <c r="A12" s="201"/>
       <c r="B12" s="67" t="s">
         <v>318</v>
       </c>
@@ -54310,7 +54413,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="202"/>
+      <c r="A13" s="201"/>
       <c r="B13" s="67" t="s">
         <v>320</v>
       </c>
@@ -54322,7 +54425,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="203"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="69" t="s">
         <v>322</v>
       </c>
@@ -54348,7 +54451,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="201" t="s">
+      <c r="A17" s="200" t="s">
         <v>397</v>
       </c>
       <c r="B17" s="67" t="s">
@@ -54362,7 +54465,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="202"/>
+      <c r="A18" s="201"/>
       <c r="B18" s="67" t="s">
         <v>328</v>
       </c>
@@ -54374,7 +54477,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="202"/>
+      <c r="A19" s="201"/>
       <c r="B19" s="67" t="s">
         <v>331</v>
       </c>
@@ -54386,13 +54489,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="202"/>
+      <c r="A20" s="201"/>
       <c r="B20" s="67"/>
       <c r="C20" s="67"/>
       <c r="D20" s="68"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="203"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="69"/>
       <c r="C21" s="69"/>
       <c r="D21" s="70"/>
@@ -54412,7 +54515,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="201" t="s">
+      <c r="A24" s="200" t="s">
         <v>392</v>
       </c>
       <c r="B24" s="67" t="s">
@@ -54426,7 +54529,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="202"/>
+      <c r="A25" s="201"/>
       <c r="B25" s="67" t="s">
         <v>335</v>
       </c>
@@ -54438,7 +54541,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="202"/>
+      <c r="A26" s="201"/>
       <c r="B26" s="67" t="s">
         <v>337</v>
       </c>
@@ -54450,7 +54553,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="202"/>
+      <c r="A27" s="201"/>
       <c r="B27" s="67" t="s">
         <v>339</v>
       </c>
@@ -54462,7 +54565,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="203"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="69" t="s">
         <v>341</v>
       </c>
@@ -54488,7 +54591,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="201" t="s">
+      <c r="A31" s="200" t="s">
         <v>394</v>
       </c>
       <c r="B31" s="67" t="s">
@@ -54502,7 +54605,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="202"/>
+      <c r="A32" s="201"/>
       <c r="B32" s="67" t="s">
         <v>345</v>
       </c>
@@ -54514,7 +54617,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="202"/>
+      <c r="A33" s="201"/>
       <c r="B33" s="67" t="s">
         <v>347</v>
       </c>
@@ -54526,7 +54629,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="202"/>
+      <c r="A34" s="201"/>
       <c r="B34" s="67" t="s">
         <v>401</v>
       </c>
@@ -54536,7 +54639,7 @@
       <c r="D34" s="68"/>
     </row>
     <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="203"/>
+      <c r="A35" s="202"/>
       <c r="B35" s="69"/>
       <c r="C35" s="69"/>
       <c r="D35" s="70"/>
@@ -54556,7 +54659,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="201" t="s">
+      <c r="A38" s="200" t="s">
         <v>396</v>
       </c>
       <c r="B38" s="67" t="s">
@@ -54570,7 +54673,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="202"/>
+      <c r="A39" s="201"/>
       <c r="B39" s="67" t="s">
         <v>395</v>
       </c>
@@ -54582,7 +54685,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="202"/>
+      <c r="A40" s="201"/>
       <c r="B40" s="67" t="s">
         <v>352</v>
       </c>
@@ -54594,7 +54697,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="202"/>
+      <c r="A41" s="201"/>
       <c r="B41" s="67" t="s">
         <v>354</v>
       </c>
@@ -54606,254 +54709,266 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="203"/>
-      <c r="B42" s="69" t="s">
+      <c r="A42" s="201"/>
+      <c r="B42" s="204" t="s">
+        <v>403</v>
+      </c>
+      <c r="C42" s="204" t="s">
+        <v>404</v>
+      </c>
+      <c r="D42" s="205" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A43" s="202"/>
+      <c r="B43" s="69" t="s">
         <v>356</v>
       </c>
-      <c r="C42" s="69" t="s">
+      <c r="C43" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="D42" s="106" t="s">
+      <c r="D43" s="106" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="64" t="s">
+    <row r="44" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="45" spans="1:4" ht="15" customHeight="1">
+      <c r="A45" s="64" t="s">
         <v>324</v>
       </c>
-      <c r="B44" s="65" t="s">
+      <c r="B45" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="65" t="s">
+      <c r="C45" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="66" t="s">
+      <c r="D45" s="66" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1">
-      <c r="A45" s="201" t="s">
+    <row r="46" spans="1:4" ht="15" customHeight="1">
+      <c r="A46" s="200" t="s">
         <v>398</v>
       </c>
-      <c r="B45" s="67" t="s">
+      <c r="B46" s="67" t="s">
         <v>358</v>
       </c>
-      <c r="C45" s="67" t="s">
+      <c r="C46" s="67" t="s">
         <v>359</v>
       </c>
-      <c r="D45" s="105" t="s">
+      <c r="D46" s="105" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="202"/>
-      <c r="B46" s="67" t="s">
+    <row r="47" spans="1:4" ht="15" customHeight="1">
+      <c r="A47" s="201"/>
+      <c r="B47" s="67" t="s">
         <v>360</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C47" s="67" t="s">
         <v>361</v>
       </c>
-      <c r="D46" s="105" t="s">
+      <c r="D47" s="105" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="202"/>
-      <c r="B47" s="67" t="s">
+    <row r="48" spans="1:4" ht="15" customHeight="1">
+      <c r="A48" s="201"/>
+      <c r="B48" s="67" t="s">
         <v>362</v>
       </c>
-      <c r="C47" s="67" t="s">
+      <c r="C48" s="67" t="s">
         <v>363</v>
       </c>
-      <c r="D47" s="105" t="s">
+      <c r="D48" s="105" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="202"/>
-      <c r="B48" s="67" t="s">
+    <row r="49" spans="1:4" ht="15" customHeight="1">
+      <c r="A49" s="201"/>
+      <c r="B49" s="67" t="s">
         <v>364</v>
       </c>
-      <c r="C48" s="67" t="s">
+      <c r="C49" s="67" t="s">
         <v>365</v>
       </c>
-      <c r="D48" s="105" t="s">
+      <c r="D49" s="105" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A49" s="203"/>
-      <c r="B49" s="69" t="s">
+    <row r="50" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A50" s="202"/>
+      <c r="B50" s="69" t="s">
         <v>366</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C50" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="D49" s="106" t="s">
+      <c r="D50" s="106" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
-    <row r="51" spans="1:4" ht="15" customHeight="1">
-      <c r="A51" s="64" t="s">
+    <row r="51" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="52" spans="1:4" ht="15" customHeight="1">
+      <c r="A52" s="64" t="s">
         <v>325</v>
       </c>
-      <c r="B51" s="65" t="s">
+      <c r="B52" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="65" t="s">
+      <c r="C52" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="66" t="s">
+      <c r="D52" s="66" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1">
-      <c r="A52" s="201" t="s">
+    <row r="53" spans="1:4" ht="15" customHeight="1">
+      <c r="A53" s="200" t="s">
         <v>399</v>
       </c>
-      <c r="B52" s="67" t="s">
+      <c r="B53" s="67" t="s">
         <v>368</v>
       </c>
-      <c r="C52" s="67" t="s">
+      <c r="C53" s="67" t="s">
         <v>369</v>
       </c>
-      <c r="D52" s="105" t="s">
+      <c r="D53" s="105" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1">
-      <c r="A53" s="202"/>
-      <c r="B53" s="67" t="s">
+    <row r="54" spans="1:4" ht="15" customHeight="1">
+      <c r="A54" s="201"/>
+      <c r="B54" s="67" t="s">
         <v>370</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C54" s="67" t="s">
         <v>371</v>
       </c>
-      <c r="D53" s="105" t="s">
+      <c r="D54" s="105" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1">
-      <c r="A54" s="202"/>
-      <c r="B54" s="67" t="s">
+    <row r="55" spans="1:4" ht="15" customHeight="1">
+      <c r="A55" s="201"/>
+      <c r="B55" s="67" t="s">
         <v>372</v>
       </c>
-      <c r="C54" s="67" t="s">
+      <c r="C55" s="67" t="s">
         <v>373</v>
       </c>
-      <c r="D54" s="105" t="s">
+      <c r="D55" s="105" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1">
-      <c r="A55" s="202"/>
-      <c r="B55" s="67" t="s">
+    <row r="56" spans="1:4" ht="15" customHeight="1">
+      <c r="A56" s="201"/>
+      <c r="B56" s="67" t="s">
         <v>375</v>
       </c>
-      <c r="C55" s="67" t="s">
+      <c r="C56" s="67" t="s">
         <v>376</v>
       </c>
-      <c r="D55" s="105" t="s">
+      <c r="D56" s="105" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A56" s="203"/>
-      <c r="B56" s="69" t="s">
+    <row r="57" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A57" s="202"/>
+      <c r="B57" s="69" t="s">
         <v>377</v>
       </c>
-      <c r="C56" s="69" t="s">
+      <c r="C57" s="69" t="s">
         <v>378</v>
       </c>
-      <c r="D56" s="106" t="s">
+      <c r="D57" s="106" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
-    <row r="58" spans="1:4" ht="15" customHeight="1">
-      <c r="A58" s="64" t="s">
+    <row r="58" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="59" spans="1:4" ht="15" customHeight="1">
+      <c r="A59" s="64" t="s">
         <v>381</v>
       </c>
-      <c r="B58" s="65" t="s">
+      <c r="B59" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="65" t="s">
+      <c r="C59" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="D58" s="66" t="s">
+      <c r="D59" s="66" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15" customHeight="1">
-      <c r="A59" s="201" t="s">
+    <row r="60" spans="1:4" ht="15" customHeight="1">
+      <c r="A60" s="200" t="s">
         <v>400</v>
       </c>
-      <c r="B59" s="67" t="s">
+      <c r="B60" s="67" t="s">
         <v>382</v>
       </c>
-      <c r="C59" s="67" t="s">
+      <c r="C60" s="67" t="s">
         <v>383</v>
       </c>
-      <c r="D59" s="105" t="s">
+      <c r="D60" s="105" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15" customHeight="1">
-      <c r="A60" s="202"/>
-      <c r="B60" s="67" t="s">
+    <row r="61" spans="1:4" ht="15" customHeight="1">
+      <c r="A61" s="201"/>
+      <c r="B61" s="67" t="s">
         <v>384</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C61" s="67" t="s">
         <v>385</v>
       </c>
-      <c r="D60" s="105" t="s">
+      <c r="D61" s="105" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15" customHeight="1">
-      <c r="A61" s="202"/>
-      <c r="B61" s="67" t="s">
+    <row r="62" spans="1:4" ht="15" customHeight="1">
+      <c r="A62" s="201"/>
+      <c r="B62" s="67" t="s">
         <v>386</v>
       </c>
-      <c r="C61" s="67" t="s">
+      <c r="C62" s="67" t="s">
         <v>387</v>
       </c>
-      <c r="D61" s="105" t="s">
+      <c r="D62" s="105" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15" customHeight="1">
-      <c r="A62" s="202"/>
-      <c r="B62" s="67" t="s">
+    <row r="63" spans="1:4" ht="15" customHeight="1">
+      <c r="A63" s="201"/>
+      <c r="B63" s="67" t="s">
         <v>388</v>
       </c>
-      <c r="C62" s="67" t="s">
+      <c r="C63" s="67" t="s">
         <v>389</v>
       </c>
-      <c r="D62" s="105" t="s">
+      <c r="D63" s="105" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15" customHeight="1" thickBot="1">
-      <c r="A63" s="203"/>
-      <c r="B63" s="69"/>
-      <c r="C63" s="69"/>
-      <c r="D63" s="106"/>
+    <row r="64" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A64" s="202"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A59:A63"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A38:A42"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" xr:uid="{FA945836-C25F-4474-8842-6571893ABEC3}"/>
@@ -54877,23 +54992,24 @@
     <hyperlink ref="D39" r:id="rId19" xr:uid="{2B1CC0C3-9EBA-4237-AE39-8EECDFDB332E}"/>
     <hyperlink ref="D40" r:id="rId20" xr:uid="{D9E5286D-BB25-415E-816C-EC4C2AC0AD36}"/>
     <hyperlink ref="D41" r:id="rId21" xr:uid="{858F76E0-AC42-4EE4-AE28-7C22F530C001}"/>
-    <hyperlink ref="D42" r:id="rId22" xr:uid="{AE2AE62E-751D-4129-98B4-3378821D7C8F}"/>
-    <hyperlink ref="D45" r:id="rId23" xr:uid="{A9FD7F94-5319-4B7E-98A9-CF339C13B44B}"/>
-    <hyperlink ref="D46" r:id="rId24" xr:uid="{6D5D8002-AC4E-4CDF-A584-4282C3563E6A}"/>
-    <hyperlink ref="D47" r:id="rId25" xr:uid="{F78DDB51-9B36-45B2-A886-4DA47CF56FF1}"/>
-    <hyperlink ref="D48" r:id="rId26" xr:uid="{95BE7735-F0A1-4224-8DB7-2754A5C2F110}"/>
-    <hyperlink ref="D49" r:id="rId27" xr:uid="{8F1428B9-D1B6-4A15-850E-3B5AB333E5B6}"/>
-    <hyperlink ref="D52" r:id="rId28" xr:uid="{1FF8371E-7C20-4097-A07D-66B02C44B570}"/>
-    <hyperlink ref="D53" r:id="rId29" xr:uid="{F05EAE91-443C-4557-AB32-DD362C6654E5}"/>
-    <hyperlink ref="D54" r:id="rId30" xr:uid="{6EBAD996-6F61-4D1E-8E07-6F47EEAF96EE}"/>
-    <hyperlink ref="D55" r:id="rId31" xr:uid="{48EAF0F4-FD59-41AB-9D50-6F6355392185}"/>
-    <hyperlink ref="D56" r:id="rId32" xr:uid="{2BE48D34-0AFD-4799-ABA0-D8E70E5DB6C3}"/>
+    <hyperlink ref="D43" r:id="rId22" xr:uid="{AE2AE62E-751D-4129-98B4-3378821D7C8F}"/>
+    <hyperlink ref="D46" r:id="rId23" xr:uid="{A9FD7F94-5319-4B7E-98A9-CF339C13B44B}"/>
+    <hyperlink ref="D47" r:id="rId24" xr:uid="{6D5D8002-AC4E-4CDF-A584-4282C3563E6A}"/>
+    <hyperlink ref="D48" r:id="rId25" xr:uid="{F78DDB51-9B36-45B2-A886-4DA47CF56FF1}"/>
+    <hyperlink ref="D49" r:id="rId26" xr:uid="{95BE7735-F0A1-4224-8DB7-2754A5C2F110}"/>
+    <hyperlink ref="D50" r:id="rId27" xr:uid="{8F1428B9-D1B6-4A15-850E-3B5AB333E5B6}"/>
+    <hyperlink ref="D53" r:id="rId28" xr:uid="{1FF8371E-7C20-4097-A07D-66B02C44B570}"/>
+    <hyperlink ref="D54" r:id="rId29" xr:uid="{F05EAE91-443C-4557-AB32-DD362C6654E5}"/>
+    <hyperlink ref="D55" r:id="rId30" xr:uid="{6EBAD996-6F61-4D1E-8E07-6F47EEAF96EE}"/>
+    <hyperlink ref="D56" r:id="rId31" xr:uid="{48EAF0F4-FD59-41AB-9D50-6F6355392185}"/>
+    <hyperlink ref="D57" r:id="rId32" xr:uid="{2BE48D34-0AFD-4799-ABA0-D8E70E5DB6C3}"/>
     <hyperlink ref="D14" r:id="rId33" xr:uid="{B42E3AFE-1346-4EBA-9FCA-66D78FB7217E}"/>
     <hyperlink ref="D5" r:id="rId34" xr:uid="{4A1904B0-0837-40AC-886C-126483D63A70}"/>
-    <hyperlink ref="D59" r:id="rId35" xr:uid="{1A0FD7F9-FAB2-4C46-96E1-23C278BAAFEE}"/>
-    <hyperlink ref="D60" r:id="rId36" xr:uid="{C49ABC81-DB8E-4F2E-9C85-2D624440584B}"/>
-    <hyperlink ref="D61" r:id="rId37" xr:uid="{C4482557-B698-4542-81E9-63BE65D1CD80}"/>
-    <hyperlink ref="D62" r:id="rId38" xr:uid="{E4C328B2-4566-46A1-ADF6-DEFB234BD68A}"/>
+    <hyperlink ref="D60" r:id="rId35" xr:uid="{1A0FD7F9-FAB2-4C46-96E1-23C278BAAFEE}"/>
+    <hyperlink ref="D61" r:id="rId36" xr:uid="{C49ABC81-DB8E-4F2E-9C85-2D624440584B}"/>
+    <hyperlink ref="D62" r:id="rId37" xr:uid="{C4482557-B698-4542-81E9-63BE65D1CD80}"/>
+    <hyperlink ref="D63" r:id="rId38" xr:uid="{E4C328B2-4566-46A1-ADF6-DEFB234BD68A}"/>
+    <hyperlink ref="D42" r:id="rId39" xr:uid="{9A930166-67FB-4F30-AF7F-391514C3BA04}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
